--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -438,20 +438,20 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>52W RS High</t>
+          <t>% Off RS High</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -560,7 +560,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="n">
+        <v>-8.539999999999999</v>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -616,7 +618,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="n">
+        <v>-1.83</v>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -672,7 +676,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -728,7 +734,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr"/>
+      <c r="J5" s="1" t="n">
+        <v>-1.91</v>
+      </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -784,7 +792,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="n">
+        <v>-14.32</v>
+      </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -840,7 +850,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="n">
+        <v>-4.6</v>
+      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -896,7 +908,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr"/>
+      <c r="J8" s="1" t="n">
+        <v>-2.78</v>
+      </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -952,7 +966,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr"/>
+      <c r="J9" s="1" t="n">
+        <v>-4.35</v>
+      </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1008,7 +1024,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="n">
+        <v>-7.69</v>
+      </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -1064,7 +1082,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr"/>
+      <c r="J11" s="1" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1120,7 +1140,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr"/>
+      <c r="J12" s="1" t="n">
+        <v>-6.93</v>
+      </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1176,7 +1198,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="n">
+        <v>-3.65</v>
+      </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -1232,7 +1256,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="n">
+        <v>-16.52</v>
+      </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -1288,7 +1314,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="n">
+        <v>-7.87</v>
+      </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -1344,7 +1372,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr"/>
+      <c r="J16" s="1" t="n">
+        <v>-11.6</v>
+      </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -1400,7 +1430,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr"/>
+      <c r="J17" s="1" t="n">
+        <v>-15.27</v>
+      </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -1456,7 +1488,9 @@
           <t>Down</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr"/>
+      <c r="J18" s="1" t="n">
+        <v>-9.949999999999999</v>
+      </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1512,7 +1546,9 @@
           <t>Up</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="n">
+        <v>-25.9</v>
+      </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1556,8 +1592,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J19">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
-      <formula>"Yes"</formula>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="-15"/>
+        <cfvo type="num" val="-5"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K19">
@@ -1605,25 +1648,25 @@
   <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>918.7</v>
+        <v>938.6</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-2.12</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-2.07</v>
+        <v>0.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>11.39</v>
+        <v>13.8</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.41</v>
+        <v>16.89</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-8.539999999999999</v>
+        <v>-6.55</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -711,31 +711,31 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>16.72</v>
+        <v>1484.3</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-1.47</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.42</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>4.05</v>
+        <v>-2.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>9.82</v>
+        <v>2.68</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-1.91</v>
+        <v>-16.41</v>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -769,31 +769,31 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1521.45</v>
+        <v>32688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2.56</v>
+        <v>0.05</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.48</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>5.25</v>
+        <v>2.19</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-14.32</v>
+        <v>-2.22</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,40 +827,40 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>102.41</v>
+        <v>58521.4</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.49</v>
+        <v>1.63</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-1.73</v>
+        <v>0.87</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-2.45</v>
+        <v>0.4</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>3.78</v>
+        <v>1.39</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-4.6</v>
+        <v>-4.35</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="1" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -889,36 +889,36 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>32498.4</v>
+        <v>11737.75</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.53</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-1.05</v>
+        <v>0.49</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.6</v>
+        <v>0.78</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-2.78</v>
+        <v>-7.43</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,35 +943,35 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>58521.4</v>
+        <v>26860.75</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.87</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.4</v>
+        <v>-0.13</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.39</v>
+        <v>-0.42</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-4.35</v>
+        <v>-5.94</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1005,31 +1005,31 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>11705</v>
+        <v>9429.450000000001</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>-0.23</v>
+        <v>0.05</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.21</v>
+        <v>-1.29</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-7.69</v>
+        <v>-3.11</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -1044,14 +1044,14 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,45 +1059,45 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>27099.75</v>
+        <v>39242.05</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.76</v>
+        <v>-3.54</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.46</v>
+        <v>-1.09</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-5.1</v>
+        <v>-7.02</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1117,23 +1117,23 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>39277</v>
+        <v>49310.6</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-3.46</v>
+        <v>-1.25</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-1</v>
+        <v>-2.69</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-6.93</v>
+        <v>-15.56</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>9377.35</v>
+        <v>12688.9</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.5</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-1.84</v>
+        <v>-3.01</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-1.31</v>
+        <v>-3.45</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-3.65</v>
+        <v>-9.81</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>48748.7</v>
+        <v>9891.450000000001</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-1.09</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-2.37</v>
+        <v>-2.51</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-3.79</v>
+        <v>-3.86</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,33 +1257,33 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-16.52</v>
+        <v>-7.31</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="M14" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1291,23 +1291,23 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>9832.1</v>
+        <v>8451.6</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.55</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-3.1</v>
+        <v>-4.17</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-4.44</v>
+        <v>-6.55</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -1315,33 +1315,33 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-7.87</v>
+        <v>-14.56</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,23 +1349,23 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12436.95</v>
+        <v>9911.25</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-1.99</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-1.93</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-4.94</v>
+        <v>-3.25</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-5.37</v>
+        <v>-8.27</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-11.6</v>
+        <v>-10.19</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1411,36 +1411,36 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>8381.75</v>
+        <v>29226.6</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.83</v>
+        <v>1.75</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.78</v>
+        <v>4.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-4.97</v>
+        <v>2.1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-7.32</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-15.27</v>
+        <v>-25.9</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>9938.549999999999</v>
+        <v>16282.9</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.28</v>
+        <v/>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.33</v>
+        <v/>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-2.98</v>
+        <v/>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-8.01</v>
+        <v/>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1527,46 +1527,46 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>29226.6</v>
+        <v>102.41</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>1.75</v>
+        <v>0.49</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>4.4</v>
+        <v>-1.73</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>2.1</v>
+        <v>-2.45</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-9.960000000000001</v>
+        <v>3.78</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-25.9</v>
+        <v>-4.6</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="N19" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -1773,25 +1773,25 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
@@ -1800,31 +1800,31 @@
         <v>3</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1834,25 +1834,25 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>1</v>
@@ -1861,31 +1861,31 @@
         <v>3</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -1895,25 +1895,25 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>1</v>
@@ -1922,31 +1922,31 @@
         <v>3</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1956,25 +1956,25 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>1</v>
@@ -1983,31 +1983,31 @@
         <v>3</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -2017,25 +2017,25 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
@@ -2044,31 +2044,31 @@
         <v>3</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -2078,25 +2078,25 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>1</v>
@@ -2105,31 +2105,31 @@
         <v>3</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -2139,25 +2139,25 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>1</v>
@@ -2166,31 +2166,31 @@
         <v>3</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2200,58 +2200,58 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -2261,58 +2261,58 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -2322,58 +2322,58 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -2383,58 +2383,58 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -2444,58 +2444,58 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -2505,58 +2505,58 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -2566,58 +2566,58 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -2627,58 +2627,58 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -2688,58 +2688,58 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -2749,58 +2749,58 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -2810,58 +2810,58 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -2871,58 +2871,58 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -2932,58 +2932,58 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2993,58 +2993,58 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -3054,58 +3054,58 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -3115,58 +3115,58 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -3176,22 +3176,22 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>4</v>
@@ -3203,31 +3203,31 @@
         <v>1</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -3237,19 +3237,19 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>1</v>
@@ -3258,37 +3258,37 @@
         <v>2</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -3298,19 +3298,19 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>4</v>
@@ -3319,37 +3319,37 @@
         <v>1</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -3359,16 +3359,16 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>5</v>
@@ -3380,37 +3380,37 @@
         <v>1</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -3420,58 +3420,58 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P29" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -3481,58 +3481,58 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -3542,58 +3542,58 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -3603,58 +3603,58 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -3664,58 +3664,58 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
@@ -3725,58 +3725,58 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
@@ -3786,58 +3786,58 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
@@ -3847,16 +3847,16 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>3</v>
@@ -3868,37 +3868,37 @@
         <v>2</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>4</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
@@ -3908,58 +3908,58 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -3969,16 +3969,16 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>3</v>
@@ -3990,37 +3990,37 @@
         <v>2</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
@@ -4030,16 +4030,16 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>3</v>
@@ -4051,37 +4051,37 @@
         <v>2</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
@@ -4091,58 +4091,58 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
@@ -4152,58 +4152,58 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -4213,58 +4213,58 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
@@ -4274,58 +4274,58 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -4335,58 +4335,58 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -4396,58 +4396,58 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
@@ -4457,58 +4457,58 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -4518,58 +4518,58 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -4579,58 +4579,58 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
@@ -4640,58 +4640,58 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
@@ -4701,58 +4701,58 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
@@ -4762,58 +4762,58 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -4823,58 +4823,58 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -4884,58 +4884,58 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -4945,58 +4945,58 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
@@ -5006,37 +5006,37 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>6</v>
@@ -5045,19 +5045,19 @@
         <v>5</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -5067,37 +5067,37 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>6</v>
@@ -5106,19 +5106,19 @@
         <v>5</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -5128,37 +5128,37 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>6</v>
@@ -5167,19 +5167,19 @@
         <v>5</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
@@ -5189,37 +5189,37 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>6</v>
@@ -5228,19 +5228,19 @@
         <v>5</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
@@ -5250,58 +5250,58 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -5311,37 +5311,37 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>6</v>
@@ -5350,19 +5350,19 @@
         <v>5</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
@@ -5372,58 +5372,58 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -5433,58 +5433,58 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
@@ -5494,58 +5494,58 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
@@ -5555,58 +5555,58 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -5616,19 +5616,19 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>2</v>
@@ -5637,37 +5637,37 @@
         <v>1</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
@@ -5677,19 +5677,19 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>1</v>
@@ -5698,37 +5698,37 @@
         <v>2</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>938.6</v>
+        <v>918.7</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0</v>
+        <v>-2.12</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.05</v>
+        <v>-2.07</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>13.8</v>
+        <v>11.39</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>16.89</v>
+        <v>14.41</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-6.55</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -715,36 +715,36 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1484.3</v>
+        <v>1521.45</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.05</v>
+        <v>2.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-2.5</v>
+        <v>-0.06</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>2.68</v>
+        <v>5.25</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-16.41</v>
+        <v>-14.32</v>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>32688</v>
+        <v>32498.4</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.48</v>
+        <v>-1.05</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-2.22</v>
+        <v>-2.78</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" s="1" t="inlineStr">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>11737.75</v>
+        <v>11705</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.23</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -909,26 +909,26 @@
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-7.43</v>
+        <v>-7.69</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="M8" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>26860.75</v>
+        <v>27099.75</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.76</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-0.42</v>
+        <v>0.46</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-5.94</v>
+        <v>-5.1</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,23 +1001,23 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>9429.450000000001</v>
+        <v>39277</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-1.29</v>
+        <v>-3.46</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-0.76</v>
+        <v>-1</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-3.11</v>
+        <v>-6.93</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,23 +1059,23 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>39242.05</v>
+        <v>9377.35</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-3.54</v>
+        <v>-1.84</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.09</v>
+        <v>-1.31</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-7.02</v>
+        <v>-3.65</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>49310.6</v>
+        <v>48748.7</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.05</v>
+        <v>-1.09</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-1.25</v>
+        <v>-2.37</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-2.69</v>
+        <v>-3.79</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-15.56</v>
+        <v>-16.52</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>12688.9</v>
+        <v>9832.1</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.55</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-3.01</v>
+        <v>-3.1</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-3.45</v>
+        <v>-4.44</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-9.81</v>
+        <v>-7.87</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>9891.450000000001</v>
+        <v>12436.95</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.05</v>
+        <v>-1.93</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-2.51</v>
+        <v>-4.94</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-3.86</v>
+        <v>-5.37</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,11 +1257,11 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-7.31</v>
+        <v>-11.6</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -1295,19 +1295,19 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>8451.6</v>
+        <v>8381.75</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.78</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-4.17</v>
+        <v>-4.97</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-6.55</v>
+        <v>-7.32</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -1315,16 +1315,16 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-14.56</v>
+        <v>-15.27</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M15" s="1" t="inlineStr">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>9911.25</v>
+        <v>9938.549999999999</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.05</v>
+        <v>0.33</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-3.25</v>
+        <v>-2.98</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-8.27</v>
+        <v>-8.01</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-10.19</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -1788,10 +1788,10 @@
         <v>2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
@@ -1800,13 +1800,13 @@
         <v>3</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>7</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N2" s="1" t="n">
         <v>15</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -645,7 +645,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -653,31 +653,31 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>29250.6</v>
+        <v>16.72</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v/>
+        <v>-1.47</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v/>
+        <v>-0.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v/>
+        <v>4.05</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v/>
+        <v>9.82</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0</v>
+        <v>-1.91</v>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
@@ -686,17 +686,17 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -761,7 +761,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -769,23 +769,23 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>32498.4</v>
+        <v>102.41</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.58</v>
+        <v>0.49</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.53</v>
+        <v>-1.73</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-1.05</v>
+        <v>-2.45</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.6</v>
+        <v>3.78</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-2.78</v>
+        <v>-4.6</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,40 +827,40 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>58521.4</v>
+        <v>32498.4</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.63</v>
+        <v>-0.58</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.87</v>
+        <v>-0.53</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.4</v>
+        <v>-1.05</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-4.35</v>
+        <v>-2.78</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M7" s="1" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,23 +885,23 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>11705</v>
+        <v>58521.4</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.28</v>
+        <v>1.63</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.23</v>
+        <v>0.87</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.5</v>
+        <v>1.39</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-7.69</v>
+        <v>-4.35</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -928,14 +928,14 @@
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,23 +943,23 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>27099.75</v>
+        <v>11705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.28</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.23</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.76</v>
+        <v>0.21</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -967,33 +967,33 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-5.1</v>
+        <v>-7.69</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="M9" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,31 +1001,31 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>39277</v>
+        <v>27099.75</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.09</v>
+        <v>0.89</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-3.46</v>
+        <v>0.76</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-1</v>
+        <v>0.46</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-6.93</v>
+        <v>-5.1</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N10" s="1" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,40 +1059,40 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>9377.35</v>
+        <v>26903.35</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.55</v>
+        <v>0.27</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-0.5</v>
+        <v>0.32</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-1.84</v>
+        <v>0.65</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.31</v>
+        <v>-0.59</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-3.65</v>
+        <v>-5.05</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M11" s="1" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1117,23 +1117,23 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>48748.7</v>
+        <v>39277</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-1.14</v>
+        <v>0.09</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-2.37</v>
+        <v>-3.46</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-3.79</v>
+        <v>-1</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,33 +1141,33 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-16.52</v>
+        <v>-6.93</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>9832.1</v>
+        <v>9377.35</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-3.1</v>
+        <v>-1.84</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-4.44</v>
+        <v>-1.31</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-7.87</v>
+        <v>-3.65</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12436.95</v>
+        <v>48748.7</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-1.99</v>
+        <v>-1.14</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-1.93</v>
+        <v>-1.09</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-4.94</v>
+        <v>-2.37</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-5.37</v>
+        <v>-3.79</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-11.6</v>
+        <v>-16.52</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
@@ -1276,14 +1276,14 @@
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1291,23 +1291,23 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>8381.75</v>
+        <v>9832.1</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.83</v>
+        <v>-0.6</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.78</v>
+        <v>-0.55</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-4.97</v>
+        <v>-3.1</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-7.32</v>
+        <v>-4.44</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-15.27</v>
+        <v>-7.87</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
@@ -1329,19 +1329,19 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,23 +1349,23 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>9938.549999999999</v>
+        <v>12436.95</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.28</v>
+        <v>-1.99</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.33</v>
+        <v>-1.93</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-2.98</v>
+        <v>-4.94</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-8.01</v>
+        <v>-5.37</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,33 +1373,33 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-9.949999999999999</v>
+        <v>-11.6</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1411,36 +1411,36 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>29226.6</v>
+        <v>8381.75</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1.75</v>
+        <v>-0.83</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>4.4</v>
+        <v>-0.78</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>2.1</v>
+        <v>-4.97</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-9.960000000000001</v>
+        <v>-7.32</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-25.9</v>
+        <v>-15.27</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>16282.9</v>
+        <v>9938.549999999999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v/>
+        <v>0.28</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v/>
+        <v>0.33</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v/>
+        <v>-2.98</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v/>
+        <v>-8.01</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1527,46 +1527,46 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>102.41</v>
+        <v>29226.6</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>0.49</v>
+        <v>1.75</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>-1.73</v>
+        <v>4.4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-2.45</v>
+        <v>2.1</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>3.78</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-4.6</v>
+        <v>-25.9</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1773,58 +1773,58 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1834,58 +1834,58 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1895,58 +1895,58 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1956,58 +1956,58 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2017,58 +2017,58 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2078,58 +2078,58 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2139,58 +2139,58 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2200,58 +2200,58 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2261,58 +2261,58 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2322,58 +2322,58 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2383,43 +2383,43 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>4</v>
@@ -2428,13 +2428,13 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2444,43 +2444,43 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>4</v>
@@ -2489,13 +2489,13 @@
         <v>3</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2505,43 +2505,43 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>4</v>
@@ -2550,13 +2550,13 @@
         <v>3</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2566,43 +2566,43 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>4</v>
@@ -2611,13 +2611,13 @@
         <v>3</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>4</v>
@@ -2648,22 +2648,22 @@
         <v>6</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>7</v>
@@ -2672,13 +2672,13 @@
         <v>3</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>8</v>
@@ -2697,7 +2697,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>7</v>
@@ -2709,22 +2709,22 @@
         <v>6</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>4</v>
@@ -2733,13 +2733,13 @@
         <v>3</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2749,43 +2749,43 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>4</v>
@@ -2794,13 +2794,13 @@
         <v>3</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2810,16 +2810,16 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4</v>
@@ -2831,22 +2831,22 @@
         <v>7</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>5</v>
@@ -2855,13 +2855,13 @@
         <v>3</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2871,58 +2871,58 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>6</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2932,16 +2932,16 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -2956,19 +2956,19 @@
         <v>3</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O21" s="1" t="n">
         <v>6</v>
@@ -2977,13 +2977,13 @@
         <v>2</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2993,19 +2993,19 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>4</v>
@@ -3017,19 +3017,19 @@
         <v>3</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O22" s="1" t="n">
         <v>6</v>
@@ -3038,13 +3038,13 @@
         <v>2</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>11</v>
@@ -3063,10 +3063,10 @@
         <v>7</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>4</v>
@@ -3078,7 +3078,7 @@
         <v>3</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>9</v>
@@ -3090,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O23" s="1" t="n">
         <v>6</v>
@@ -3099,13 +3099,13 @@
         <v>2</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>12</v>
@@ -3136,10 +3136,10 @@
         <v>5</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>9</v>
@@ -3151,7 +3151,7 @@
         <v>11</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>6</v>
@@ -3160,13 +3160,13 @@
         <v>3</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3176,16 +3176,16 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>11</v>
@@ -3194,13 +3194,13 @@
         <v>5</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>9</v>
@@ -3212,22 +3212,22 @@
         <v>8</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -3237,16 +3237,16 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>8</v>
@@ -3255,40 +3255,40 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>6</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3298,58 +3298,58 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>6</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -3359,58 +3359,58 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -3420,58 +3420,58 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3481,58 +3481,58 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3542,16 +3542,16 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>5</v>
@@ -3560,40 +3560,40 @@
         <v>4</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3603,58 +3603,58 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3664,37 +3664,37 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>7</v>
@@ -3706,16 +3706,16 @@
         <v>8</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3725,43 +3725,43 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>6</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>8</v>
@@ -3770,13 +3770,13 @@
         <v>7</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3786,58 +3786,58 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3847,58 +3847,58 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -3908,58 +3908,58 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3969,58 +3969,58 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4030,19 +4030,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>1</v>
@@ -4051,37 +4051,37 @@
         <v>2</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -4091,58 +4091,58 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -4152,58 +4152,58 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4213,58 +4213,58 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -4274,58 +4274,58 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4335,58 +4335,58 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4396,58 +4396,58 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -4457,58 +4457,58 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4518,58 +4518,58 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4579,58 +4579,58 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4640,58 +4640,58 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4701,58 +4701,58 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4762,58 +4762,58 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4823,58 +4823,58 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -4884,58 +4884,58 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4945,58 +4945,58 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -5006,58 +5006,58 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P55" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5067,22 +5067,22 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>1</v>
@@ -5091,34 +5091,34 @@
         <v>7</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -5128,58 +5128,58 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -5189,58 +5189,58 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P58" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -5250,37 +5250,37 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>5</v>
@@ -5295,13 +5295,13 @@
         <v>6</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -5311,58 +5311,58 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -5372,37 +5372,37 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>5</v>
@@ -5417,13 +5417,13 @@
         <v>7</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5433,37 +5433,37 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>5</v>
@@ -5478,13 +5478,13 @@
         <v>7</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -5494,37 +5494,37 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>8</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>5</v>
@@ -5539,13 +5539,13 @@
         <v>7</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -5555,37 +5555,37 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K64" s="1" t="n">
         <v>9</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>5</v>
@@ -5603,10 +5603,10 @@
         <v>7</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -5616,19 +5616,19 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>2</v>
@@ -5637,16 +5637,16 @@
         <v>1</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K65" s="1" t="n">
         <v>9</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>5</v>
@@ -5664,10 +5664,10 @@
         <v>7</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -5677,19 +5677,19 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>1</v>
@@ -5698,16 +5698,16 @@
         <v>2</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>9</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>5</v>
@@ -5725,10 +5725,10 @@
         <v>6</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -438,12 +438,12 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -1648,25 +1648,25 @@
   <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="7" customWidth="1" min="14" max="14"/>
-    <col width="7" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>918.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-2.12</v>
+        <v>1.11</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-2.07</v>
+        <v>-1.98</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.41</v>
+        <v>14.18</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>25645</v>
+        <v>26.39</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-1.4</v>
+        <v>-1.38</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>5.02</v>
+        <v>5.39</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>11.71</v>
+        <v>11.86</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-1.83</v>
+        <v>-1.82</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -711,40 +711,40 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1521.45</v>
+        <v>102.41</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>2.5</v>
+        <v>0.49</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2.56</v>
+        <v>-1.73</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.06</v>
+        <v>-2.45</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-14.32</v>
+        <v>-4.6</v>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -769,23 +769,23 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>102.41</v>
+        <v>33.39</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.49</v>
+        <v>-0.3</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-1.73</v>
+        <v>-0.72</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-2.45</v>
+        <v>-0.65</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>3.78</v>
+        <v>1.78</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-4.6</v>
+        <v>-3.58</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,40 +827,40 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>32498.4</v>
+        <v>604.9</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.58</v>
+        <v>1.31</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-0.53</v>
+        <v>0.84</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-1.05</v>
+        <v>0.63</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-2.78</v>
+        <v>-4.2</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M7" s="1" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,23 +885,23 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>58521.4</v>
+        <v>279.46</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.39</v>
+        <v>0.76</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-4.35</v>
+        <v>-4.64</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>11705</v>
+        <v>130.15</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-0.28</v>
+        <v>0.39</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -967,11 +967,11 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-7.69</v>
+        <v>-7.76</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,35 +1001,35 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>27099.75</v>
+        <v>32.53</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.89</v>
+        <v>0.37</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.49</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.76</v>
+        <v>0.28</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-5.1</v>
+        <v>-2.55</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,31 +1059,31 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>26903.35</v>
+        <v>96.53</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.27</v>
+        <v>0.77</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.32</v>
+        <v>-0.54</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.65</v>
+        <v>-1.88</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-0.59</v>
+        <v>-0.86</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-5.05</v>
+        <v>-3.47</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>39277</v>
+        <v>39.29</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.09</v>
+        <v>-0.25</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.14</v>
+        <v>-0.3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-3.46</v>
+        <v>-3.58</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-1</v>
+        <v>-1.24</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-6.93</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>9377.35</v>
+        <v>52.31</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.55</v>
+        <v>0.54</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.5</v>
+        <v>-0.91</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-1.84</v>
+        <v>-1.94</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-1.31</v>
+        <v>-3.66</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-3.65</v>
+        <v>-16.14</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
@@ -1213,19 +1213,19 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>48748.7</v>
+        <v>100</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-1.14</v>
+        <v>0.19</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-1.09</v>
+        <v>-0.57</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-2.37</v>
+        <v>-2.9</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-3.79</v>
+        <v>-4.47</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-16.52</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
@@ -1276,14 +1276,14 @@
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1291,23 +1291,23 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>9832.1</v>
+        <v>12.5</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.6</v>
+        <v>-0.48</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-3.1</v>
+        <v>-4.89</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-4.44</v>
+        <v>-5.48</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-7.87</v>
+        <v>-11.7</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,23 +1349,23 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12436.95</v>
+        <v>93.58</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-1.99</v>
+        <v>0.36</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-1.93</v>
+        <v>-0.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-4.94</v>
+        <v>-5.24</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-5.37</v>
+        <v>-6.89</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-11.6</v>
+        <v>-14.9</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1387,19 +1387,19 @@
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1411,19 +1411,19 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>8381.75</v>
+        <v>10.31</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.83</v>
+        <v>0.19</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.78</v>
+        <v>0.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-4.97</v>
+        <v>-3.19</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-7.32</v>
+        <v>-7.98</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-15.27</v>
+        <v>-10.04</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="M17" s="1" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1469,27 +1469,27 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>9938.549999999999</v>
+        <v>32.44</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.28</v>
+        <v>1.79</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.33</v>
+        <v>4.56</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-2.98</v>
+        <v>2.02</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-8.01</v>
+        <v>-9.4</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-9.949999999999999</v>
+        <v>-25.38</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
@@ -1498,80 +1498,22 @@
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>29226.6</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:H19">
+  <conditionalFormatting sqref="F2:H18">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-10"/>
@@ -1583,7 +1525,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
+  <conditionalFormatting sqref="I2:I18">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>"Up"</formula>
     </cfRule>
@@ -1591,7 +1533,7 @@
       <formula>"Down"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
+  <conditionalFormatting sqref="J2:J18">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-15"/>
@@ -1603,7 +1545,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
+  <conditionalFormatting sqref="K2:K18">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1611,7 +1553,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
+  <conditionalFormatting sqref="L2:L18">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1619,7 +1561,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M19">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1627,7 +1569,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N19">
+  <conditionalFormatting sqref="N2:N18">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1645,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1656,17 +1598,16 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1707,62 +1648,57 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fin Services</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Consumption</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>PSU Bank</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Defence</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Realty</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fin Services</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>PSE</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MNC</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>PSU Bank</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Defence</t>
         </is>
       </c>
     </row>
@@ -1773,57 +1709,54 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1834,16 +1767,16 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2</v>
@@ -1852,40 +1785,37 @@
         <v>14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1895,58 +1825,55 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1956,58 +1883,55 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>13</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2017,13 +1941,13 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>13</v>
@@ -2035,40 +1959,37 @@
         <v>11</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2078,16 +1999,16 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2</v>
@@ -2096,40 +2017,37 @@
         <v>12</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2139,7 +2057,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>12</v>
@@ -2157,40 +2075,37 @@
         <v>9</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2200,7 +2115,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>10</v>
@@ -2209,49 +2124,46 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>11</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2261,58 +2173,55 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>11</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2322,7 +2231,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>8</v>
@@ -2331,49 +2240,46 @@
         <v>7</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2383,58 +2289,55 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -2444,58 +2347,55 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>15</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2505,58 +2405,55 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2566,58 +2463,55 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2627,58 +2521,55 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -2688,58 +2579,55 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>12</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2749,58 +2637,55 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>12</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2810,7 +2695,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>9</v>
@@ -2819,49 +2704,46 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>11</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2871,58 +2753,55 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2932,7 +2811,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>13</v>
@@ -2941,49 +2820,46 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S21" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2993,58 +2869,55 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>16</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3054,13 +2927,13 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>15</v>
@@ -3069,43 +2942,40 @@
         <v>13</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3115,58 +2985,55 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>12</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -3176,7 +3043,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>13</v>
@@ -3185,49 +3052,46 @@
         <v>10</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -3237,7 +3101,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>13</v>
@@ -3246,49 +3110,46 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>11</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3298,58 +3159,55 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -3359,57 +3217,54 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S28" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3429,49 +3284,46 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R29" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3493,46 +3345,43 @@
         <v>13</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L30" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -3542,7 +3391,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>16</v>
@@ -3551,49 +3400,46 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -3615,46 +3461,43 @@
         <v>14</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3664,7 +3507,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>16</v>
@@ -3682,40 +3525,37 @@
         <v>3</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3743,40 +3583,37 @@
         <v>2</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -3792,52 +3629,49 @@
         <v>16</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3850,7 +3684,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>15</v>
@@ -3865,40 +3699,37 @@
         <v>1</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S36" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3911,10 +3742,10 @@
         <v>15</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>12</v>
@@ -3923,43 +3754,40 @@
         <v>4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S37" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -3969,10 +3797,10 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>13</v>
@@ -3987,40 +3815,37 @@
         <v>1</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -4030,10 +3855,10 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>13</v>
@@ -4048,40 +3873,37 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -4091,58 +3913,55 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -4152,10 +3971,10 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>13</v>
@@ -4170,40 +3989,37 @@
         <v>2</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -4213,16 +4029,16 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>4</v>
@@ -4231,40 +4047,37 @@
         <v>3</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -4274,16 +4087,16 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>2</v>
@@ -4292,40 +4105,37 @@
         <v>5</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -4335,16 +4145,16 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>13</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>2</v>
@@ -4353,40 +4163,37 @@
         <v>5</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -4396,16 +4203,16 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>13</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>1</v>
@@ -4414,40 +4221,37 @@
         <v>5</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -4457,10 +4261,10 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>13</v>
@@ -4475,40 +4279,37 @@
         <v>4</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -4518,10 +4319,10 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>13</v>
@@ -4536,40 +4337,37 @@
         <v>3</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S47" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -4579,58 +4377,55 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>13</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>2</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S48" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -4640,58 +4435,55 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>13</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S49" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -4701,16 +4493,16 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>13</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>4</v>
@@ -4719,40 +4511,37 @@
         <v>3</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="S50" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -4762,10 +4551,10 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>14</v>
@@ -4774,46 +4563,43 @@
         <v>12</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>5</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S51" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -4823,10 +4609,10 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>12</v>
@@ -4835,46 +4621,43 @@
         <v>14</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="S52" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -4884,10 +4667,10 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>12</v>
@@ -4902,40 +4685,37 @@
         <v>9</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S53" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -4945,10 +4725,10 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>14</v>
@@ -4963,40 +4743,37 @@
         <v>5</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S54" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -5006,10 +4783,10 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>14</v>
@@ -5018,46 +4795,43 @@
         <v>12</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="S55" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -5067,10 +4841,10 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>14</v>
@@ -5085,40 +4859,37 @@
         <v>3</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S56" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -5128,10 +4899,10 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>14</v>
@@ -5140,46 +4911,43 @@
         <v>12</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="S57" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -5189,10 +4957,10 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>15</v>
@@ -5207,40 +4975,37 @@
         <v>3</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S58" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -5250,10 +5015,10 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>15</v>
@@ -5262,46 +5027,43 @@
         <v>12</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S59" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -5311,58 +5073,55 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S60" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -5372,58 +5131,55 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S61" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -5433,58 +5189,55 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S62" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -5494,58 +5247,55 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S63" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -5555,13 +5305,13 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>12</v>
@@ -5573,40 +5323,37 @@
         <v>3</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="S64" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -5616,16 +5363,16 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>11</v>
@@ -5634,40 +5381,37 @@
         <v>2</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="S65" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -5677,16 +5421,16 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>11</v>
@@ -5695,49 +5439,46 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="S66" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:S66">
+  <conditionalFormatting sqref="B2:R66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="1"/>
         <cfvo type="num" val="9"/>
-        <cfvo type="num" val="18"/>
+        <cfvo type="num" val="17"/>
         <color rgb="0063BE7B"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00F8696B"/>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -435,10 +435,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -761,7 +761,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -769,40 +769,40 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>102.41</v>
+        <v>29.05</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.49</v>
+        <v>1.72</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-1.73</v>
+        <v>1.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-2.45</v>
+        <v>1.65</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-4.6</v>
+        <v>-1.8</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M6" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,23 +827,23 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>29.05</v>
+        <v>604.9</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1.59</v>
+        <v>0.84</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1.65</v>
+        <v>0.63</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-1.8</v>
+        <v>-4.2</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,40 +885,40 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>33.39</v>
+        <v>279.46</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.3</v>
+        <v>1.21</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.72</v>
+        <v>0.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.78</v>
+        <v>0.76</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-3.58</v>
+        <v>-4.64</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,57 +943,57 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>604.9</v>
+        <v>54.19</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.31</v>
+        <v>-0.13</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.84</v>
+        <v>-2.66</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.63</v>
+        <v>-3.22</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.71</v>
+        <v/>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,23 +1001,23 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>279.46</v>
+        <v>13.44</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.21</v>
+        <v>-0.37</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.8</v>
+        <v>-0.98</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.75</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.76</v>
+        <v>6.39</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-4.64</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,23 +1059,23 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>130.15</v>
+        <v>79.33</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-0.24</v>
+        <v>-2.41</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.36</v>
+        <v>1.67</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.51</v>
+        <v>4.39</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-7.76</v>
+        <v>-16.48</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M11" s="1" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1121,27 +1121,27 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>161.76</v>
+        <v>31.47</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.7</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.21</v>
+        <v>0.27</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-1.25</v>
+        <v>0.3</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.32</v>
+        <v>3.91</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-2.83</v>
+        <v>-2.4</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>32.53</v>
+        <v>102.41</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-1.49</v>
+        <v>-1.73</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.28</v>
+        <v>-2.45</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>3.78</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-2.55</v>
+        <v>-4.6</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>96.53</v>
+        <v>33.39</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.3</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-0.54</v>
+        <v>-0.72</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-1.88</v>
+        <v>-0.65</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-0.86</v>
+        <v>1.78</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-3.47</v>
+        <v>-3.58</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1291,45 +1291,45 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>39.29</v>
+        <v>130.15</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.25</v>
+        <v>0.39</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.24</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-3.58</v>
+        <v>0.36</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-1.24</v>
+        <v>0.51</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0</v>
+        <v>-7.76</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,23 +1349,23 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>11.44</v>
+        <v>161.76</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.88</v>
+        <v>-0.13</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>1.02</v>
+        <v>-0.21</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-0.64</v>
+        <v>-1.25</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-3.19</v>
+        <v>0.32</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-8.57</v>
+        <v>-2.83</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1407,23 +1407,23 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>52.31</v>
+        <v>32.53</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.91</v>
+        <v>-1.49</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-1.94</v>
+        <v>0.28</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-3.66</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-16.14</v>
+        <v>-2.55</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
@@ -1440,24 +1440,24 @@
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1465,57 +1465,57 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>100</v>
+        <v>85.27</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.19</v>
+        <v>0.71</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>-0.57</v>
+        <v>1.56</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-2.9</v>
+        <v>2.87</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-4.47</v>
+        <v>-0.76</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-8.460000000000001</v>
+        <v>-13.44</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1523,23 +1523,23 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>12.5</v>
+        <v>96.53</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-0.48</v>
+        <v>0.77</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>-1.91</v>
+        <v>-0.54</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-4.89</v>
+        <v>-1.88</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-5.48</v>
+        <v>-0.86</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-11.7</v>
+        <v>-3.47</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1581,40 +1581,40 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>93.58</v>
+        <v>31.52</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.36</v>
+        <v>0.99</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>-0.76</v>
+        <v>0.85</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-5.24</v>
+        <v>1.54</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-6.89</v>
+        <v>-1.09</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J20" s="1" t="n">
-        <v>-14.9</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M20" s="1" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1639,23 +1639,23 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>10.31</v>
+        <v>39.29</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-3.19</v>
+        <v>-3.58</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-7.98</v>
+        <v>-1.24</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -1663,11 +1663,11 @@
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-10.04</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1697,55 +1697,403 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>-8.57</v>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>-16.14</v>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>-4.89</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>-5.48</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>PSU Bank</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D26" s="1" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M26" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>PSE</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>-7.98</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>32.44</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E28" s="1" t="n">
         <v>1.79</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F28" s="1" t="n">
         <v>4.56</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G28" s="1" t="n">
         <v>2.02</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H28" s="1" t="n">
         <v>-9.4</v>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J28" s="1" t="n">
         <v>-25.38</v>
       </c>
-      <c r="K22" s="1" t="inlineStr">
+      <c r="K28" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="L28" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="M28" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="N28" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:H22">
+  <conditionalFormatting sqref="F2:H28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-10"/>
@@ -1757,7 +2105,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I22">
+  <conditionalFormatting sqref="I2:I28">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>"Up"</formula>
     </cfRule>
@@ -1765,7 +2113,7 @@
       <formula>"Down"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J22">
+  <conditionalFormatting sqref="J2:J28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-15"/>
@@ -1777,7 +2125,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K22">
+  <conditionalFormatting sqref="K2:K28">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1785,7 +2133,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L22">
+  <conditionalFormatting sqref="L2:L28">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1793,7 +2141,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M22">
+  <conditionalFormatting sqref="M2:M28">
     <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1801,7 +2149,7 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N22">
+  <conditionalFormatting sqref="N2:N28">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1819,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:AB66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1838,12 +2186,18 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1924,37 +2278,67 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MNC</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Defence</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>MNC</t>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Capital Market</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
     </row>
@@ -1965,22 +2349,22 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>2</v>
@@ -1989,43 +2373,61 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="M2" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="N2" s="1" t="n">
+      <c r="T2" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U2" s="1" t="n">
+      <c r="AA2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB2" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V2" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2035,22 +2437,22 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2059,43 +2461,61 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="M3" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="N3" s="1" t="n">
+      <c r="W3" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2105,22 +2525,22 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2</v>
@@ -2129,43 +2549,61 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="R4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="S4" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2175,22 +2613,22 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
@@ -2199,43 +2637,61 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M5" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="N5" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>4</v>
-      </c>
       <c r="Q5" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="R5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="R5" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="S5" s="1" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2245,22 +2701,22 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="G6" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
@@ -2269,43 +2725,61 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S6" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" s="1" t="n">
+      <c r="AA6" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB6" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -2315,67 +2789,85 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="E7" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S7" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" s="1" t="n">
+      <c r="AA7" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2385,22 +2877,22 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="E8" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="G8" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -2409,43 +2901,61 @@
         <v>4</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="N8" s="1" t="n">
+      <c r="V8" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB8" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="O8" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2455,67 +2965,85 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="H9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>4</v>
-      </c>
       <c r="J9" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P9" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="T9" s="1" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="U9" s="1" t="n">
         <v>9</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2525,67 +3053,85 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="E10" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="H10" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="N10" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="R10" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S10" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T10" s="1" t="n">
+      <c r="W10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="U10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>6</v>
+      <c r="Z10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2595,67 +3141,85 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="E11" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="H11" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="n">
+      <c r="S11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="T11" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R11" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T11" s="1" t="n">
+      <c r="W11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="AA11" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB11" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2665,67 +3229,85 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="M12" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" s="1" t="n">
+      <c r="AA12" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB12" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -2735,67 +3317,85 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="J13" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" s="1" t="n">
+      <c r="AA13" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB13" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2805,67 +3405,85 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="E14" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F14" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="G14" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z14" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="M14" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="N14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>3</v>
+      <c r="AA14" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -2875,67 +3493,85 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB15" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U15" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -2945,67 +3581,85 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="H16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="J16" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="1" t="n">
+      <c r="W16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="R16" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>8</v>
+      <c r="AA16" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3015,67 +3669,85 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="H17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="M17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O17" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="R17" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="T17" s="1" t="n">
+      <c r="V17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="U17" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V17" s="1" t="n">
+      <c r="X17" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" s="1" t="n">
         <v>4</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -3085,67 +3757,85 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="I18" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N18" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V18" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O18" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="R18" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="T18" s="1" t="n">
+      <c r="W18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="U18" s="1" t="n">
+      <c r="X18" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V18" s="1" t="n">
+      <c r="Z18" s="1" t="n">
         <v>4</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -3155,67 +3845,85 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="E19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>4</v>
-      </c>
       <c r="I19" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="R19" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="N19" s="1" t="n">
+      <c r="S19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O19" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="1" t="n">
+      <c r="W19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S19" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="T19" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>7</v>
+      <c r="AA19" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB19" s="1" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -3225,22 +3933,22 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>4</v>
@@ -3255,37 +3963,55 @@
         <v>5</v>
       </c>
       <c r="L20" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y20" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="Z20" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB20" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S20" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V20" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -3295,66 +4021,84 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="I21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R21" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="S21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" s="1" t="n">
+      <c r="W21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="S21" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="T21" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" s="1" t="n">
+      <c r="Y21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="V21" s="1" t="n">
+      <c r="Z21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB21" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3365,28 +4109,28 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F22" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="1" t="n">
+      <c r="G22" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>3</v>
@@ -3395,37 +4139,55 @@
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M22" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" s="1" t="n">
+      <c r="O22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="P22" s="1" t="n">
+      <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="T22" s="1" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <v>6</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB22" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3435,66 +4197,84 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="I23" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="R23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="S23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="W23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z23" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="O23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V23" s="1" t="n">
+      <c r="AA23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB23" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3505,66 +4285,84 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="J24" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M24" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" s="1" t="n">
+      <c r="S24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="O24" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="P24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S24" s="1" t="n">
+      <c r="V24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z24" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="T24" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U24" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="V24" s="1" t="n">
+      <c r="AA24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3575,67 +4373,85 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C25" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D25" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H25" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="I25" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N25" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="R25" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="O25" s="1" t="n">
+      <c r="S25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="P25" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" s="1" t="n">
+      <c r="Y25" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="U25" s="1" t="n">
+      <c r="Z25" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="V25" s="1" t="n">
-        <v>6</v>
+      <c r="AA25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB25" s="1" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -3645,67 +4461,85 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C26" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="D26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>10</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>6</v>
+      <c r="Z26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB26" s="1" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -3715,28 +4549,28 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="G27" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>1</v>
@@ -3745,37 +4579,55 @@
         <v>6</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="M27" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>7</v>
+      <c r="AA27" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB27" s="1" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -3785,22 +4637,22 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="G28" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>2</v>
@@ -3812,40 +4664,58 @@
         <v>3</v>
       </c>
       <c r="K28" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB28" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -3855,22 +4725,22 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>5</v>
@@ -3882,40 +4752,58 @@
         <v>4</v>
       </c>
       <c r="K29" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y29" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" s="1" t="n">
+      <c r="Z29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB29" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -3925,22 +4813,22 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>5</v>
@@ -3952,40 +4840,58 @@
         <v>3</v>
       </c>
       <c r="K30" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V30" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB30" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="L30" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N30" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O30" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -3995,22 +4901,22 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E31" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>4</v>
@@ -4022,40 +4928,58 @@
         <v>3</v>
       </c>
       <c r="K31" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB31" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N31" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="O31" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="P31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R31" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -4065,22 +4989,22 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C32" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>4</v>
@@ -4092,41 +5016,59 @@
         <v>3</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="O32" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="P32" s="1" t="n">
+      <c r="S32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R32" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="T32" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U32" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="U32" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="V32" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="W32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB32" s="1" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -4135,22 +5077,22 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C33" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>4</v>
@@ -4162,41 +5104,59 @@
         <v>3</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L33" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="M33" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="N33" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O33" s="1" t="n">
+      <c r="P33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R33" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="P33" s="1" t="n">
+      <c r="S33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="T33" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U33" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="U33" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="V33" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="W33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB33" s="1" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -4208,19 +5168,19 @@
         <v>11</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E34" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>4</v>
@@ -4235,37 +5195,55 @@
         <v>13</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" s="1" t="n">
+      <c r="T34" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="V34" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X34" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S34" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T34" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V34" s="1" t="n">
-        <v>9</v>
+      <c r="Y34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB34" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -4278,19 +5256,19 @@
         <v>7</v>
       </c>
       <c r="C35" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>4</v>
@@ -4302,40 +5280,58 @@
         <v>1</v>
       </c>
       <c r="K35" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R35" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="L35" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M35" s="1" t="n">
+      <c r="S35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="V35" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y35" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="N35" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O35" s="1" t="n">
+      <c r="Z35" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB35" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="P35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S35" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T35" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V35" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -4348,19 +5344,19 @@
         <v>13</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E36" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G36" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>4</v>
@@ -4372,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L36" s="1" t="n">
         <v>11</v>
@@ -4381,31 +5377,49 @@
         <v>12</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R36" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" s="1" t="n">
+      <c r="T36" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U36" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V36" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X36" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="S36" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="U36" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V36" s="1" t="n">
-        <v>8</v>
+      <c r="Y36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA36" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB36" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="37">
@@ -4415,22 +5429,22 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F37" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="G37" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4</v>
@@ -4442,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>11</v>
@@ -4451,31 +5465,49 @@
         <v>12</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R37" s="1" t="n">
+      <c r="T37" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U37" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V37" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X37" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y37" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="S37" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T37" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="U37" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V37" s="1" t="n">
-        <v>6</v>
+      <c r="Z37" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB37" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -4485,22 +5517,22 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F38" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="G38" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F38" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
@@ -4512,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>11</v>
@@ -4521,31 +5553,49 @@
         <v>12</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P38" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R38" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R38" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="T38" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U38" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="U38" s="1" t="n">
+      <c r="V38" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V38" s="1" t="n">
-        <v>7</v>
+      <c r="W38" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X38" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y38" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z38" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA38" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB38" s="1" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -4555,22 +5605,22 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="G39" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F39" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
@@ -4582,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>11</v>
@@ -4591,31 +5641,49 @@
         <v>12</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R39" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q39" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R39" s="1" t="n">
+      <c r="T39" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W39" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X39" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y39" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="S39" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T39" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="U39" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V39" s="1" t="n">
-        <v>7</v>
+      <c r="Z39" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA39" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB39" s="1" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -4625,19 +5693,19 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F40" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>13</v>
@@ -4652,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>11</v>
@@ -4661,31 +5729,49 @@
         <v>12</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q40" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R40" s="1" t="n">
+      <c r="T40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U40" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V40" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X40" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z40" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA40" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB40" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="U40" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V40" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -4695,19 +5781,19 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C41" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F41" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>12</v>
@@ -4722,7 +5808,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>11</v>
@@ -4731,31 +5817,49 @@
         <v>13</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R41" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R41" s="1" t="n">
+      <c r="T41" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U41" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X41" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z41" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB41" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V41" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -4765,19 +5869,19 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F42" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F42" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>12</v>
@@ -4792,7 +5896,7 @@
         <v>3</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
@@ -4801,31 +5905,49 @@
         <v>13</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P42" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R42" s="1" t="n">
+      <c r="T42" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U42" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V42" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W42" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X42" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y42" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z42" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA42" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB42" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T42" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="U42" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V42" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -4835,19 +5957,19 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="F43" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>13</v>
@@ -4862,7 +5984,7 @@
         <v>5</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
@@ -4871,31 +5993,49 @@
         <v>12</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R43" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S43" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R43" s="1" t="n">
+      <c r="T43" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U43" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V43" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X43" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y43" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z43" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB43" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U43" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V43" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -4905,19 +6045,19 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="D44" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="E44" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F44" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>12</v>
@@ -4932,7 +6072,7 @@
         <v>5</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
@@ -4941,31 +6081,49 @@
         <v>13</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P44" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R44" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R44" s="1" t="n">
+      <c r="T44" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U44" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V44" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W44" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X44" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y44" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z44" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA44" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB44" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="U44" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V44" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -4975,19 +6133,19 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C45" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="E45" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>12</v>
@@ -5002,7 +6160,7 @@
         <v>5</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
@@ -5011,31 +6169,49 @@
         <v>13</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P45" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R45" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S45" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="R45" s="1" t="n">
+      <c r="T45" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U45" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X45" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y45" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z45" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA45" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB45" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U45" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V45" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -5045,19 +6221,19 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>11</v>
@@ -5072,7 +6248,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>12</v>
@@ -5081,31 +6257,49 @@
         <v>13</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P46" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R46" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S46" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="R46" s="1" t="n">
+      <c r="T46" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U46" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W46" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X46" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y46" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z46" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA46" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB46" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V46" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -5115,19 +6309,19 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C47" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="F47" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>12</v>
@@ -5142,7 +6336,7 @@
         <v>3</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>11</v>
@@ -5151,31 +6345,49 @@
         <v>13</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P47" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R47" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="R47" s="1" t="n">
+      <c r="T47" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U47" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V47" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W47" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X47" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y47" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z47" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA47" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB47" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S47" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T47" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="U47" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V47" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -5185,19 +6397,19 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C48" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="E48" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>11</v>
@@ -5212,7 +6424,7 @@
         <v>2</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L48" s="1" t="n">
         <v>12</v>
@@ -5221,31 +6433,49 @@
         <v>13</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R48" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R48" s="1" t="n">
+      <c r="T48" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U48" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V48" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W48" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X48" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y48" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z48" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA48" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB48" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="S48" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T48" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="U48" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V48" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -5255,19 +6485,19 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C49" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E49" s="1" t="n">
+      <c r="F49" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>11</v>
@@ -5282,7 +6512,7 @@
         <v>2</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>12</v>
@@ -5291,31 +6521,49 @@
         <v>13</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R49" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S49" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="R49" s="1" t="n">
+      <c r="T49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U49" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V49" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W49" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X49" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y49" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z49" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA49" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB49" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S49" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T49" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U49" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V49" s="1" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -5325,19 +6573,19 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C50" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E50" s="1" t="n">
+      <c r="F50" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>11</v>
@@ -5352,7 +6600,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L50" s="1" t="n">
         <v>12</v>
@@ -5361,31 +6609,49 @@
         <v>13</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="P50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R50" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S50" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" s="1" t="n">
+      <c r="T50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U50" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y50" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z50" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA50" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB50" s="1" t="n">
         <v>15</v>
-      </c>
-      <c r="S50" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T50" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="V50" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -5395,19 +6661,19 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F51" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F51" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>14</v>
@@ -5431,31 +6697,49 @@
         <v>13</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P51" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S51" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R51" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="S51" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="T51" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U51" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="U51" s="1" t="n">
+      <c r="V51" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V51" s="1" t="n">
-        <v>8</v>
+      <c r="W51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X51" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y51" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z51" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA51" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB51" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -5465,22 +6749,22 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>3</v>
@@ -5501,31 +6785,49 @@
         <v>13</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R52" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="S52" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="T52" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U52" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U52" s="1" t="n">
+      <c r="V52" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="V52" s="1" t="n">
-        <v>7</v>
+      <c r="W52" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X52" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y52" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z52" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA52" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB52" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -5535,22 +6837,22 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E53" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F53" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>3</v>
@@ -5559,43 +6861,61 @@
         <v>4</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M53" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="N53" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O53" s="1" t="n">
+      <c r="R53" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S53" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U53" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V53" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="W53" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="P53" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="S53" s="1" t="n">
+      <c r="X53" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y53" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z53" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA53" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB53" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="T53" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U53" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V53" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -5605,22 +6925,22 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F54" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D54" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" s="1" t="n">
+      <c r="G54" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F54" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>3</v>
@@ -5635,37 +6955,55 @@
         <v>8</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R54" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S54" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="S54" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="T54" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U54" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="U54" s="1" t="n">
+      <c r="V54" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="V54" s="1" t="n">
-        <v>6</v>
+      <c r="W54" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X54" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y54" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z54" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA54" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB54" s="1" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -5675,22 +7013,22 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F55" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="E55" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="F55" s="1" t="n">
+      <c r="G55" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>7</v>
@@ -5711,31 +7049,49 @@
         <v>12</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>3</v>
       </c>
       <c r="P55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R55" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" s="1" t="n">
+      <c r="T55" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="U55" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="V55" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W55" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="S55" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T55" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="U55" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="V55" s="1" t="n">
-        <v>8</v>
+      <c r="X55" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y55" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z55" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA55" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB55" s="1" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -5745,22 +7101,22 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F56" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D56" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E56" s="1" t="n">
+      <c r="G56" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F56" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>6</v>
@@ -5775,37 +7131,55 @@
         <v>9</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>11</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R56" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S56" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" s="1" t="n">
+      <c r="T56" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="S56" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T56" s="1" t="n">
+      <c r="U56" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="U56" s="1" t="n">
+      <c r="V56" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V56" s="1" t="n">
-        <v>7</v>
+      <c r="W56" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X56" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y56" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z56" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA56" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB56" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -5815,22 +7189,22 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D57" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E57" s="1" t="n">
+      <c r="G57" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="F57" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>7</v>
@@ -5845,37 +7219,55 @@
         <v>13</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O57" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R57" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" s="1" t="n">
+      <c r="T57" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="S57" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T57" s="1" t="n">
+      <c r="U57" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="U57" s="1" t="n">
+      <c r="V57" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V57" s="1" t="n">
-        <v>6</v>
+      <c r="W57" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X57" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y57" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z57" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA57" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB57" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -5885,22 +7277,22 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D58" s="1" t="n">
+      <c r="F58" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="F58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>6</v>
@@ -5915,37 +7307,55 @@
         <v>13</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>11</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O58" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R58" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S58" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" s="1" t="n">
+      <c r="T58" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="S58" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T58" s="1" t="n">
+      <c r="U58" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="U58" s="1" t="n">
+      <c r="V58" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V58" s="1" t="n">
-        <v>7</v>
+      <c r="W58" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X58" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z58" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB58" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -5955,22 +7365,22 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D59" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="F59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>7</v>
@@ -5985,37 +7395,55 @@
         <v>13</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O59" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R59" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" s="1" t="n">
+      <c r="T59" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="S59" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" s="1" t="n">
+      <c r="U59" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="U59" s="1" t="n">
+      <c r="V59" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V59" s="1" t="n">
-        <v>6</v>
+      <c r="W59" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X59" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z59" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA59" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB59" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -6025,22 +7453,22 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C60" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C60" s="1" t="n">
-        <v>19</v>
-      </c>
       <c r="D60" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F60" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="E60" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="G60" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>6</v>
@@ -6052,40 +7480,58 @@
         <v>3</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O60" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R60" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" s="1" t="n">
+      <c r="T60" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="S60" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T60" s="1" t="n">
+      <c r="U60" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="U60" s="1" t="n">
+      <c r="V60" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V60" s="1" t="n">
-        <v>7</v>
+      <c r="W60" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="X60" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y60" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z60" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA60" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB60" s="1" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -6095,19 +7541,19 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="F61" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>12</v>
@@ -6122,40 +7568,58 @@
         <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L61" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="L61" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O61" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R61" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="S61" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="T61" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U61" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="U61" s="1" t="n">
+      <c r="V61" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V61" s="1" t="n">
-        <v>6</v>
+      <c r="W61" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X61" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y61" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z61" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA61" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB61" s="1" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="62">
@@ -6165,19 +7629,19 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
         <v>17</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>13</v>
@@ -6192,7 +7656,7 @@
         <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L62" s="1" t="n">
         <v>12</v>
@@ -6207,25 +7671,43 @@
         <v>4</v>
       </c>
       <c r="P62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R62" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" s="1" t="n">
+      <c r="T62" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="S62" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T62" s="1" t="n">
+      <c r="U62" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U62" s="1" t="n">
+      <c r="V62" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V62" s="1" t="n">
-        <v>5</v>
+      <c r="W62" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="X62" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y62" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z62" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA62" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB62" s="1" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="63">
@@ -6235,19 +7717,19 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>17</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>13</v>
@@ -6262,7 +7744,7 @@
         <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L63" s="1" t="n">
         <v>12</v>
@@ -6277,25 +7759,43 @@
         <v>4</v>
       </c>
       <c r="P63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R63" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S63" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" s="1" t="n">
+      <c r="T63" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="S63" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T63" s="1" t="n">
+      <c r="U63" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U63" s="1" t="n">
+      <c r="V63" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V63" s="1" t="n">
-        <v>6</v>
+      <c r="W63" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="X63" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y63" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z63" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA63" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB63" s="1" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="64">
@@ -6305,22 +7805,22 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F64" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>12</v>
@@ -6332,7 +7832,7 @@
         <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L64" s="1" t="n">
         <v>10</v>
@@ -6341,31 +7841,49 @@
         <v>9</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S64" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="1" t="n">
+      <c r="T64" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="S64" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T64" s="1" t="n">
+      <c r="U64" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U64" s="1" t="n">
+      <c r="V64" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="V64" s="1" t="n">
-        <v>6</v>
+      <c r="W64" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="X64" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y64" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z64" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA64" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB64" s="1" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -6375,19 +7893,19 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>15</v>
@@ -6402,7 +7920,7 @@
         <v>2</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L65" s="1" t="n">
         <v>9</v>
@@ -6417,25 +7935,43 @@
         <v>4</v>
       </c>
       <c r="P65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R65" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S65" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q65" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" s="1" t="n">
+      <c r="T65" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="S65" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T65" s="1" t="n">
+      <c r="U65" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U65" s="1" t="n">
+      <c r="V65" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="V65" s="1" t="n">
-        <v>6</v>
+      <c r="W65" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="X65" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y65" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z65" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA65" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB65" s="1" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="66">
@@ -6445,7 +7981,7 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>15</v>
@@ -6457,10 +7993,10 @@
         <v>6</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>12</v>
@@ -6472,7 +8008,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L66" s="1" t="n">
         <v>10</v>
@@ -6487,34 +8023,52 @@
         <v>4</v>
       </c>
       <c r="P66" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R66" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S66" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q66" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" s="1" t="n">
+      <c r="T66" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="S66" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T66" s="1" t="n">
+      <c r="U66" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="U66" s="1" t="n">
+      <c r="V66" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="V66" s="1" t="n">
-        <v>7</v>
+      <c r="W66" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="X66" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y66" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA66" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB66" s="1" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V66">
+  <conditionalFormatting sqref="B2:AB66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="1"/>
-        <cfvo type="num" val="11"/>
-        <cfvo type="num" val="21"/>
+        <cfvo type="num" val="14"/>
+        <cfvo type="num" val="27"/>
         <color rgb="0063BE7B"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00F8696B"/>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>91.59999999999999</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.11</v>
+        <v>0.09</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-1.98</v>
+        <v>-1.85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>11.36</v>
+        <v>12.31</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.18</v>
+        <v>14.81</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>26.39</v>
+        <v>26.77</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-1.38</v>
+        <v>1.44</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.48</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>5.39</v>
+        <v>5.81</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>11.86</v>
+        <v>13.94</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-1.82</v>
+        <v>-0.41</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>16.72</v>
+        <v>16.96</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-1.47</v>
+        <v>1.44</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.42</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>4.05</v>
+        <v>4.34</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>9.82</v>
+        <v>11.82</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-1.91</v>
+        <v>-0.51</v>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>30.34</v>
+        <v>30.52</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.59</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1.69</v>
+        <v>3.01</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>6.46</v>
+        <v>7.95</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -769,40 +769,40 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>29.05</v>
+        <v>102.62</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.72</v>
+        <v>0.21</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.59</v>
+        <v>-0.79</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.65</v>
+        <v>-3.35</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>3.3</v>
+        <v>4.49</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-1.8</v>
+        <v>-4.41</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,23 +827,23 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>604.9</v>
+        <v>28.44</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.31</v>
+        <v>-2.1</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.84</v>
+        <v>-0.87</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.63</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-4.2</v>
+        <v>-3.87</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M7" s="1" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,57 +885,57 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>279.46</v>
+        <v>54.48</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.21</v>
+        <v>0.54</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.8</v>
+        <v>-1.96</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.07</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.76</v>
+        <v/>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-4.64</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,27 +943,27 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>54.19</v>
+        <v>13.43</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>-2.66</v>
+        <v>-0.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-3.22</v>
+        <v>5.95</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v/>
+        <v>6.26</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
@@ -971,29 +971,29 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,23 +1001,23 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>13.44</v>
+        <v>79.09</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>-0.98</v>
+        <v>-2.25</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>6.75</v>
+        <v>0.17</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>6.39</v>
+        <v>4</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,33 +1025,33 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0</v>
+        <v>-16.74</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,23 +1059,23 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>79.33</v>
+        <v>31.51</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-2.41</v>
+        <v>1.03</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1.67</v>
+        <v>-0.51</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4.39</v>
+        <v>3.56</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-16.48</v>
+        <v>-2.28</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M11" s="1" t="inlineStr">
@@ -1102,14 +1102,14 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1121,27 +1121,27 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>31.47</v>
+        <v>33.46</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.7</v>
+        <v>0.21</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>0.3</v>
+        <v>-0.62</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>3.91</v>
+        <v>1.87</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-2.4</v>
+        <v>-3.39</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,40 +1175,40 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>102.41</v>
+        <v>130.7</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-1.73</v>
+        <v>0.85</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-2.45</v>
+        <v>0.55</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>3.78</v>
+        <v>0.97</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-4.6</v>
+        <v>-7.38</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,40 +1233,40 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>33.39</v>
+        <v>600.21</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.78</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-0.72</v>
+        <v>-0.05</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-0.65</v>
+        <v>-0.35</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.78</v>
+        <v>0.92</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-3.58</v>
+        <v>-4.95</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1295,27 +1295,27 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>130.15</v>
+        <v>162.88</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.93</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.36</v>
+        <v>-0.8</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.51</v>
+        <v>0.87</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-7.76</v>
+        <v>-2.16</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,31 +1349,31 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>161.76</v>
+        <v>279</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-0.21</v>
+        <v>0.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-1.25</v>
+        <v>0.91</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.32</v>
+        <v>0.55</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-2.83</v>
+        <v>-4.81</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1411,19 +1411,19 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>32.53</v>
+        <v>32.64</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-1.49</v>
+        <v>-1.11</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-2.55</v>
+        <v>-2.23</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -1465,23 +1465,23 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>85.27</v>
+        <v>85.28</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.71</v>
+        <v>0.01</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>1.56</v>
+        <v>0.16</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>2.87</v>
+        <v>3.81</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.76</v>
+        <v>-0.27</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-13.44</v>
+        <v>-13.43</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
@@ -1523,23 +1523,23 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>96.53</v>
+        <v>97.25</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>-0.54</v>
+        <v>0.72</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-1.88</v>
+        <v>-1.21</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.86</v>
+        <v>-0.34</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-3.47</v>
+        <v>-2.76</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1581,27 +1581,27 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>31.52</v>
+        <v>39.76</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>1.54</v>
+        <v>-3</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.09</v>
+        <v>-0.85</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J20" s="1" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1639,27 +1639,27 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>39.29</v>
+        <v>31.39</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.41</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.09</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-3.58</v>
+        <v>1.53</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.24</v>
+        <v>-1.99</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J21" s="1" t="n">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N21" s="1" t="inlineStr">
@@ -1701,19 +1701,19 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>11.44</v>
+        <v>11.51</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-3.19</v>
+        <v>-2.7</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-8.57</v>
+        <v>-8.02</v>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
@@ -1755,23 +1755,23 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>52.31</v>
+        <v>52.62</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>-0.91</v>
+        <v>0.31</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-1.94</v>
+        <v>-1.45</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-3.66</v>
+        <v>-3</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1779,11 +1779,11 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-16.14</v>
+        <v>-15.65</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -1813,23 +1813,23 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>100</v>
+        <v>101.03</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.19</v>
+        <v>1.03</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>-0.57</v>
+        <v>1.05</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-2.9</v>
+        <v>-1.93</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-4.47</v>
+        <v>-3.73</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -1837,16 +1837,16 @@
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-8.460000000000001</v>
+        <v>-7.53</v>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M24" s="1" t="inlineStr">
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>12.5</v>
+        <v>12.62</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-1.91</v>
+        <v>-0.43</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-4.89</v>
+        <v>-4.46</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-5.48</v>
+        <v>-4.22</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-11.7</v>
+        <v>-10.86</v>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
@@ -1929,40 +1929,40 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>93.58</v>
+        <v>96.16</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.36</v>
+        <v>2.76</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>-0.76</v>
+        <v>1.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-5.24</v>
+        <v>-2.23</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-6.89</v>
+        <v>-5.1</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-14.9</v>
+        <v>-12.56</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1987,23 +1987,23 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>10.31</v>
+        <v>10.38</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.19</v>
+        <v>0.68</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-3.19</v>
+        <v>-2.24</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-7.98</v>
+        <v>-7.8</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-10.04</v>
+        <v>-9.44</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M27" s="1" t="inlineStr">
@@ -2049,19 +2049,19 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>32.44</v>
+        <v>32.38</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.79</v>
+        <v>-0.18</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>4.56</v>
+        <v>0.72</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>2.02</v>
+        <v>5.59</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-9.4</v>
+        <v>-8.84</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-25.38</v>
+        <v>-25.52</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
@@ -2345,23 +2345,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C2" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>22</v>
@@ -2385,22 +2385,22 @@
         <v>18</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>21</v>
@@ -2409,50 +2409,50 @@
         <v>4</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z2" s="1" t="n">
+      <c r="AA2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB2" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2470,7 +2470,7 @@
         <v>16</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>14</v>
@@ -2479,68 +2479,68 @@
         <v>26</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S3" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V3" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y3" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z3" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2</v>
@@ -2549,25 +2549,25 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>23</v>
@@ -2576,31 +2576,31 @@
         <v>9</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V4" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>10</v>
@@ -2609,26 +2609,26 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
@@ -2637,13 +2637,13 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>18</v>
@@ -2652,10 +2652,10 @@
         <v>15</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
@@ -2670,25 +2670,25 @@
         <v>24</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>10</v>
@@ -2697,26 +2697,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
@@ -2737,13 +2737,13 @@
         <v>18</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
@@ -2761,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>4</v>
@@ -2776,7 +2776,7 @@
         <v>7</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -2795,16 +2795,16 @@
         <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
@@ -2822,22 +2822,22 @@
         <v>11</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O7" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S7" s="1" t="n">
         <v>6</v>
@@ -2849,13 +2849,13 @@
         <v>8</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>5</v>
@@ -2864,71 +2864,71 @@
         <v>7</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O8" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P8" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q8" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>24</v>
@@ -2940,13 +2940,13 @@
         <v>13</v>
       </c>
       <c r="W8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y8" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X8" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y8" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z8" s="1" t="n">
         <v>7</v>
@@ -2955,117 +2955,117 @@
         <v>23</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>20</v>
@@ -3074,7 +3074,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>19</v>
@@ -3095,10 +3095,10 @@
         <v>25</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R10" s="1" t="n">
         <v>10</v>
@@ -3107,53 +3107,53 @@
         <v>2</v>
       </c>
       <c r="T10" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X10" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>20</v>
@@ -3162,25 +3162,25 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>17</v>
@@ -3189,31 +3189,31 @@
         <v>22</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U11" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W11" s="1" t="n">
+      <c r="Y11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y11" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z11" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA11" s="1" t="n">
         <v>21</v>
@@ -3225,32 +3225,32 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>18</v>
@@ -3259,13 +3259,13 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>24</v>
@@ -3277,28 +3277,28 @@
         <v>22</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z12" s="1" t="n">
         <v>5</v>
@@ -3307,68 +3307,68 @@
         <v>21</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E13" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" s="1" t="n">
         <v>26</v>
@@ -3377,7 +3377,7 @@
         <v>7</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>4</v>
@@ -3395,62 +3395,62 @@
         <v>21</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>3</v>
@@ -3459,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1" t="n">
         <v>7</v>
@@ -3471,7 +3471,7 @@
         <v>4</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>6</v>
@@ -3483,47 +3483,47 @@
         <v>21</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>19</v>
@@ -3532,43 +3532,43 @@
         <v>17</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="1" t="n">
         <v>9</v>
@@ -3577,7 +3577,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -3587,10 +3587,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>18</v>
@@ -3599,19 +3599,19 @@
         <v>21</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>19</v>
@@ -3623,122 +3623,122 @@
         <v>23</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA16" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z17" s="1" t="n">
         <v>4</v>
@@ -3753,41 +3753,41 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
@@ -3802,7 +3802,7 @@
         <v>12</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>7</v>
@@ -3811,13 +3811,13 @@
         <v>1</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>3</v>
@@ -3826,7 +3826,7 @@
         <v>23</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z18" s="1" t="n">
         <v>4</v>
@@ -3841,190 +3841,190 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V19" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X19" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y19" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z19" s="1" t="n">
+      <c r="AA19" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB19" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA19" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB19" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>15</v>
@@ -4033,128 +4033,128 @@
         <v>25</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K21" s="1" t="n">
+      <c r="P21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N21" s="1" t="n">
+      <c r="Q21" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="R21" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y21" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W21" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y21" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z21" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J22" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N22" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>10</v>
@@ -4166,77 +4166,77 @@
         <v>26</v>
       </c>
       <c r="U22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V22" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y22" s="1" t="n">
+      <c r="AA22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB22" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="Z22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA22" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB22" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N23" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O23" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>8</v>
@@ -4257,83 +4257,83 @@
         <v>7</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I24" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>1</v>
@@ -4345,47 +4345,47 @@
         <v>7</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y24" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z24" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>22</v>
@@ -4394,43 +4394,43 @@
         <v>20</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J25" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U25" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S25" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T25" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U25" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V25" s="1" t="n">
         <v>15</v>
@@ -4439,25 +4439,25 @@
         <v>3</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -4467,37 +4467,37 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J26" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L26" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M26" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>24</v>
@@ -4506,13 +4506,13 @@
         <v>2</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" s="1" t="n">
         <v>25</v>
@@ -4521,19 +4521,19 @@
         <v>6</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X26" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y26" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z26" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA26" s="1" t="n">
         <v>23</v>
@@ -4545,86 +4545,86 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N27" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="W27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S27" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X27" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z27" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="AA27" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB27" s="1" t="n">
         <v>8</v>
@@ -4633,141 +4633,141 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="F28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G28" s="1" t="n">
+      <c r="H28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M28" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M28" s="1" t="n">
+      <c r="N28" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="1" t="n">
         <v>11</v>
@@ -4776,13 +4776,13 @@
         <v>7</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V29" s="1" t="n">
         <v>12</v>
@@ -4791,44 +4791,44 @@
         <v>8</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y29" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z29" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA29" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB29" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D30" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>5</v>
@@ -4837,110 +4837,110 @@
         <v>6</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R30" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V30" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA30" s="1" t="n">
         <v>26</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K31" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N31" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O31" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O31" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P31" s="1" t="n">
         <v>2</v>
@@ -4949,34 +4949,34 @@
         <v>7</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y31" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W31" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X31" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y31" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z31" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>10</v>
@@ -4985,11 +4985,11 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>26</v>
@@ -5004,13 +5004,13 @@
         <v>22</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>3</v>
@@ -5022,13 +5022,13 @@
         <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N32" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O32" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>2</v>
@@ -5037,53 +5037,53 @@
         <v>7</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W32" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W32" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X32" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB32" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z32" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA32" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB32" s="1" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>27</v>
@@ -5104,19 +5104,19 @@
         <v>3</v>
       </c>
       <c r="K33" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L33" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N33" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O33" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>2</v>
@@ -5131,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U33" s="1" t="n">
         <v>5</v>
@@ -5161,17 +5161,17 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>27</v>
@@ -5180,7 +5180,7 @@
         <v>22</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>4</v>
@@ -5189,37 +5189,37 @@
         <v>6</v>
       </c>
       <c r="J34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P34" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K34" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N34" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U34" s="1" t="n">
         <v>5</v>
@@ -5228,47 +5228,47 @@
         <v>8</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z34" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA34" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA34" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB34" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C35" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F35" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>4</v>
@@ -5277,155 +5277,155 @@
         <v>6</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L35" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N35" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N35" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O35" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U35" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z35" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB35" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V36" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W36" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W36" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X36" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z36" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB36" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -5435,16 +5435,16 @@
         <v>14</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4</v>
@@ -5456,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L37" s="1" t="n">
         <v>11</v>
@@ -5465,7 +5465,7 @@
         <v>12</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O37" s="1" t="n">
         <v>10</v>
@@ -5474,10 +5474,10 @@
         <v>3</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>2</v>
@@ -5486,7 +5486,7 @@
         <v>23</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37" s="1" t="n">
         <v>9</v>
@@ -5495,13 +5495,13 @@
         <v>15</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y37" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA37" s="1" t="n">
         <v>26</v>
@@ -5513,26 +5513,26 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
@@ -5544,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>12</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>10</v>
@@ -5562,16 +5562,16 @@
         <v>3</v>
       </c>
       <c r="Q38" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R38" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R38" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U38" s="1" t="n">
         <v>8</v>
@@ -5580,28 +5580,28 @@
         <v>9</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X38" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z38" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -5611,7 +5611,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>11</v>
@@ -5647,7 +5647,7 @@
         <v>10</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="1" t="n">
         <v>6</v>
@@ -5656,10 +5656,10 @@
         <v>7</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>8</v>
@@ -5677,7 +5677,7 @@
         <v>16</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA39" s="1" t="n">
         <v>25</v>
@@ -5689,26 +5689,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>11</v>
@@ -5729,28 +5729,28 @@
         <v>12</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U40" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U40" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V40" s="1" t="n">
         <v>9</v>
@@ -5759,16 +5759,16 @@
         <v>14</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z40" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB40" s="1" t="n">
         <v>15</v>
@@ -5777,11 +5777,11 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>25</v>
@@ -5790,13 +5790,13 @@
         <v>22</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
@@ -5805,43 +5805,43 @@
         <v>5</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R41" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>14</v>
@@ -5850,13 +5850,13 @@
         <v>21</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z41" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA41" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA41" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB41" s="1" t="n">
         <v>15</v>
@@ -5865,23 +5865,23 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>12</v>
@@ -5893,10 +5893,10 @@
         <v>5</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
@@ -5911,13 +5911,13 @@
         <v>9</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>1</v>
@@ -5926,7 +5926,7 @@
         <v>17</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V42" s="1" t="n">
         <v>10</v>
@@ -5935,16 +5935,16 @@
         <v>14</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y42" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA42" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA42" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB42" s="1" t="n">
         <v>15</v>
@@ -5953,7 +5953,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -5963,7 +5963,7 @@
         <v>25</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>27</v>
@@ -5972,16 +5972,16 @@
         <v>20</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="1" t="n">
         <v>19</v>
@@ -5990,16 +5990,16 @@
         <v>11</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>6</v>
@@ -6014,7 +6014,7 @@
         <v>17</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V43" s="1" t="n">
         <v>10</v>
@@ -6023,7 +6023,7 @@
         <v>14</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y43" s="1" t="n">
         <v>18</v>
@@ -6041,26 +6041,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>2</v>
@@ -6072,28 +6072,28 @@
         <v>5</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P44" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R44" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R44" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>17</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V44" s="1" t="n">
         <v>10</v>
@@ -6111,7 +6111,7 @@
         <v>14</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y44" s="1" t="n">
         <v>18</v>
@@ -6120,7 +6120,7 @@
         <v>23</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB44" s="1" t="n">
         <v>15</v>
@@ -6129,32 +6129,32 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45" s="1" t="n">
         <v>5</v>
@@ -6169,65 +6169,65 @@
         <v>13</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R45" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U45" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U45" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V45" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA45" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB45" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>25</v>
@@ -6236,22 +6236,22 @@
         <v>14</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M46" s="1" t="n">
         <v>13</v>
@@ -6260,28 +6260,28 @@
         <v>17</v>
       </c>
       <c r="O46" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P46" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R46" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P46" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R46" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U46" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V46" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V46" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>15</v>
@@ -6293,7 +6293,7 @@
         <v>19</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA46" s="1" t="n">
         <v>22</v>
@@ -6305,7 +6305,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
@@ -6315,31 +6315,31 @@
         <v>24</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J47" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K47" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>13</v>
@@ -6348,7 +6348,7 @@
         <v>17</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P47" s="1" t="n">
         <v>5</v>
@@ -6357,16 +6357,16 @@
         <v>6</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V47" s="1" t="n">
         <v>9</v>
@@ -6378,13 +6378,13 @@
         <v>26</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z47" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA47" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>16</v>
@@ -6393,41 +6393,41 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="E48" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G48" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I48" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L48" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>13</v>
@@ -6436,25 +6436,25 @@
         <v>17</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V48" s="1" t="n">
         <v>9</v>
@@ -6466,10 +6466,10 @@
         <v>26</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA48" s="1" t="n">
         <v>25</v>
@@ -6481,23 +6481,23 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>11</v>
@@ -6521,7 +6521,7 @@
         <v>13</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>8</v>
@@ -6539,16 +6539,16 @@
         <v>1</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U49" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V49" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V49" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W49" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X49" s="1" t="n">
         <v>26</v>
@@ -6557,19 +6557,19 @@
         <v>20</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -6579,7 +6579,7 @@
         <v>24</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>21</v>
@@ -6597,7 +6597,7 @@
         <v>5</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="n">
         <v>19</v>
@@ -6612,19 +6612,19 @@
         <v>16</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>17</v>
@@ -6645,7 +6645,7 @@
         <v>20</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>25</v>
@@ -6657,7 +6657,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -6667,43 +6667,43 @@
         <v>24</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H51" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I51" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K51" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L51" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>6</v>
@@ -6712,19 +6712,19 @@
         <v>8</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X51" s="1" t="n">
         <v>26</v>
@@ -6733,19 +6733,19 @@
         <v>20</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -6755,16 +6755,16 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E52" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F52" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>3</v>
@@ -6776,10 +6776,10 @@
         <v>5</v>
       </c>
       <c r="K52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>13</v>
@@ -6791,25 +6791,25 @@
         <v>10</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U52" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V52" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V52" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W52" s="1" t="n">
         <v>15</v>
@@ -6818,10 +6818,10 @@
         <v>26</v>
       </c>
       <c r="Y52" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z52" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z52" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>25</v>
@@ -6833,23 +6833,23 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D53" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F53" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>18</v>
@@ -6861,46 +6861,46 @@
         <v>4</v>
       </c>
       <c r="J53" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M53" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K53" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L53" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M53" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N53" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S53" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X53" s="1" t="n">
         <v>26</v>
@@ -6909,35 +6909,35 @@
         <v>21</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>18</v>
@@ -6949,31 +6949,31 @@
         <v>4</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N54" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>2</v>
@@ -6982,98 +6982,98 @@
         <v>20</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X54" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D55" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="E55" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U55" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V55" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V55" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>14</v>
@@ -7082,7 +7082,7 @@
         <v>26</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z55" s="1" t="n">
         <v>21</v>
@@ -7097,17 +7097,17 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>22</v>
@@ -7116,31 +7116,31 @@
         <v>19</v>
       </c>
       <c r="G56" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M56" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N56" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H56" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="1" t="n">
+      <c r="O56" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M56" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N56" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P56" s="1" t="n">
         <v>1</v>
@@ -7149,56 +7149,56 @@
         <v>5</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y56" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z56" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z56" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>19</v>
@@ -7207,7 +7207,7 @@
         <v>18</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>8</v>
@@ -7216,13 +7216,13 @@
         <v>3</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L57" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N57" s="1" t="n">
         <v>14</v>
@@ -7237,7 +7237,7 @@
         <v>5</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
@@ -7246,10 +7246,10 @@
         <v>12</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>15</v>
@@ -7258,13 +7258,13 @@
         <v>26</v>
       </c>
       <c r="Y57" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z57" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA57" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Z57" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA57" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB57" s="1" t="n">
         <v>16</v>
@@ -7273,7 +7273,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -7286,16 +7286,16 @@
         <v>23</v>
       </c>
       <c r="E58" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="F58" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>18</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>8</v>
@@ -7310,7 +7310,7 @@
         <v>17</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N58" s="1" t="n">
         <v>14</v>
@@ -7325,7 +7325,7 @@
         <v>5</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
@@ -7334,7 +7334,7 @@
         <v>12</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V58" s="1" t="n">
         <v>9</v>
@@ -7361,17 +7361,17 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D59" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>19</v>
@@ -7383,7 +7383,7 @@
         <v>18</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>8</v>
@@ -7398,7 +7398,7 @@
         <v>17</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>14</v>
@@ -7413,16 +7413,16 @@
         <v>5</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V59" s="1" t="n">
         <v>9</v>
@@ -7434,13 +7434,13 @@
         <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB59" s="1" t="n">
         <v>16</v>
@@ -7449,29 +7449,29 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>20</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>8</v>
@@ -7480,16 +7480,16 @@
         <v>3</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O60" s="1" t="n">
         <v>4</v>
@@ -7501,7 +7501,7 @@
         <v>5</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
@@ -7516,7 +7516,7 @@
         <v>9</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>26</v>
@@ -7525,41 +7525,41 @@
         <v>24</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E61" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F61" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="H61" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>8</v>
@@ -7568,16 +7568,16 @@
         <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O61" s="1" t="n">
         <v>4</v>
@@ -7589,83 +7589,83 @@
         <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V61" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H62" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O62" s="1" t="n">
         <v>4</v>
@@ -7674,25 +7674,25 @@
         <v>1</v>
       </c>
       <c r="Q62" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R62" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R62" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V62" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X62" s="1" t="n">
         <v>26</v>
@@ -7701,19 +7701,19 @@
         <v>25</v>
       </c>
       <c r="Z62" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA62" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA62" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB62" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
@@ -7735,10 +7735,10 @@
         <v>13</v>
       </c>
       <c r="H63" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>3</v>
@@ -7762,10 +7762,10 @@
         <v>1</v>
       </c>
       <c r="Q63" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R63" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="R63" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
@@ -7801,32 +7801,32 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>20</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>3</v>
@@ -7835,13 +7835,13 @@
         <v>22</v>
       </c>
       <c r="L64" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M64" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M64" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="N64" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
@@ -7859,16 +7859,16 @@
         <v>2</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U64" s="1" t="n">
         <v>14</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X64" s="1" t="n">
         <v>26</v>
@@ -7877,19 +7877,19 @@
         <v>25</v>
       </c>
       <c r="Z64" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA64" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AA64" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="AB64" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -7908,7 +7908,7 @@
         <v>21</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H65" s="1" t="n">
         <v>12</v>
@@ -7917,19 +7917,19 @@
         <v>11</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L65" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M65" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="M65" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="N65" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O65" s="1" t="n">
         <v>4</v>
@@ -7944,7 +7944,7 @@
         <v>6</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T65" s="1" t="n">
         <v>13</v>
@@ -7956,47 +7956,47 @@
         <v>8</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X65" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y65" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z65" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="Z65" s="1" t="n">
+      <c r="AA65" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA65" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="AB65" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>12</v>
@@ -8005,31 +8005,31 @@
         <v>11</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M66" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="N66" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="1" t="n">
         <v>5</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>3</v>
@@ -8050,10 +8050,10 @@
         <v>26</v>
       </c>
       <c r="Y66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z66" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="Z66" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AA66" s="1" t="n">
         <v>22</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -537,23 +537,23 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>91.68000000000001</v>
+        <v>26.86</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-1.85</v>
+        <v>0.35</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>12.31</v>
+        <v>5.38</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.81</v>
+        <v>14.98</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-8.369999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -595,23 +595,23 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>26.77</v>
+        <v>92.44</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.44</v>
+        <v>0.83</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1.48</v>
+        <v>0.12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>5.81</v>
+        <v>13.36</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>13.94</v>
+        <v>14.22</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-0.41</v>
+        <v>-7.67</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>16.96</v>
+        <v>17.03</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.44</v>
+        <v>0.41</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>4.34</v>
+        <v>4.59</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>11.82</v>
+        <v>12.55</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-0.51</v>
+        <v>-0.16</v>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>30.52</v>
+        <v>31.03</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.59</v>
+        <v>1.67</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3.01</v>
+        <v>3.93</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.5</v>
+        <v>3.41</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>7.95</v>
+        <v>10.22</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>102.62</v>
+        <v>103.55</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.21</v>
+        <v>0.91</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.79</v>
+        <v>0.65</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-3.35</v>
+        <v>-3.53</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4.49</v>
+        <v>5.21</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-4.41</v>
+        <v>-3.6</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M6" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,31 +827,31 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>28.44</v>
+        <v>54.22</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-2.1</v>
+        <v>-0.48</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-0.87</v>
+        <v>-2.29</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-3.64</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.7</v>
+        <v/>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-3.87</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,27 +885,27 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>54.48</v>
+        <v>13.37</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-1.96</v>
+        <v>-1.17</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-3.07</v>
+        <v>5.2</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v/>
+        <v>5.21</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
@@ -918,24 +918,24 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,23 +943,23 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>13.43</v>
+        <v>31.84</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>-0.77</v>
+        <v>1.91</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>5.95</v>
+        <v>0.91</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>6.26</v>
+        <v>5.08</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>-1.31</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>79.09</v>
+        <v>79.31</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-0.3</v>
+        <v>0.28</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>-2.25</v>
+        <v>-1.26</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0.17</v>
+        <v>-0.22</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-16.74</v>
+        <v>-16.56</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,31 +1059,31 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>31.51</v>
+        <v>163.28</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>1.03</v>
+        <v>0.58</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-0.51</v>
+        <v>-0.79</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>3.56</v>
+        <v>1.83</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-2.28</v>
+        <v>-1.98</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>33.46</v>
+        <v>33.57</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.62</v>
+        <v>-0.89</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-3.39</v>
+        <v>-3.13</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>130.7</v>
+        <v>281.5</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.42</v>
+        <v>0.9</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.85</v>
+        <v>1.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.97</v>
+        <v>1.69</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-7.38</v>
+        <v>-4.01</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>600.21</v>
+        <v>28.43</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.78</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.65</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-0.35</v>
+        <v>-0.74</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-4.95</v>
+        <v>-3.97</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1295,27 +1295,27 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>162.88</v>
+        <v>131.14</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.8</v>
+        <v>1.53</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.87</v>
+        <v>0.65</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-2.16</v>
+        <v>-7.12</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,23 +1349,23 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>279</v>
+        <v>32.71</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.16</v>
+        <v>0.21</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.09</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.91</v>
+        <v>0.29</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-4.81</v>
+        <v>-2.08</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1407,31 +1407,31 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>32.64</v>
+        <v>599.55</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-1.11</v>
+        <v>0.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-2.23</v>
+        <v>-5.11</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>85.28</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.32</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.27</v>
+        <v>-0.13</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-13.43</v>
+        <v>-13.76</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
@@ -1527,19 +1527,19 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>97.25</v>
+        <v>97.02</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>0.75</v>
+        <v>-0.24</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.72</v>
+        <v>0.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-1.21</v>
+        <v>-1.37</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-2.76</v>
+        <v>-3.05</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
@@ -1581,23 +1581,23 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>39.76</v>
+        <v>39.64</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>1.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-3</v>
+        <v>-3.43</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.85</v>
+        <v>-0.83</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1639,31 +1639,31 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>31.39</v>
+        <v>11.46</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.09</v>
+        <v>1.2</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>1.53</v>
+        <v>-0.21</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-1.99</v>
+        <v>-2.35</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0</v>
+        <v>-8.48</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1697,31 +1697,31 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>11.51</v>
+        <v>31.28</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.61</v>
+        <v>-0.35</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1.63</v>
+        <v>-0.4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.32</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-2.7</v>
+        <v>-2.54</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-8.02</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1755,23 +1755,23 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>52.62</v>
+        <v>12.72</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.31</v>
+        <v>-1.04</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-1.45</v>
+        <v>-3.42</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-3</v>
+        <v>-2.63</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-15.65</v>
+        <v>-10.21</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>101.03</v>
+        <v>101.42</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>1.05</v>
+        <v>0.46</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-1.93</v>
+        <v>-1.66</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-3.73</v>
+        <v>-2.94</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-7.53</v>
+        <v>-7.23</v>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -1871,23 +1871,23 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>12.62</v>
+        <v>52.44</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.96</v>
+        <v>-0.34</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-0.43</v>
+        <v>-0.1</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-4.46</v>
+        <v>-1.01</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-4.22</v>
+        <v>-4.88</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-10.86</v>
+        <v>-15.99</v>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1933,19 +1933,19 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>96.16</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2.76</v>
+        <v>-0.76</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-2.23</v>
+        <v>-2.88</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-5.1</v>
+        <v>-5.99</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-12.56</v>
+        <v>-13.27</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>10.38</v>
+        <v>10.39</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.68</v>
+        <v>0.1</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-2.24</v>
+        <v>-2.27</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-7.8</v>
+        <v>-6.97</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-9.44</v>
+        <v>-9.41</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2049,19 +2049,19 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>32.38</v>
+        <v>32.2</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>5.59</v>
+        <v>4.51</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-8.84</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-25.52</v>
+        <v>-25.98</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
@@ -2345,47 +2345,47 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>26</v>
@@ -2403,53 +2403,53 @@
         <v>5</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z2" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>22</v>
@@ -2473,22 +2473,22 @@
         <v>18</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>21</v>
@@ -2497,50 +2497,50 @@
         <v>4</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z3" s="1" t="n">
+      <c r="AA3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2</v>
@@ -2558,7 +2558,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>14</v>
@@ -2567,68 +2567,68 @@
         <v>26</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X4" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y4" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z4" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
@@ -2637,25 +2637,25 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
@@ -2664,31 +2664,31 @@
         <v>9</v>
       </c>
       <c r="S5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V5" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>10</v>
@@ -2697,26 +2697,26 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
@@ -2725,13 +2725,13 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>18</v>
@@ -2740,10 +2740,10 @@
         <v>15</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
@@ -2758,25 +2758,25 @@
         <v>24</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>10</v>
@@ -2785,26 +2785,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F7" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
@@ -2825,13 +2825,13 @@
         <v>18</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
@@ -2849,7 +2849,7 @@
         <v>8</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>4</v>
@@ -2864,7 +2864,7 @@
         <v>7</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -2883,16 +2883,16 @@
         <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -2910,22 +2910,22 @@
         <v>11</v>
       </c>
       <c r="M8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N8" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O8" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S8" s="1" t="n">
         <v>6</v>
@@ -2937,13 +2937,13 @@
         <v>8</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>5</v>
@@ -2952,71 +2952,71 @@
         <v>7</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N9" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O9" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q9" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>24</v>
@@ -3028,13 +3028,13 @@
         <v>13</v>
       </c>
       <c r="W9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y9" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X9" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y9" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z9" s="1" t="n">
         <v>7</v>
@@ -3043,117 +3043,117 @@
         <v>23</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>20</v>
@@ -3162,7 +3162,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>19</v>
@@ -3183,10 +3183,10 @@
         <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>10</v>
@@ -3195,53 +3195,53 @@
         <v>2</v>
       </c>
       <c r="T11" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>20</v>
@@ -3250,25 +3250,25 @@
         <v>6</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>17</v>
@@ -3277,31 +3277,31 @@
         <v>22</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T12" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U12" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W12" s="1" t="n">
+      <c r="Y12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X12" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z12" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA12" s="1" t="n">
         <v>21</v>
@@ -3313,32 +3313,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>18</v>
@@ -3347,13 +3347,13 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>24</v>
@@ -3365,28 +3365,28 @@
         <v>22</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z13" s="1" t="n">
         <v>5</v>
@@ -3395,68 +3395,68 @@
         <v>21</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E14" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" s="1" t="n">
         <v>26</v>
@@ -3465,7 +3465,7 @@
         <v>7</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>4</v>
@@ -3483,62 +3483,62 @@
         <v>21</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O15" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="R15" s="1" t="n">
         <v>3</v>
@@ -3547,7 +3547,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U15" s="1" t="n">
         <v>7</v>
@@ -3559,7 +3559,7 @@
         <v>4</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>6</v>
@@ -3571,47 +3571,47 @@
         <v>21</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>19</v>
@@ -3620,43 +3620,43 @@
         <v>17</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB16" s="1" t="n">
         <v>9</v>
@@ -3665,7 +3665,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -3675,10 +3675,10 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>18</v>
@@ -3687,19 +3687,19 @@
         <v>21</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>19</v>
@@ -3711,122 +3711,122 @@
         <v>23</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA17" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z18" s="1" t="n">
         <v>4</v>
@@ -3841,41 +3841,41 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
@@ -3890,7 +3890,7 @@
         <v>12</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19" s="1" t="n">
         <v>7</v>
@@ -3899,13 +3899,13 @@
         <v>1</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>3</v>
@@ -3914,7 +3914,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z19" s="1" t="n">
         <v>4</v>
@@ -3929,190 +3929,190 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V20" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X20" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z20" s="1" t="n">
+      <c r="AA20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB20" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA20" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB20" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>15</v>
@@ -4121,128 +4121,128 @@
         <v>25</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K22" s="1" t="n">
+      <c r="P22" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L22" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N22" s="1" t="n">
+      <c r="Q22" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="R22" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W22" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y22" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z22" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J23" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>10</v>
@@ -4254,77 +4254,77 @@
         <v>26</v>
       </c>
       <c r="U23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V23" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W23" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y23" s="1" t="n">
+      <c r="AA23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB23" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="Z23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA23" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB23" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M24" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O24" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>8</v>
@@ -4345,83 +4345,83 @@
         <v>7</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H25" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I25" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O25" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S25" s="1" t="n">
         <v>1</v>
@@ -4433,47 +4433,47 @@
         <v>7</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>22</v>
@@ -4482,43 +4482,43 @@
         <v>20</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V26" s="1" t="n">
         <v>15</v>
@@ -4527,25 +4527,25 @@
         <v>3</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y26" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA26" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -4555,37 +4555,37 @@
         <v>21</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J27" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L27" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>24</v>
@@ -4594,13 +4594,13 @@
         <v>2</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" s="1" t="n">
         <v>25</v>
@@ -4609,19 +4609,19 @@
         <v>6</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y27" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X27" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y27" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z27" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA27" s="1" t="n">
         <v>23</v>
@@ -4633,86 +4633,86 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M28" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N28" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V28" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="W28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z28" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S28" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X28" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z28" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="AA28" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB28" s="1" t="n">
         <v>8</v>
@@ -4721,141 +4721,141 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="F29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G29" s="1" t="n">
+      <c r="H29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M29" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M29" s="1" t="n">
+      <c r="N29" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA29" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="1" t="n">
         <v>11</v>
@@ -4864,13 +4864,13 @@
         <v>7</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V30" s="1" t="n">
         <v>12</v>
@@ -4879,44 +4879,44 @@
         <v>8</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA30" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB30" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z30" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA30" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB30" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C31" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C31" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D31" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>5</v>
@@ -4925,110 +4925,110 @@
         <v>6</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R31" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R31" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V31" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA31" s="1" t="n">
         <v>26</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O32" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>2</v>
@@ -5037,34 +5037,34 @@
         <v>7</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y32" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W32" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X32" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y32" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z32" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>10</v>
@@ -5073,11 +5073,11 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>26</v>
@@ -5092,13 +5092,13 @@
         <v>22</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>3</v>
@@ -5110,13 +5110,13 @@
         <v>18</v>
       </c>
       <c r="M33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N33" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O33" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>2</v>
@@ -5125,53 +5125,53 @@
         <v>7</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W33" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X33" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB33" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z33" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA33" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB33" s="1" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>27</v>
@@ -5192,19 +5192,19 @@
         <v>3</v>
       </c>
       <c r="K34" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N34" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P34" s="1" t="n">
         <v>2</v>
@@ -5219,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U34" s="1" t="n">
         <v>5</v>
@@ -5249,17 +5249,17 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>27</v>
@@ -5268,7 +5268,7 @@
         <v>22</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>4</v>
@@ -5277,37 +5277,37 @@
         <v>6</v>
       </c>
       <c r="J35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P35" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O35" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P35" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q35" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U35" s="1" t="n">
         <v>5</v>
@@ -5316,47 +5316,47 @@
         <v>8</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z35" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA35" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA35" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB35" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F36" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G36" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>4</v>
@@ -5365,155 +5365,155 @@
         <v>6</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L36" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N36" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M36" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N36" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O36" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U36" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z36" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB36" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V37" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W37" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W37" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X37" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z37" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB37" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -5523,16 +5523,16 @@
         <v>14</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
@@ -5544,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L38" s="1" t="n">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>12</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O38" s="1" t="n">
         <v>10</v>
@@ -5562,10 +5562,10 @@
         <v>3</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>2</v>
@@ -5574,7 +5574,7 @@
         <v>23</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V38" s="1" t="n">
         <v>9</v>
@@ -5583,13 +5583,13 @@
         <v>15</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y38" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA38" s="1" t="n">
         <v>26</v>
@@ -5601,26 +5601,26 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F39" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>11</v>
@@ -5641,7 +5641,7 @@
         <v>12</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>10</v>
@@ -5650,16 +5650,16 @@
         <v>3</v>
       </c>
       <c r="Q39" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R39" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R39" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S39" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>8</v>
@@ -5668,28 +5668,28 @@
         <v>9</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X39" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z39" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -5699,7 +5699,7 @@
         <v>13</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>11</v>
@@ -5735,7 +5735,7 @@
         <v>10</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>6</v>
@@ -5744,10 +5744,10 @@
         <v>7</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>8</v>
@@ -5765,7 +5765,7 @@
         <v>16</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA40" s="1" t="n">
         <v>25</v>
@@ -5777,26 +5777,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>11</v>
@@ -5817,28 +5817,28 @@
         <v>12</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U41" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V41" s="1" t="n">
         <v>9</v>
@@ -5847,16 +5847,16 @@
         <v>14</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z41" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB41" s="1" t="n">
         <v>15</v>
@@ -5865,11 +5865,11 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C42" s="1" t="n">
         <v>25</v>
@@ -5878,13 +5878,13 @@
         <v>22</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4</v>
@@ -5893,43 +5893,43 @@
         <v>5</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R42" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>14</v>
@@ -5938,13 +5938,13 @@
         <v>21</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA42" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA42" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB42" s="1" t="n">
         <v>15</v>
@@ -5953,23 +5953,23 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>12</v>
@@ -5981,10 +5981,10 @@
         <v>5</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
@@ -5999,13 +5999,13 @@
         <v>9</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S43" s="1" t="n">
         <v>1</v>
@@ -6014,7 +6014,7 @@
         <v>17</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V43" s="1" t="n">
         <v>10</v>
@@ -6023,16 +6023,16 @@
         <v>14</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y43" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z43" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA43" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA43" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB43" s="1" t="n">
         <v>15</v>
@@ -6041,7 +6041,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -6051,7 +6051,7 @@
         <v>25</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>27</v>
@@ -6060,16 +6060,16 @@
         <v>20</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1" t="n">
         <v>19</v>
@@ -6078,16 +6078,16 @@
         <v>11</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>6</v>
@@ -6102,7 +6102,7 @@
         <v>17</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V44" s="1" t="n">
         <v>10</v>
@@ -6111,7 +6111,7 @@
         <v>14</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y44" s="1" t="n">
         <v>18</v>
@@ -6129,26 +6129,26 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>2</v>
@@ -6160,28 +6160,28 @@
         <v>5</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P45" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R45" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R45" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>1</v>
@@ -6190,7 +6190,7 @@
         <v>17</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V45" s="1" t="n">
         <v>10</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y45" s="1" t="n">
         <v>18</v>
@@ -6208,7 +6208,7 @@
         <v>23</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>15</v>
@@ -6217,32 +6217,32 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46" s="1" t="n">
         <v>5</v>
@@ -6257,65 +6257,65 @@
         <v>13</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R46" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U46" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V46" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA46" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB46" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>25</v>
@@ -6324,22 +6324,22 @@
         <v>14</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>13</v>
@@ -6348,28 +6348,28 @@
         <v>17</v>
       </c>
       <c r="O47" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R47" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P47" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R47" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U47" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V47" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V47" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>15</v>
@@ -6381,7 +6381,7 @@
         <v>19</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA47" s="1" t="n">
         <v>22</v>
@@ -6393,7 +6393,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -6403,31 +6403,31 @@
         <v>24</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J48" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K48" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>13</v>
@@ -6436,7 +6436,7 @@
         <v>17</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P48" s="1" t="n">
         <v>5</v>
@@ -6445,16 +6445,16 @@
         <v>6</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V48" s="1" t="n">
         <v>9</v>
@@ -6466,13 +6466,13 @@
         <v>26</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z48" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA48" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA48" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>16</v>
@@ -6481,41 +6481,41 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D49" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="E49" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G49" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L49" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L49" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>13</v>
@@ -6524,25 +6524,25 @@
         <v>17</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>9</v>
@@ -6554,10 +6554,10 @@
         <v>26</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA49" s="1" t="n">
         <v>25</v>
@@ -6569,23 +6569,23 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>11</v>
@@ -6609,7 +6609,7 @@
         <v>13</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>8</v>
@@ -6627,16 +6627,16 @@
         <v>1</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U50" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V50" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V50" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W50" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X50" s="1" t="n">
         <v>26</v>
@@ -6645,19 +6645,19 @@
         <v>20</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -6667,7 +6667,7 @@
         <v>24</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>21</v>
@@ -6685,7 +6685,7 @@
         <v>5</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" s="1" t="n">
         <v>19</v>
@@ -6700,19 +6700,19 @@
         <v>16</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T51" s="1" t="n">
         <v>17</v>
@@ -6733,7 +6733,7 @@
         <v>20</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>25</v>
@@ -6745,7 +6745,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -6755,43 +6755,43 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I52" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K52" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>6</v>
@@ -6800,19 +6800,19 @@
         <v>8</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X52" s="1" t="n">
         <v>26</v>
@@ -6821,19 +6821,19 @@
         <v>20</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -6843,16 +6843,16 @@
         <v>24</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E53" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F53" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>3</v>
@@ -6864,10 +6864,10 @@
         <v>5</v>
       </c>
       <c r="K53" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L53" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>13</v>
@@ -6879,25 +6879,25 @@
         <v>10</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T53" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U53" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V53" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V53" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>15</v>
@@ -6906,10 +6906,10 @@
         <v>26</v>
       </c>
       <c r="Y53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z53" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z53" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>25</v>
@@ -6921,23 +6921,23 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D54" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F54" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>18</v>
@@ -6949,46 +6949,46 @@
         <v>4</v>
       </c>
       <c r="J54" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L54" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M54" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M54" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N54" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X54" s="1" t="n">
         <v>26</v>
@@ -6997,35 +6997,35 @@
         <v>21</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>18</v>
@@ -7037,31 +7037,31 @@
         <v>4</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N55" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>2</v>
@@ -7070,98 +7070,98 @@
         <v>20</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X55" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="E56" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U56" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>14</v>
@@ -7170,7 +7170,7 @@
         <v>26</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z56" s="1" t="n">
         <v>21</v>
@@ -7185,17 +7185,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D57" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>22</v>
@@ -7204,31 +7204,31 @@
         <v>19</v>
       </c>
       <c r="G57" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M57" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N57" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H57" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J57" s="1" t="n">
+      <c r="O57" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K57" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L57" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M57" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N57" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O57" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P57" s="1" t="n">
         <v>1</v>
@@ -7237,56 +7237,56 @@
         <v>5</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y57" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z57" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z57" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>19</v>
@@ -7295,7 +7295,7 @@
         <v>18</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>8</v>
@@ -7304,13 +7304,13 @@
         <v>3</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L58" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N58" s="1" t="n">
         <v>14</v>
@@ -7325,7 +7325,7 @@
         <v>5</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
@@ -7334,10 +7334,10 @@
         <v>12</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>15</v>
@@ -7346,13 +7346,13 @@
         <v>26</v>
       </c>
       <c r="Y58" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z58" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA58" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Z58" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA58" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB58" s="1" t="n">
         <v>16</v>
@@ -7361,7 +7361,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -7374,16 +7374,16 @@
         <v>23</v>
       </c>
       <c r="E59" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="F59" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>18</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>8</v>
@@ -7398,7 +7398,7 @@
         <v>17</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>14</v>
@@ -7413,7 +7413,7 @@
         <v>5</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
@@ -7422,7 +7422,7 @@
         <v>12</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V59" s="1" t="n">
         <v>9</v>
@@ -7449,17 +7449,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D60" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>19</v>
@@ -7471,7 +7471,7 @@
         <v>18</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>8</v>
@@ -7486,7 +7486,7 @@
         <v>17</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>14</v>
@@ -7501,16 +7501,16 @@
         <v>5</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V60" s="1" t="n">
         <v>9</v>
@@ -7522,13 +7522,13 @@
         <v>26</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB60" s="1" t="n">
         <v>16</v>
@@ -7537,29 +7537,29 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>20</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>8</v>
@@ -7568,16 +7568,16 @@
         <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O61" s="1" t="n">
         <v>4</v>
@@ -7589,7 +7589,7 @@
         <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
@@ -7604,7 +7604,7 @@
         <v>9</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X61" s="1" t="n">
         <v>26</v>
@@ -7613,41 +7613,41 @@
         <v>24</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA61" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E62" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F62" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="H62" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>8</v>
@@ -7656,16 +7656,16 @@
         <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O62" s="1" t="n">
         <v>4</v>
@@ -7677,83 +7677,83 @@
         <v>5</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V62" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X62" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA62" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E63" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E63" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H63" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>4</v>
@@ -7762,25 +7762,25 @@
         <v>1</v>
       </c>
       <c r="Q63" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R63" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R63" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X63" s="1" t="n">
         <v>26</v>
@@ -7789,19 +7789,19 @@
         <v>25</v>
       </c>
       <c r="Z63" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA63" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA63" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB63" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -7823,10 +7823,10 @@
         <v>13</v>
       </c>
       <c r="H64" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>3</v>
@@ -7850,10 +7850,10 @@
         <v>1</v>
       </c>
       <c r="Q64" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R64" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="R64" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
@@ -7889,32 +7889,32 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>20</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>3</v>
@@ -7923,13 +7923,13 @@
         <v>22</v>
       </c>
       <c r="L65" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M65" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M65" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="N65" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O65" s="1" t="n">
         <v>4</v>
@@ -7947,16 +7947,16 @@
         <v>2</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U65" s="1" t="n">
         <v>14</v>
       </c>
       <c r="V65" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X65" s="1" t="n">
         <v>26</v>
@@ -7965,19 +7965,19 @@
         <v>25</v>
       </c>
       <c r="Z65" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA65" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AA65" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="AB65" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -7996,7 +7996,7 @@
         <v>21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>12</v>
@@ -8005,19 +8005,19 @@
         <v>11</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="M66" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="N66" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>4</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T66" s="1" t="n">
         <v>13</v>
@@ -8044,22 +8044,22 @@
         <v>8</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X66" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y66" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z66" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="Z66" s="1" t="n">
+      <c r="AA66" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA66" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="AB66" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>26.86</v>
+        <v>26.51</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.34</v>
+        <v>-1.3</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>5.38</v>
+        <v>2.59</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.98</v>
+        <v>14.5</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,11 +561,11 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -595,23 +595,23 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>92.44</v>
+        <v>16.83</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.83</v>
+        <v>-1.17</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>13.36</v>
+        <v>2.34</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>14.22</v>
+        <v>12.13</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-7.67</v>
+        <v>-0.45</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -653,23 +653,23 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>17.03</v>
+        <v>90.25</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.41</v>
+        <v>-2.37</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.29</v>
+        <v>-0.71</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>4.59</v>
+        <v>11.43</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>12.55</v>
+        <v>11.66</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-0.16</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -711,23 +711,23 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>31.03</v>
+        <v>30.63</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.67</v>
+        <v>-1.29</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3.93</v>
+        <v>2.83</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>3.41</v>
+        <v>2.71</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>10.22</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -773,27 +773,27 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>103.55</v>
+        <v>103.28</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.91</v>
+        <v>-0.26</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.65</v>
+        <v>1.5</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-3.53</v>
+        <v>-2.99</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>5.21</v>
+        <v>4.33</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-3.6</v>
+        <v>-2.99</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>54.22</v>
+        <v>53.66</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.48</v>
+        <v>-1.03</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-2.29</v>
+        <v>-3.01</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-3.64</v>
+        <v>-3.39</v>
       </c>
       <c r="H7" s="1" t="n">
         <v/>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>13.37</v>
+        <v>13.21</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.45</v>
+        <v>-1.2</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-1.17</v>
+        <v>-2.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>5.21</v>
+        <v>4.3</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>31.84</v>
+        <v>31.66</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.57</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.91</v>
+        <v>1.28</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>5.08</v>
+        <v>4.28</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-1.31</v>
+        <v>-0.99</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,23 +1001,23 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>79.31</v>
+        <v>281.82</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>-1.26</v>
+        <v>2.87</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-0.22</v>
+        <v>2.66</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>3.76</v>
+        <v>3.03</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-16.56</v>
+        <v>-3.04</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M10" s="1" t="inlineStr">
@@ -1044,14 +1044,14 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>163.28</v>
+        <v>78.11</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.25</v>
+        <v>-1.51</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.58</v>
+        <v>-2.26</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.22</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.83</v>
+        <v>2.99</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-1.98</v>
+        <v>-17.09</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1117,23 +1117,23 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>33.57</v>
+        <v>162.61</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.33</v>
+        <v>-0.41</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.14</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-3.13</v>
+        <v>-1.51</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>281.5</v>
+        <v>131.35</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.9</v>
+        <v>0.16</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-4.01</v>
+        <v>-6.14</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>28.43</v>
+        <v>33.6</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>-0.65</v>
+        <v>1.48</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-0.74</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-3.97</v>
+        <v>-2.18</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1291,23 +1291,23 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>131.14</v>
+        <v>84.11</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.34</v>
+        <v>-1.06</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.96</v>
+        <v>-0.35</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>1.53</v>
+        <v>3.51</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -1315,33 +1315,33 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-7.12</v>
+        <v>-13.91</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,57 +1349,57 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>32.71</v>
+        <v>28.06</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.21</v>
+        <v>-1.3</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-0.38</v>
+        <v>-0.93</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.29</v>
+        <v>-1.42</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.14</v>
+        <v>0.52</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-2.08</v>
+        <v>-4.37</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1407,40 +1407,40 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>599.55</v>
+        <v>32.34</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.11</v>
+        <v>-1.13</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.24</v>
+        <v>-0.93</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-0.29</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-5.11</v>
+        <v>-2.32</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1465,23 +1465,23 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>85.01000000000001</v>
+        <v>592.24</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>-0.32</v>
+        <v>-1.22</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.38</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>3.36</v>
+        <v>-0.63</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-13.76</v>
+        <v>-5.43</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M18" s="1" t="inlineStr">
@@ -1527,19 +1527,19 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>97.02</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-0.24</v>
+        <v>-0.8</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.09</v>
+        <v>0.59</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-1.37</v>
+        <v>-1.84</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.31</v>
+        <v>-0.7</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-3.05</v>
+        <v>-2.97</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -1581,27 +1581,27 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>39.64</v>
+        <v>30.95</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.3</v>
+        <v>-1.05</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.26</v>
+        <v>-0.86</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-3.43</v>
+        <v>1.09</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.83</v>
+        <v>-1.74</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J20" s="1" t="n">
@@ -1609,17 +1609,17 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1639,23 +1639,23 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>11.46</v>
+        <v>39.45</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.43</v>
+        <v>-0.48</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>1.2</v>
+        <v>0.21</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-0.21</v>
+        <v>-2.65</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-2.35</v>
+        <v>-2.04</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-8.48</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N21" s="1" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1701,27 +1701,27 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>31.28</v>
+        <v>12.66</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.35</v>
+        <v>-0.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>-0.4</v>
+        <v>0.67</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-0.32</v>
+        <v>-1.2</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-2.54</v>
+        <v>-2.81</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0</v>
+        <v>-9.83</v>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
@@ -1730,24 +1730,24 @@
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N22" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1755,23 +1755,23 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>12.72</v>
+        <v>11.38</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.79</v>
+        <v>-0.7</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>-1.04</v>
+        <v>0.96</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-3.42</v>
+        <v>-0.4</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-2.63</v>
+        <v>-3.05</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1779,26 +1779,26 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-10.21</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="M23" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="N23" s="1" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>101.42</v>
+        <v>100.98</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.39</v>
+        <v>-0.43</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.46</v>
+        <v>1.52</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-1.66</v>
+        <v>-0.93</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-2.94</v>
+        <v>-3.67</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-7.23</v>
+        <v>-6.8</v>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
@@ -1871,23 +1871,23 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>52.44</v>
+        <v>52.82</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.34</v>
+        <v>0.72</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-0.1</v>
+        <v>2.28</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-1.01</v>
+        <v>-0.03</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-4.88</v>
+        <v>-4.1</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -1895,16 +1895,16 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-15.99</v>
+        <v>-14.63</v>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M25" s="1" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -1929,50 +1929,50 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>95.43000000000001</v>
+        <v>31.71</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-0.76</v>
+        <v>-1.52</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>2.18</v>
+        <v>0.67</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-2.88</v>
+        <v>5.16</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-5.99</v>
+        <v>-6.5</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-13.27</v>
+        <v>-26.46</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="M26" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1987,23 +1987,23 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.7</v>
+        <v>1.69</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-2.27</v>
+        <v>-1.81</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-6.97</v>
+        <v>-7.11</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-9.41</v>
+        <v>-8.68</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2030,14 +2030,14 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -2045,40 +2045,40 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>32.2</v>
+        <v>93.67</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.84</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>4.51</v>
+        <v>-3.17</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-9.119999999999999</v>
+        <v>-7.23</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-25.98</v>
+        <v>-14.11</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M28" s="1" t="inlineStr">
@@ -2345,23 +2345,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F2" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24</v>
@@ -2370,61 +2370,61 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L2" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W2" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y2" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>8</v>
@@ -2433,47 +2433,47 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>26</v>
@@ -2491,53 +2491,53 @@
         <v>5</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z3" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>22</v>
@@ -2561,22 +2561,22 @@
         <v>18</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T4" s="1" t="n">
         <v>21</v>
@@ -2585,50 +2585,50 @@
         <v>4</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="AA4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB4" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA4" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
@@ -2646,7 +2646,7 @@
         <v>16</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>14</v>
@@ -2655,68 +2655,68 @@
         <v>26</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S5" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y5" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z5" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
@@ -2725,25 +2725,25 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
@@ -2752,31 +2752,31 @@
         <v>9</v>
       </c>
       <c r="S6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V6" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>10</v>
@@ -2785,26 +2785,26 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
@@ -2813,13 +2813,13 @@
         <v>3</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>18</v>
@@ -2828,10 +2828,10 @@
         <v>15</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
@@ -2846,25 +2846,25 @@
         <v>24</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>10</v>
@@ -2873,26 +2873,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -2913,13 +2913,13 @@
         <v>18</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
@@ -2937,7 +2937,7 @@
         <v>8</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>4</v>
@@ -2952,7 +2952,7 @@
         <v>7</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>10</v>
@@ -2961,7 +2961,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -2971,16 +2971,16 @@
         <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
@@ -2998,22 +2998,22 @@
         <v>11</v>
       </c>
       <c r="M9" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N9" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O9" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>6</v>
@@ -3025,13 +3025,13 @@
         <v>8</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y9" s="1" t="n">
         <v>5</v>
@@ -3040,71 +3040,71 @@
         <v>7</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P10" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O10" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P10" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q10" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>24</v>
@@ -3116,13 +3116,13 @@
         <v>13</v>
       </c>
       <c r="W10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y10" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X10" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y10" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z10" s="1" t="n">
         <v>7</v>
@@ -3131,117 +3131,117 @@
         <v>23</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z11" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>20</v>
@@ -3250,7 +3250,7 @@
         <v>6</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>19</v>
@@ -3271,10 +3271,10 @@
         <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R12" s="1" t="n">
         <v>10</v>
@@ -3283,53 +3283,53 @@
         <v>2</v>
       </c>
       <c r="T12" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X12" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>20</v>
@@ -3338,25 +3338,25 @@
         <v>6</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
         <v>17</v>
@@ -3365,31 +3365,31 @@
         <v>22</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U13" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W13" s="1" t="n">
+      <c r="Y13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z13" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X13" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z13" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA13" s="1" t="n">
         <v>21</v>
@@ -3401,32 +3401,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>18</v>
@@ -3435,13 +3435,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>24</v>
@@ -3453,28 +3453,28 @@
         <v>22</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z14" s="1" t="n">
         <v>5</v>
@@ -3483,68 +3483,68 @@
         <v>21</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E15" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>26</v>
@@ -3553,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>4</v>
@@ -3571,62 +3571,62 @@
         <v>21</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O16" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>3</v>
@@ -3635,7 +3635,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U16" s="1" t="n">
         <v>7</v>
@@ -3647,7 +3647,7 @@
         <v>4</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y16" s="1" t="n">
         <v>6</v>
@@ -3659,47 +3659,47 @@
         <v>21</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>19</v>
@@ -3708,43 +3708,43 @@
         <v>17</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB17" s="1" t="n">
         <v>9</v>
@@ -3753,7 +3753,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -3763,10 +3763,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>18</v>
@@ -3775,19 +3775,19 @@
         <v>21</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
@@ -3799,122 +3799,122 @@
         <v>23</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA18" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z19" s="1" t="n">
         <v>4</v>
@@ -3929,41 +3929,41 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
@@ -3978,7 +3978,7 @@
         <v>12</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R20" s="1" t="n">
         <v>7</v>
@@ -3987,13 +3987,13 @@
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>3</v>
@@ -4002,7 +4002,7 @@
         <v>23</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z20" s="1" t="n">
         <v>4</v>
@@ -4017,190 +4017,190 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V21" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z21" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X21" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y21" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z21" s="1" t="n">
+      <c r="AA21" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB21" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA21" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB21" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>15</v>
@@ -4209,128 +4209,128 @@
         <v>25</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" s="1" t="n">
+      <c r="P23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L23" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N23" s="1" t="n">
+      <c r="Q23" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="O23" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P23" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="R23" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U23" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W23" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y23" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W23" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X23" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y23" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z23" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J24" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N24" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P24" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R24" s="1" t="n">
         <v>10</v>
@@ -4342,77 +4342,77 @@
         <v>26</v>
       </c>
       <c r="U24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V24" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W24" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X24" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y24" s="1" t="n">
+      <c r="AA24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB24" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="Z24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA24" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB24" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N25" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M25" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O25" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P25" s="1" t="n">
         <v>8</v>
@@ -4433,83 +4433,83 @@
         <v>7</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H26" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I26" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S26" s="1" t="n">
         <v>1</v>
@@ -4521,47 +4521,47 @@
         <v>7</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y26" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA26" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>22</v>
@@ -4570,43 +4570,43 @@
         <v>20</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V27" s="1" t="n">
         <v>15</v>
@@ -4615,25 +4615,25 @@
         <v>3</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y27" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -4643,37 +4643,37 @@
         <v>21</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L28" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>24</v>
@@ -4682,13 +4682,13 @@
         <v>2</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R28" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>25</v>
@@ -4697,19 +4697,19 @@
         <v>6</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X28" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z28" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>23</v>
@@ -4721,86 +4721,86 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M29" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N29" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="W29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S29" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W29" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X29" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y29" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z29" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="AA29" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>8</v>
@@ -4809,141 +4809,141 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="F30" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D30" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G30" s="1" t="n">
+      <c r="H30" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M30" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L30" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M30" s="1" t="n">
+      <c r="N30" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N30" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA30" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="1" t="n">
         <v>11</v>
@@ -4952,13 +4952,13 @@
         <v>7</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V31" s="1" t="n">
         <v>12</v>
@@ -4967,44 +4967,44 @@
         <v>8</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA31" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB31" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z31" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA31" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB31" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C32" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D32" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>5</v>
@@ -5013,110 +5013,110 @@
         <v>6</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R32" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R32" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA32" s="1" t="n">
         <v>26</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L33" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N33" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O33" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>2</v>
@@ -5125,34 +5125,34 @@
         <v>7</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V33" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y33" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W33" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X33" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y33" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z33" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>10</v>
@@ -5161,11 +5161,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>26</v>
@@ -5180,13 +5180,13 @@
         <v>22</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>3</v>
@@ -5198,13 +5198,13 @@
         <v>18</v>
       </c>
       <c r="M34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N34" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P34" s="1" t="n">
         <v>2</v>
@@ -5213,53 +5213,53 @@
         <v>7</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W34" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W34" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X34" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y34" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB34" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z34" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA34" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB34" s="1" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>27</v>
@@ -5280,19 +5280,19 @@
         <v>3</v>
       </c>
       <c r="K35" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N35" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O35" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P35" s="1" t="n">
         <v>2</v>
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U35" s="1" t="n">
         <v>5</v>
@@ -5337,17 +5337,17 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
@@ -5356,7 +5356,7 @@
         <v>22</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>4</v>
@@ -5365,37 +5365,37 @@
         <v>6</v>
       </c>
       <c r="J36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P36" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K36" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N36" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O36" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P36" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U36" s="1" t="n">
         <v>5</v>
@@ -5404,47 +5404,47 @@
         <v>8</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z36" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA36" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA36" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB36" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C37" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D37" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F37" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4</v>
@@ -5453,155 +5453,155 @@
         <v>6</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L37" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N37" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M37" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O37" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z37" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB37" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P38" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W38" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W38" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X38" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z38" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -5611,16 +5611,16 @@
         <v>14</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>11</v>
@@ -5641,7 +5641,7 @@
         <v>12</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O39" s="1" t="n">
         <v>10</v>
@@ -5650,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S39" s="1" t="n">
         <v>2</v>
@@ -5662,7 +5662,7 @@
         <v>23</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V39" s="1" t="n">
         <v>9</v>
@@ -5671,13 +5671,13 @@
         <v>15</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y39" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA39" s="1" t="n">
         <v>26</v>
@@ -5689,26 +5689,26 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F40" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>11</v>
@@ -5729,7 +5729,7 @@
         <v>12</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>10</v>
@@ -5738,16 +5738,16 @@
         <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R40" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R40" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>8</v>
@@ -5756,28 +5756,28 @@
         <v>9</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X40" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z40" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -5787,7 +5787,7 @@
         <v>13</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>27</v>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>11</v>
@@ -5823,7 +5823,7 @@
         <v>10</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>6</v>
@@ -5832,10 +5832,10 @@
         <v>7</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>8</v>
@@ -5853,7 +5853,7 @@
         <v>16</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA41" s="1" t="n">
         <v>25</v>
@@ -5865,26 +5865,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4</v>
@@ -5896,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
@@ -5905,28 +5905,28 @@
         <v>12</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R42" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U42" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U42" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V42" s="1" t="n">
         <v>9</v>
@@ -5935,16 +5935,16 @@
         <v>14</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z42" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB42" s="1" t="n">
         <v>15</v>
@@ -5953,11 +5953,11 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C43" s="1" t="n">
         <v>25</v>
@@ -5966,13 +5966,13 @@
         <v>22</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>4</v>
@@ -5981,43 +5981,43 @@
         <v>5</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P43" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R43" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W43" s="1" t="n">
         <v>14</v>
@@ -6026,13 +6026,13 @@
         <v>21</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z43" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA43" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA43" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB43" s="1" t="n">
         <v>15</v>
@@ -6041,23 +6041,23 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>12</v>
@@ -6069,10 +6069,10 @@
         <v>5</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
@@ -6087,13 +6087,13 @@
         <v>9</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>17</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V44" s="1" t="n">
         <v>10</v>
@@ -6111,16 +6111,16 @@
         <v>14</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y44" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z44" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA44" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA44" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB44" s="1" t="n">
         <v>15</v>
@@ -6129,7 +6129,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -6139,7 +6139,7 @@
         <v>25</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>27</v>
@@ -6148,16 +6148,16 @@
         <v>20</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K45" s="1" t="n">
         <v>19</v>
@@ -6166,16 +6166,16 @@
         <v>11</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>6</v>
@@ -6190,7 +6190,7 @@
         <v>17</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V45" s="1" t="n">
         <v>10</v>
@@ -6199,7 +6199,7 @@
         <v>14</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y45" s="1" t="n">
         <v>18</v>
@@ -6217,26 +6217,26 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>2</v>
@@ -6248,28 +6248,28 @@
         <v>5</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P46" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q46" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R46" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R46" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S46" s="1" t="n">
         <v>1</v>
@@ -6278,7 +6278,7 @@
         <v>17</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V46" s="1" t="n">
         <v>10</v>
@@ -6287,7 +6287,7 @@
         <v>14</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y46" s="1" t="n">
         <v>18</v>
@@ -6296,7 +6296,7 @@
         <v>23</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>15</v>
@@ -6305,32 +6305,32 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47" s="1" t="n">
         <v>5</v>
@@ -6345,65 +6345,65 @@
         <v>13</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R47" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U47" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S47" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T47" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U47" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V47" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA47" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>25</v>
@@ -6412,22 +6412,22 @@
         <v>14</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M48" s="1" t="n">
         <v>13</v>
@@ -6436,28 +6436,28 @@
         <v>17</v>
       </c>
       <c r="O48" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R48" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P48" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R48" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U48" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V48" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V48" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>15</v>
@@ -6469,7 +6469,7 @@
         <v>19</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA48" s="1" t="n">
         <v>22</v>
@@ -6481,7 +6481,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -6491,31 +6491,31 @@
         <v>24</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J49" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K49" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>13</v>
@@ -6524,7 +6524,7 @@
         <v>17</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P49" s="1" t="n">
         <v>5</v>
@@ -6533,16 +6533,16 @@
         <v>6</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>9</v>
@@ -6554,13 +6554,13 @@
         <v>26</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z49" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA49" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA49" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>16</v>
@@ -6569,41 +6569,41 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="E50" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G50" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L50" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L50" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>13</v>
@@ -6612,25 +6612,25 @@
         <v>17</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V50" s="1" t="n">
         <v>9</v>
@@ -6642,10 +6642,10 @@
         <v>26</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>25</v>
@@ -6657,23 +6657,23 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>11</v>
@@ -6697,7 +6697,7 @@
         <v>13</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>8</v>
@@ -6715,16 +6715,16 @@
         <v>1</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U51" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V51" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V51" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W51" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X51" s="1" t="n">
         <v>26</v>
@@ -6733,19 +6733,19 @@
         <v>20</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -6755,7 +6755,7 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>21</v>
@@ -6773,7 +6773,7 @@
         <v>5</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K52" s="1" t="n">
         <v>19</v>
@@ -6788,19 +6788,19 @@
         <v>16</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>17</v>
@@ -6821,7 +6821,7 @@
         <v>20</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>25</v>
@@ -6833,7 +6833,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -6843,43 +6843,43 @@
         <v>24</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J53" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K53" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L53" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>6</v>
@@ -6888,19 +6888,19 @@
         <v>8</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X53" s="1" t="n">
         <v>26</v>
@@ -6909,19 +6909,19 @@
         <v>20</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -6931,16 +6931,16 @@
         <v>24</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E54" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F54" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>3</v>
@@ -6952,10 +6952,10 @@
         <v>5</v>
       </c>
       <c r="K54" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>13</v>
@@ -6967,25 +6967,25 @@
         <v>10</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T54" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U54" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V54" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V54" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W54" s="1" t="n">
         <v>15</v>
@@ -6994,10 +6994,10 @@
         <v>26</v>
       </c>
       <c r="Y54" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z54" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z54" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
@@ -7009,23 +7009,23 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D55" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F55" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>18</v>
@@ -7037,46 +7037,46 @@
         <v>4</v>
       </c>
       <c r="J55" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M55" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K55" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L55" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M55" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N55" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X55" s="1" t="n">
         <v>26</v>
@@ -7085,35 +7085,35 @@
         <v>21</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>18</v>
@@ -7125,31 +7125,31 @@
         <v>4</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N56" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>2</v>
@@ -7158,98 +7158,98 @@
         <v>20</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D57" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="E57" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U57" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>14</v>
@@ -7258,7 +7258,7 @@
         <v>26</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>21</v>
@@ -7273,17 +7273,17 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>22</v>
@@ -7292,31 +7292,31 @@
         <v>19</v>
       </c>
       <c r="G58" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M58" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N58" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H58" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I58" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" s="1" t="n">
+      <c r="O58" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K58" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L58" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M58" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N58" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O58" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P58" s="1" t="n">
         <v>1</v>
@@ -7325,56 +7325,56 @@
         <v>5</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y58" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z58" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z58" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>19</v>
@@ -7383,7 +7383,7 @@
         <v>18</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>8</v>
@@ -7392,13 +7392,13 @@
         <v>3</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L59" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>14</v>
@@ -7413,7 +7413,7 @@
         <v>5</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
@@ -7422,10 +7422,10 @@
         <v>12</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>15</v>
@@ -7434,13 +7434,13 @@
         <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z59" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA59" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Z59" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA59" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB59" s="1" t="n">
         <v>16</v>
@@ -7449,7 +7449,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -7462,16 +7462,16 @@
         <v>23</v>
       </c>
       <c r="E60" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>18</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>8</v>
@@ -7486,7 +7486,7 @@
         <v>17</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>14</v>
@@ -7501,7 +7501,7 @@
         <v>5</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
@@ -7510,7 +7510,7 @@
         <v>12</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V60" s="1" t="n">
         <v>9</v>
@@ -7537,17 +7537,17 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>19</v>
@@ -7559,7 +7559,7 @@
         <v>18</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>8</v>
@@ -7574,7 +7574,7 @@
         <v>17</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N61" s="1" t="n">
         <v>14</v>
@@ -7589,16 +7589,16 @@
         <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V61" s="1" t="n">
         <v>9</v>
@@ -7610,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB61" s="1" t="n">
         <v>16</v>
@@ -7625,29 +7625,29 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>20</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>8</v>
@@ -7656,16 +7656,16 @@
         <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O62" s="1" t="n">
         <v>4</v>
@@ -7677,7 +7677,7 @@
         <v>5</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
@@ -7692,7 +7692,7 @@
         <v>9</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X62" s="1" t="n">
         <v>26</v>
@@ -7701,41 +7701,41 @@
         <v>24</v>
       </c>
       <c r="Z62" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA62" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E63" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G63" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F63" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="H63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>8</v>
@@ -7744,16 +7744,16 @@
         <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>4</v>
@@ -7765,83 +7765,83 @@
         <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X63" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H64" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
@@ -7850,25 +7850,25 @@
         <v>1</v>
       </c>
       <c r="Q64" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R64" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V64" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X64" s="1" t="n">
         <v>26</v>
@@ -7877,19 +7877,19 @@
         <v>25</v>
       </c>
       <c r="Z64" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA64" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA64" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB64" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -7911,10 +7911,10 @@
         <v>13</v>
       </c>
       <c r="H65" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>3</v>
@@ -7938,10 +7938,10 @@
         <v>1</v>
       </c>
       <c r="Q65" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R65" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="R65" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>2</v>
@@ -7977,32 +7977,32 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" s="1" t="n">
         <v>20</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>3</v>
@@ -8011,13 +8011,13 @@
         <v>22</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="M66" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="N66" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>4</v>
@@ -8035,16 +8035,16 @@
         <v>2</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U66" s="1" t="n">
         <v>14</v>
       </c>
       <c r="V66" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X66" s="1" t="n">
         <v>26</v>
@@ -8053,13 +8053,13 @@
         <v>25</v>
       </c>
       <c r="Z66" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA66" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="AA66" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="AB66" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -537,23 +537,23 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>26.51</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-1.3</v>
+        <v>-1.86</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-0.39</v>
+        <v>-1.17</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>2.59</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>14.5</v>
+        <v>11.52</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-10.11</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -595,23 +595,23 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>16.83</v>
+        <v>26.32</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-1.17</v>
+        <v>-0.72</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.57</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2.34</v>
+        <v>2.97</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>12.13</v>
+        <v>10.6</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-0.45</v>
+        <v>-0.57</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -653,23 +653,23 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>90.25</v>
+        <v>16.73</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-2.37</v>
+        <v>-0.59</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.71</v>
+        <v>-0.34</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>11.43</v>
+        <v>2.84</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>11.66</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>-9.050000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
@@ -711,23 +711,23 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>30.63</v>
+        <v>30.15</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-1.29</v>
+        <v>-1.57</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2.83</v>
+        <v>0.32</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2.71</v>
+        <v>1.57</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>6.31</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -769,23 +769,23 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>103.28</v>
+        <v>283.7</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.26</v>
+        <v>0.67</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.5</v>
+        <v>3.87</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-2.99</v>
+        <v>5.02</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4.33</v>
+        <v>5.94</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-2.99</v>
+        <v>-1.71</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>53.66</v>
+        <v>52.96</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-1.03</v>
+        <v>-1.3</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-3.01</v>
+        <v>-1.33</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-3.39</v>
+        <v>-2.79</v>
       </c>
       <c r="H7" s="1" t="n">
         <v/>
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,23 +885,23 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>13.21</v>
+        <v>31.56</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-1.2</v>
+        <v>-0.32</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-2.8</v>
+        <v>2.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>5.15</v>
+        <v>2.54</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4.3</v>
+        <v>5.75</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,23 +943,23 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>31.66</v>
+        <v>13.12</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-0.57</v>
+        <v>-0.68</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>2.09</v>
+        <v>-1.68</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1.28</v>
+        <v>5.79</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-0.99</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1001,23 +1001,23 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>281.82</v>
+        <v>77.23</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0.11</v>
+        <v>-1.13</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2.87</v>
+        <v>-1.45</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>2.66</v>
+        <v>-2.33</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>3.03</v>
+        <v>3.7</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,33 +1025,33 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-3.04</v>
+        <v>-17.44</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>78.11</v>
+        <v>102.86</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-1.51</v>
+        <v>-0.41</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-2.26</v>
+        <v>2.03</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-1.22</v>
+        <v>-0.51</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-17.09</v>
+        <v>-2.7</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -1102,14 +1102,14 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1117,31 +1117,31 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>162.61</v>
+        <v>130.97</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.41</v>
+        <v>-0.29</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.91</v>
+        <v>2.12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.14</v>
+        <v>3.19</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-1.51</v>
+        <v>-5.75</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>131.35</v>
+        <v>162.06</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.16</v>
+        <v>-0.34</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>2.08</v>
+        <v>1.15</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>2.91</v>
+        <v>1.18</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-6.14</v>
+        <v>-1.15</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>33.6</v>
+        <v>33.41</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.09</v>
+        <v>-0.57</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>1.48</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>0.35</v>
-      </c>
       <c r="H14" s="1" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-2.18</v>
+        <v>-2.04</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -1291,31 +1291,31 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>84.11</v>
+        <v>27.83</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-1.06</v>
+        <v>-0.82</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.35</v>
+        <v>-1.49</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>3.51</v>
+        <v>-2.93</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-13.91</v>
+        <v>-4.48</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M15" s="1" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,31 +1349,31 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>28.06</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-1.3</v>
+        <v>-0.64</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.22</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-1.42</v>
+        <v>3.65</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.52</v>
+        <v>0.98</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-4.37</v>
+        <v>-13.86</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M16" s="1" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1411,27 +1411,27 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>32.34</v>
+        <v>586.72</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-1.13</v>
+        <v>-0.93</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.67</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.1</v>
+        <v>-1.97</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.05</v>
+        <v>0.17</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-2.32</v>
+        <v>-5.64</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
@@ -1450,14 +1450,14 @@
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1469,27 +1469,27 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>592.24</v>
+        <v>32.04</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>-1.22</v>
+        <v>-0.93</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>-0.38</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-0.63</v>
+        <v>-0.12</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-5.43</v>
+        <v>-2.54</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -1523,23 +1523,23 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>96.23999999999999</v>
+        <v>95.59</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-0.8</v>
+        <v>-0.68</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-1.84</v>
+        <v>-1.35</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.7</v>
+        <v>-0.98</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-2.97</v>
+        <v>-2.94</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1581,23 +1581,23 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>30.95</v>
+        <v>30.78</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-1.05</v>
+        <v>-0.55</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>-0.86</v>
+        <v>-0.3</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.74</v>
+        <v>-1.23</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1639,23 +1639,23 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>39.45</v>
+        <v>12.57</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.71</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.21</v>
+        <v>1.17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-2.65</v>
+        <v>-0.17</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-2.04</v>
+        <v>-2.76</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0</v>
+        <v>-9.84</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
@@ -1682,14 +1682,14 @@
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1701,19 +1701,19 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>12.66</v>
+        <v>11.28</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.47</v>
+        <v>-0.88</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-1.2</v>
+        <v>-0.43</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-2.81</v>
+        <v>-3.07</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
@@ -1721,11 +1721,11 @@
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-9.83</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
@@ -1740,14 +1740,14 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1755,23 +1755,23 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>11.38</v>
+        <v>39.08</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.96</v>
+        <v>0.29</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-0.4</v>
+        <v>-1.59</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-3.05</v>
+        <v>-3.28</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>100.98</v>
+        <v>99.92</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.43</v>
+        <v>-1.05</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.76</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-3.67</v>
+        <v>-4.09</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -1837,16 +1837,16 @@
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-6.8</v>
+        <v>-7.13</v>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M24" s="1" t="inlineStr">
@@ -1871,23 +1871,23 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>52.82</v>
+        <v>52.72</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.72</v>
+        <v>-0.19</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.87</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-4.1</v>
+        <v>-4.13</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-14.63</v>
+        <v>-14.19</v>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
@@ -1933,31 +1933,31 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>31.71</v>
+        <v>31.74</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-1.52</v>
+        <v>0.09</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>5.16</v>
+        <v>4.34</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-6.5</v>
+        <v>-5.34</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-26.46</v>
+        <v>-25.87</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
@@ -1987,23 +1987,23 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>10.38</v>
+        <v>92.88</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.84</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>1.69</v>
+        <v>0.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-1.81</v>
+        <v>-3.08</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-7.11</v>
+        <v>-6.04</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2011,16 +2011,16 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-8.68</v>
+        <v>-14.23</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M27" s="1" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
@@ -2045,23 +2045,23 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>93.67</v>
+        <v>10.35</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-1.84</v>
+        <v>-0.29</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.47</v>
+        <v>1.68</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-3.17</v>
+        <v>-0.24</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-7.23</v>
+        <v>-7.03</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-14.11</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M28" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="N28" s="1" t="inlineStr">
@@ -2345,53 +2345,53 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L2" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>23</v>
@@ -2400,56 +2400,56 @@
         <v>13</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W2" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA2" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F3" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>24</v>
@@ -2458,61 +2458,61 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L3" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>8</v>
@@ -2521,47 +2521,47 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C4" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>26</v>
@@ -2579,53 +2579,53 @@
         <v>5</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>22</v>
@@ -2649,22 +2649,22 @@
         <v>18</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T5" s="1" t="n">
         <v>21</v>
@@ -2673,50 +2673,50 @@
         <v>4</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="AA5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA5" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB5" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
@@ -2734,7 +2734,7 @@
         <v>16</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>14</v>
@@ -2743,68 +2743,68 @@
         <v>26</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S6" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X6" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y6" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z6" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
@@ -2813,25 +2813,25 @@
         <v>3</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
@@ -2840,31 +2840,31 @@
         <v>9</v>
       </c>
       <c r="S7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V7" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>10</v>
@@ -2873,26 +2873,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -2901,13 +2901,13 @@
         <v>3</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>18</v>
@@ -2916,10 +2916,10 @@
         <v>15</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
@@ -2934,25 +2934,25 @@
         <v>24</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>10</v>
@@ -2961,26 +2961,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
@@ -3001,13 +3001,13 @@
         <v>18</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>23</v>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>4</v>
@@ -3040,7 +3040,7 @@
         <v>7</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB9" s="1" t="n">
         <v>10</v>
@@ -3049,7 +3049,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -3059,16 +3059,16 @@
         <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2</v>
@@ -3086,22 +3086,22 @@
         <v>11</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N10" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O10" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>6</v>
@@ -3113,13 +3113,13 @@
         <v>8</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>5</v>
@@ -3128,71 +3128,71 @@
         <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P11" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q11" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T11" s="1" t="n">
         <v>24</v>
@@ -3204,13 +3204,13 @@
         <v>13</v>
       </c>
       <c r="W11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y11" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z11" s="1" t="n">
         <v>7</v>
@@ -3219,117 +3219,117 @@
         <v>23</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>20</v>
@@ -3338,7 +3338,7 @@
         <v>6</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>19</v>
@@ -3359,10 +3359,10 @@
         <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R13" s="1" t="n">
         <v>10</v>
@@ -3371,53 +3371,53 @@
         <v>2</v>
       </c>
       <c r="T13" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>20</v>
@@ -3426,25 +3426,25 @@
         <v>6</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
         <v>17</v>
@@ -3453,31 +3453,31 @@
         <v>22</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T14" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U14" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" s="1" t="n">
+      <c r="Y14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X14" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA14" s="1" t="n">
         <v>21</v>
@@ -3489,32 +3489,32 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>18</v>
@@ -3523,13 +3523,13 @@
         <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>24</v>
@@ -3541,28 +3541,28 @@
         <v>22</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z15" s="1" t="n">
         <v>5</v>
@@ -3571,68 +3571,68 @@
         <v>21</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E16" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" s="1" t="n">
         <v>26</v>
@@ -3641,7 +3641,7 @@
         <v>7</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>4</v>
@@ -3659,62 +3659,62 @@
         <v>21</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="R17" s="1" t="n">
         <v>3</v>
@@ -3723,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U17" s="1" t="n">
         <v>7</v>
@@ -3735,7 +3735,7 @@
         <v>4</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y17" s="1" t="n">
         <v>6</v>
@@ -3747,47 +3747,47 @@
         <v>21</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
@@ -3796,43 +3796,43 @@
         <v>17</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB18" s="1" t="n">
         <v>9</v>
@@ -3841,7 +3841,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -3851,10 +3851,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>18</v>
@@ -3863,19 +3863,19 @@
         <v>21</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
@@ -3887,122 +3887,122 @@
         <v>23</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X19" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA19" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z20" s="1" t="n">
         <v>4</v>
@@ -4017,41 +4017,41 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>19</v>
@@ -4066,7 +4066,7 @@
         <v>12</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>7</v>
@@ -4075,13 +4075,13 @@
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>3</v>
@@ -4090,7 +4090,7 @@
         <v>23</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z21" s="1" t="n">
         <v>4</v>
@@ -4105,190 +4105,190 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V22" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z22" s="1" t="n">
+      <c r="AA22" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB22" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA22" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB22" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U23" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>15</v>
@@ -4297,128 +4297,128 @@
         <v>25</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K24" s="1" t="n">
+      <c r="P24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L24" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N24" s="1" t="n">
+      <c r="Q24" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="O24" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P24" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="R24" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V24" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y24" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W24" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X24" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y24" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z24" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J25" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O25" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>10</v>
@@ -4430,77 +4430,77 @@
         <v>26</v>
       </c>
       <c r="U25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V25" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z25" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V25" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X25" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y25" s="1" t="n">
+      <c r="AA25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB25" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="Z25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA25" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB25" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N26" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O26" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>8</v>
@@ -4521,83 +4521,83 @@
         <v>7</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H27" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I27" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S27" s="1" t="n">
         <v>1</v>
@@ -4609,47 +4609,47 @@
         <v>7</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y27" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>22</v>
@@ -4658,43 +4658,43 @@
         <v>20</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U28" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R28" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T28" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U28" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V28" s="1" t="n">
         <v>15</v>
@@ -4703,25 +4703,25 @@
         <v>3</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
@@ -4731,37 +4731,37 @@
         <v>21</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J29" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L29" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>24</v>
@@ -4770,13 +4770,13 @@
         <v>2</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" s="1" t="n">
         <v>25</v>
@@ -4785,19 +4785,19 @@
         <v>6</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y29" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X29" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y29" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z29" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA29" s="1" t="n">
         <v>23</v>
@@ -4809,86 +4809,86 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C30" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F30" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J30" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M30" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="W30" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z30" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S30" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X30" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y30" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z30" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="AA30" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB30" s="1" t="n">
         <v>8</v>
@@ -4897,141 +4897,141 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="F31" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G31" s="1" t="n">
+      <c r="H31" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M31" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M31" s="1" t="n">
+      <c r="N31" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N31" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA31" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="1" t="n">
         <v>11</v>
@@ -5040,13 +5040,13 @@
         <v>7</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V32" s="1" t="n">
         <v>12</v>
@@ -5055,44 +5055,44 @@
         <v>8</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA32" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB32" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z32" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA32" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB32" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C33" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D33" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>5</v>
@@ -5101,110 +5101,110 @@
         <v>6</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R33" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R33" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V33" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K34" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N34" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P34" s="1" t="n">
         <v>2</v>
@@ -5213,34 +5213,34 @@
         <v>7</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V34" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y34" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W34" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X34" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y34" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z34" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB34" s="1" t="n">
         <v>10</v>
@@ -5249,11 +5249,11 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>26</v>
@@ -5268,13 +5268,13 @@
         <v>22</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>3</v>
@@ -5286,13 +5286,13 @@
         <v>18</v>
       </c>
       <c r="M35" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N35" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O35" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P35" s="1" t="n">
         <v>2</v>
@@ -5301,53 +5301,53 @@
         <v>7</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W35" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W35" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y35" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB35" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z35" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA35" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB35" s="1" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
@@ -5368,19 +5368,19 @@
         <v>3</v>
       </c>
       <c r="K36" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N36" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O36" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U36" s="1" t="n">
         <v>5</v>
@@ -5425,17 +5425,17 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
@@ -5444,7 +5444,7 @@
         <v>22</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4</v>
@@ -5453,37 +5453,37 @@
         <v>6</v>
       </c>
       <c r="J37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O37" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P37" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O37" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P37" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q37" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>5</v>
@@ -5492,47 +5492,47 @@
         <v>8</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z37" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA37" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA37" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB37" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C38" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D38" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
@@ -5541,155 +5541,155 @@
         <v>6</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L38" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N38" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M38" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O38" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P38" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U38" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z38" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P39" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S39" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W39" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W39" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X39" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z39" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -5699,16 +5699,16 @@
         <v>14</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>11</v>
@@ -5729,7 +5729,7 @@
         <v>12</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O40" s="1" t="n">
         <v>10</v>
@@ -5738,10 +5738,10 @@
         <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>2</v>
@@ -5750,7 +5750,7 @@
         <v>23</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V40" s="1" t="n">
         <v>9</v>
@@ -5759,13 +5759,13 @@
         <v>15</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y40" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA40" s="1" t="n">
         <v>26</v>
@@ -5777,26 +5777,26 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F41" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>11</v>
@@ -5817,7 +5817,7 @@
         <v>12</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>10</v>
@@ -5826,16 +5826,16 @@
         <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R41" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R41" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>8</v>
@@ -5844,28 +5844,28 @@
         <v>9</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X41" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z41" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -5875,7 +5875,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>27</v>
@@ -5896,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
@@ -5911,7 +5911,7 @@
         <v>10</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>6</v>
@@ -5920,10 +5920,10 @@
         <v>7</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>8</v>
@@ -5941,7 +5941,7 @@
         <v>16</v>
       </c>
       <c r="Z42" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA42" s="1" t="n">
         <v>25</v>
@@ -5953,26 +5953,26 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>4</v>
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
@@ -5993,28 +5993,28 @@
         <v>12</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R43" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U43" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T43" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U43" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V43" s="1" t="n">
         <v>9</v>
@@ -6023,16 +6023,16 @@
         <v>14</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB43" s="1" t="n">
         <v>15</v>
@@ -6041,11 +6041,11 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>25</v>
@@ -6054,13 +6054,13 @@
         <v>22</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>4</v>
@@ -6069,43 +6069,43 @@
         <v>5</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P44" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R44" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W44" s="1" t="n">
         <v>14</v>
@@ -6114,13 +6114,13 @@
         <v>21</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z44" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA44" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA44" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB44" s="1" t="n">
         <v>15</v>
@@ -6129,23 +6129,23 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>12</v>
@@ -6157,10 +6157,10 @@
         <v>5</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
@@ -6175,13 +6175,13 @@
         <v>9</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>1</v>
@@ -6190,7 +6190,7 @@
         <v>17</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V45" s="1" t="n">
         <v>10</v>
@@ -6199,16 +6199,16 @@
         <v>14</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y45" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z45" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA45" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>15</v>
@@ -6217,7 +6217,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -6227,7 +6227,7 @@
         <v>25</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>27</v>
@@ -6236,16 +6236,16 @@
         <v>20</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K46" s="1" t="n">
         <v>19</v>
@@ -6254,16 +6254,16 @@
         <v>11</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>6</v>
@@ -6278,7 +6278,7 @@
         <v>17</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V46" s="1" t="n">
         <v>10</v>
@@ -6287,7 +6287,7 @@
         <v>14</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y46" s="1" t="n">
         <v>18</v>
@@ -6305,26 +6305,26 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>2</v>
@@ -6336,28 +6336,28 @@
         <v>5</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P47" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q47" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R47" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R47" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>1</v>
@@ -6366,7 +6366,7 @@
         <v>17</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V47" s="1" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
         <v>14</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>18</v>
@@ -6384,7 +6384,7 @@
         <v>23</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>15</v>
@@ -6393,32 +6393,32 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" s="1" t="n">
         <v>5</v>
@@ -6433,65 +6433,65 @@
         <v>13</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O48" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R48" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U48" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S48" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T48" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U48" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V48" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z48" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA48" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB48" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>25</v>
@@ -6500,22 +6500,22 @@
         <v>14</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>13</v>
@@ -6524,28 +6524,28 @@
         <v>17</v>
       </c>
       <c r="O49" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R49" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P49" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R49" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U49" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V49" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>15</v>
@@ -6557,7 +6557,7 @@
         <v>19</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA49" s="1" t="n">
         <v>22</v>
@@ -6569,7 +6569,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -6579,31 +6579,31 @@
         <v>24</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F50" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I50" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J50" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K50" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>13</v>
@@ -6612,7 +6612,7 @@
         <v>17</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P50" s="1" t="n">
         <v>5</v>
@@ -6621,16 +6621,16 @@
         <v>6</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V50" s="1" t="n">
         <v>9</v>
@@ -6642,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z50" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA50" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA50" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>16</v>
@@ -6657,41 +6657,41 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D51" s="1" t="n">
+      <c r="E51" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G51" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I51" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L51" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>13</v>
@@ -6700,25 +6700,25 @@
         <v>17</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V51" s="1" t="n">
         <v>9</v>
@@ -6730,10 +6730,10 @@
         <v>26</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>25</v>
@@ -6745,23 +6745,23 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>11</v>
@@ -6785,7 +6785,7 @@
         <v>13</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>8</v>
@@ -6803,16 +6803,16 @@
         <v>1</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U52" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V52" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V52" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W52" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X52" s="1" t="n">
         <v>26</v>
@@ -6821,19 +6821,19 @@
         <v>20</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -6843,7 +6843,7 @@
         <v>24</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>21</v>
@@ -6861,7 +6861,7 @@
         <v>5</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" s="1" t="n">
         <v>19</v>
@@ -6876,19 +6876,19 @@
         <v>16</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T53" s="1" t="n">
         <v>17</v>
@@ -6909,7 +6909,7 @@
         <v>20</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>25</v>
@@ -6921,7 +6921,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -6931,43 +6931,43 @@
         <v>24</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K54" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>6</v>
@@ -6976,19 +6976,19 @@
         <v>8</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X54" s="1" t="n">
         <v>26</v>
@@ -6997,19 +6997,19 @@
         <v>20</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -7019,16 +7019,16 @@
         <v>24</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E55" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F55" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G55" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>3</v>
@@ -7040,10 +7040,10 @@
         <v>5</v>
       </c>
       <c r="K55" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L55" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>13</v>
@@ -7055,25 +7055,25 @@
         <v>10</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U55" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V55" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V55" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W55" s="1" t="n">
         <v>15</v>
@@ -7082,10 +7082,10 @@
         <v>26</v>
       </c>
       <c r="Y55" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z55" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z55" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
@@ -7097,23 +7097,23 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E56" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D56" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F56" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>18</v>
@@ -7125,46 +7125,46 @@
         <v>4</v>
       </c>
       <c r="J56" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M56" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M56" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N56" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>26</v>
@@ -7173,35 +7173,35 @@
         <v>21</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>18</v>
@@ -7213,31 +7213,31 @@
         <v>4</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N57" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
@@ -7246,98 +7246,98 @@
         <v>20</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X57" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D58" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D58" s="1" t="n">
+      <c r="E58" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U58" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V58" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V58" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>14</v>
@@ -7346,7 +7346,7 @@
         <v>26</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>21</v>
@@ -7361,17 +7361,17 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D59" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>22</v>
@@ -7380,31 +7380,31 @@
         <v>19</v>
       </c>
       <c r="G59" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M59" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N59" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H59" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J59" s="1" t="n">
+      <c r="O59" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L59" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M59" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N59" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O59" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P59" s="1" t="n">
         <v>1</v>
@@ -7413,56 +7413,56 @@
         <v>5</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X59" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z59" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z59" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>19</v>
@@ -7471,7 +7471,7 @@
         <v>18</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>8</v>
@@ -7480,13 +7480,13 @@
         <v>3</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L60" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>14</v>
@@ -7501,7 +7501,7 @@
         <v>5</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
@@ -7510,10 +7510,10 @@
         <v>12</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>15</v>
@@ -7522,13 +7522,13 @@
         <v>26</v>
       </c>
       <c r="Y60" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z60" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA60" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Z60" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA60" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB60" s="1" t="n">
         <v>16</v>
@@ -7537,7 +7537,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -7550,16 +7550,16 @@
         <v>23</v>
       </c>
       <c r="E61" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>18</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>8</v>
@@ -7574,7 +7574,7 @@
         <v>17</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N61" s="1" t="n">
         <v>14</v>
@@ -7589,7 +7589,7 @@
         <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
@@ -7598,7 +7598,7 @@
         <v>12</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V61" s="1" t="n">
         <v>9</v>
@@ -7625,17 +7625,17 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D62" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>19</v>
@@ -7647,7 +7647,7 @@
         <v>18</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>8</v>
@@ -7662,7 +7662,7 @@
         <v>17</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>14</v>
@@ -7677,16 +7677,16 @@
         <v>5</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V62" s="1" t="n">
         <v>9</v>
@@ -7698,13 +7698,13 @@
         <v>26</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AA62" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB62" s="1" t="n">
         <v>16</v>
@@ -7713,29 +7713,29 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>20</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>8</v>
@@ -7744,16 +7744,16 @@
         <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M63" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>4</v>
@@ -7765,7 +7765,7 @@
         <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
@@ -7780,7 +7780,7 @@
         <v>9</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X63" s="1" t="n">
         <v>26</v>
@@ -7789,41 +7789,41 @@
         <v>24</v>
       </c>
       <c r="Z63" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA63" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E64" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F64" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="H64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>8</v>
@@ -7832,16 +7832,16 @@
         <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
@@ -7853,83 +7853,83 @@
         <v>5</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V64" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X64" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y64" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z64" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E65" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E65" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F65" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H65" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O65" s="1" t="n">
         <v>4</v>
@@ -7938,25 +7938,25 @@
         <v>1</v>
       </c>
       <c r="Q65" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R65" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R65" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V65" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X65" s="1" t="n">
         <v>26</v>
@@ -7965,19 +7965,19 @@
         <v>25</v>
       </c>
       <c r="Z65" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA65" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA65" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB65" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
@@ -7999,10 +7999,10 @@
         <v>13</v>
       </c>
       <c r="H66" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>3</v>
@@ -8026,10 +8026,10 @@
         <v>1</v>
       </c>
       <c r="Q66" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R66" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="R66" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>2</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>88.56999999999999</v>
+        <v>88.28</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-1.86</v>
+        <v>-0.33</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>-1.17</v>
+        <v>-1.85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>8.539999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>11.52</v>
+        <v>12.07</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>-10.11</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>26.32</v>
+        <v>26.28</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-0.72</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-0.57</v>
+        <v>1.42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2.97</v>
+        <v>3.43</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>10.6</v>
+        <v>11.53</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>-0.57</v>
+        <v>-0.42</v>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>16.73</v>
+        <v>16.68</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-0.59</v>
+        <v>-0.3</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>-0.34</v>
+        <v>1.6</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>9.460000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" s="1" t="inlineStr">
@@ -711,23 +711,23 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>30.15</v>
+        <v>30.18</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-1.57</v>
+        <v>0.1</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.32</v>
+        <v>1.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>6.31</v>
+        <v>6.7</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -769,23 +769,23 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>+12</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>283.7</v>
+        <v>281.18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.67</v>
+        <v>-0.89</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3.87</v>
+        <v>2.47</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>5.02</v>
+        <v>2.3</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>5.94</v>
+        <v>4.91</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>-1.71</v>
+        <v>-2.29</v>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -827,31 +827,31 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>52.96</v>
+        <v>102.55</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-1.3</v>
+        <v>-0.3</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>-1.33</v>
+        <v>1.99</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-2.79</v>
+        <v>0.43</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v/>
+        <v>4.13</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -885,57 +885,57 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>31.56</v>
+        <v>52.81</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>2.09</v>
+        <v>-0.75</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>2.54</v>
+        <v>-2.59</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>5.75</v>
+        <v/>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -943,23 +943,23 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>13.12</v>
+        <v>31.64</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-0.68</v>
+        <v>0.25</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>-1.68</v>
+        <v>2.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>5.79</v>
+        <v>0.97</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4.25</v>
+        <v>5.61</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
@@ -1001,23 +1001,23 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>77.23</v>
+        <v>77.3</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-1.13</v>
+        <v>0.09</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>-1.45</v>
+        <v>-0.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-2.33</v>
+        <v>-2.38</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-17.44</v>
+        <v>-17.12</v>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -1059,23 +1059,23 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>102.86</v>
+        <v>12.97</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.41</v>
+        <v>-1.14</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>2.03</v>
+        <v>-1.72</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-0.51</v>
+        <v>5.26</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>-2.7</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -1102,14 +1102,14 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -1117,23 +1117,23 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>130.97</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2.12</v>
+        <v>0.38</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>3.19</v>
+        <v>4.97</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1141,26 +1141,26 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-5.75</v>
+        <v>-13.11</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1175,23 +1175,23 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>162.06</v>
+        <v>161.52</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>1.15</v>
+        <v>1.69</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>1.18</v>
+        <v>0.61</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-1.15</v>
+        <v>-1.18</v>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>33.41</v>
+        <v>130.19</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.85</v>
+        <v>1.88</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-2.04</v>
+        <v>-6.03</v>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1291,31 +1291,31 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>27.83</v>
+        <v>27.86</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.82</v>
+        <v>0.11</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-1.49</v>
+        <v>-2.33</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-2.93</v>
+        <v>-2.38</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-4.48</v>
+        <v>-4.09</v>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
@@ -1349,23 +1349,23 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>83.56999999999999</v>
+        <v>587.76</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.64</v>
+        <v>0.18</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>-0.22</v>
+        <v>-1.04</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>3.65</v>
+        <v>-1.5</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.98</v>
+        <v>0.04</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-13.86</v>
+        <v>-5.19</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M16" s="1" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
@@ -1411,19 +1411,19 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>586.72</v>
+        <v>33.37</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.93</v>
+        <v>-0.12</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.67</v>
+        <v>1.79</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-1.97</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>-5.64</v>
+        <v>-1.86</v>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
@@ -1450,14 +1450,14 @@
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
@@ -1465,57 +1465,57 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>32.04</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>-0.93</v>
+        <v>0.82</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-0.12</v>
+        <v>6.32</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-2.54</v>
+        <v>-25.03</v>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M18" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
@@ -1523,23 +1523,23 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>95.59</v>
+        <v>32.01</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-0.68</v>
+        <v>-0.09</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.88</v>
+        <v>0.22</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-1.35</v>
+        <v>0.15</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.98</v>
+        <v>-0.44</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-2.94</v>
+        <v>-2.34</v>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1581,23 +1581,23 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>30.78</v>
+        <v>30.57</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.55</v>
+        <v>-0.68</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>-0.3</v>
+        <v>-1.22</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-1.23</v>
+        <v>-1.3</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -1639,23 +1639,23 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>12.57</v>
+        <v>94.89</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>1.17</v>
+        <v>0.12</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-0.17</v>
+        <v>-1.68</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-2.76</v>
+        <v>-1.41</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-9.84</v>
+        <v>-3.36</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>11.28</v>
+        <v>11.24</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.88</v>
+        <v>-0.35</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-0.43</v>
+        <v>0.34</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-3.07</v>
+        <v>-3.47</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.51</v>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1755,23 +1755,23 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>39.08</v>
+        <v>12.5</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.29</v>
+        <v>1.85</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-1.59</v>
+        <v>1.04</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-3.28</v>
+        <v>-3.73</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0</v>
+        <v>-10.07</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -1798,14 +1798,14 @@
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1813,23 +1813,23 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>99.92</v>
+        <v>39.06</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-1.05</v>
+        <v>-0.05</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-0.76</v>
+        <v>-0.98</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-4.09</v>
+        <v>-3.84</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-7.13</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1871,23 +1871,23 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>52.72</v>
+        <v>52.69</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.19</v>
+        <v>-0.06</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.87</v>
+        <v>0.44</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-4.13</v>
+        <v>-4.56</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-14.19</v>
+        <v>-13.98</v>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
@@ -1929,50 +1929,50 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>31.74</v>
+        <v>99.62</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.09</v>
+        <v>-0.3</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.68</v>
+        <v>1.46</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>4.34</v>
+        <v>-0.02</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-5.34</v>
+        <v>-4.76</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-25.87</v>
+        <v>-7.13</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M26" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>92.88</v>
+        <v>93.42</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.84</v>
+        <v>0.58</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.7</v>
+        <v>1.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-3.08</v>
+        <v>-2.29</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-6.04</v>
+        <v>-6.22</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-14.23</v>
+        <v>-13.47</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2049,19 +2049,19 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.29</v>
+        <v>-0.19</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.97</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-7.03</v>
+        <v>-7.41</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M28" s="1" t="inlineStr">
@@ -2345,14 +2345,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>14</v>
@@ -2373,34 +2373,34 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>21</v>
@@ -2412,13 +2412,13 @@
         <v>12</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z2" s="1" t="n">
         <v>9</v>
@@ -2427,59 +2427,59 @@
         <v>19</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L3" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>23</v>
@@ -2488,56 +2488,56 @@
         <v>13</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA3" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F4" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>24</v>
@@ -2546,61 +2546,61 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L4" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z4" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>8</v>
@@ -2609,47 +2609,47 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>26</v>
@@ -2667,53 +2667,53 @@
         <v>5</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z5" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>22</v>
@@ -2737,22 +2737,22 @@
         <v>18</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T6" s="1" t="n">
         <v>21</v>
@@ -2761,50 +2761,50 @@
         <v>4</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="AA6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB6" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA6" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB6" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>2</v>
@@ -2822,7 +2822,7 @@
         <v>16</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>14</v>
@@ -2831,68 +2831,68 @@
         <v>26</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S7" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V7" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X7" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y7" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z7" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -2901,25 +2901,25 @@
         <v>3</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
@@ -2928,31 +2928,31 @@
         <v>9</v>
       </c>
       <c r="S8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V8" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>10</v>
@@ -2961,26 +2961,26 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
@@ -2989,13 +2989,13 @@
         <v>3</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>18</v>
@@ -3004,10 +3004,10 @@
         <v>15</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>23</v>
@@ -3022,25 +3022,25 @@
         <v>24</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB9" s="1" t="n">
         <v>10</v>
@@ -3049,26 +3049,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F10" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2</v>
@@ -3089,13 +3089,13 @@
         <v>18</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>23</v>
@@ -3113,7 +3113,7 @@
         <v>8</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>4</v>
@@ -3128,7 +3128,7 @@
         <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>10</v>
@@ -3137,7 +3137,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -3147,16 +3147,16 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2</v>
@@ -3174,22 +3174,22 @@
         <v>11</v>
       </c>
       <c r="M11" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N11" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O11" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>6</v>
@@ -3201,13 +3201,13 @@
         <v>8</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>5</v>
@@ -3216,71 +3216,71 @@
         <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O12" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q12" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>24</v>
@@ -3292,13 +3292,13 @@
         <v>13</v>
       </c>
       <c r="W12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y12" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X12" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y12" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z12" s="1" t="n">
         <v>7</v>
@@ -3307,117 +3307,117 @@
         <v>23</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>20</v>
@@ -3426,7 +3426,7 @@
         <v>6</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>19</v>
@@ -3447,10 +3447,10 @@
         <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>10</v>
@@ -3459,53 +3459,53 @@
         <v>2</v>
       </c>
       <c r="T14" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V14" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>20</v>
@@ -3514,25 +3514,25 @@
         <v>6</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
         <v>17</v>
@@ -3541,31 +3541,31 @@
         <v>22</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T15" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W15" s="1" t="n">
+      <c r="Y15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X15" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y15" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z15" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA15" s="1" t="n">
         <v>21</v>
@@ -3577,32 +3577,32 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>18</v>
@@ -3611,13 +3611,13 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>24</v>
@@ -3629,28 +3629,28 @@
         <v>22</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z16" s="1" t="n">
         <v>5</v>
@@ -3659,68 +3659,68 @@
         <v>21</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E17" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" s="1" t="n">
         <v>26</v>
@@ -3729,7 +3729,7 @@
         <v>7</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>4</v>
@@ -3747,62 +3747,62 @@
         <v>21</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O18" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P18" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>3</v>
@@ -3811,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U18" s="1" t="n">
         <v>7</v>
@@ -3823,7 +3823,7 @@
         <v>4</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y18" s="1" t="n">
         <v>6</v>
@@ -3835,47 +3835,47 @@
         <v>21</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
@@ -3884,43 +3884,43 @@
         <v>17</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z19" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB19" s="1" t="n">
         <v>9</v>
@@ -3929,7 +3929,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
@@ -3939,10 +3939,10 @@
         <v>16</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>18</v>
@@ -3951,19 +3951,19 @@
         <v>21</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
@@ -3975,122 +3975,122 @@
         <v>23</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z21" s="1" t="n">
         <v>4</v>
@@ -4105,41 +4105,41 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>19</v>
@@ -4154,7 +4154,7 @@
         <v>12</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>7</v>
@@ -4163,13 +4163,13 @@
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>3</v>
@@ -4178,7 +4178,7 @@
         <v>23</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z22" s="1" t="n">
         <v>4</v>
@@ -4193,190 +4193,190 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V23" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y23" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z23" s="1" t="n">
+      <c r="AA23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB23" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA23" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB23" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z24" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB24" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>15</v>
@@ -4385,128 +4385,128 @@
         <v>25</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" s="1" t="n">
+      <c r="P25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N25" s="1" t="n">
+      <c r="Q25" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="O25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P25" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="R25" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V25" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y25" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W25" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X25" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y25" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z25" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J26" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N26" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>10</v>
@@ -4518,77 +4518,77 @@
         <v>26</v>
       </c>
       <c r="U26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="V26" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X26" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y26" s="1" t="n">
+      <c r="AA26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB26" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="Z26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB26" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N27" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O27" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>8</v>
@@ -4609,83 +4609,83 @@
         <v>7</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y27" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H28" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I28" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J28" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>1</v>
@@ -4697,47 +4697,47 @@
         <v>7</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y28" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>22</v>
@@ -4746,43 +4746,43 @@
         <v>20</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U29" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T29" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V29" s="1" t="n">
         <v>15</v>
@@ -4791,25 +4791,25 @@
         <v>3</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA29" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
@@ -4819,37 +4819,37 @@
         <v>21</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J30" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L30" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M30" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>24</v>
@@ -4858,13 +4858,13 @@
         <v>2</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>25</v>
@@ -4873,19 +4873,19 @@
         <v>6</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y30" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X30" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y30" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z30" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA30" s="1" t="n">
         <v>23</v>
@@ -4897,86 +4897,86 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F31" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J31" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M31" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N31" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V31" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R31" s="1" t="n">
+      <c r="W31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z31" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S31" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X31" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y31" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z31" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="AA31" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB31" s="1" t="n">
         <v>8</v>
@@ -4985,141 +4985,141 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="F32" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G32" s="1" t="n">
+      <c r="H32" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M32" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K32" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M32" s="1" t="n">
+      <c r="N32" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N32" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA32" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="1" t="n">
         <v>11</v>
@@ -5128,13 +5128,13 @@
         <v>7</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V33" s="1" t="n">
         <v>12</v>
@@ -5143,44 +5143,44 @@
         <v>8</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA33" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB33" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z33" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA33" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB33" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>5</v>
@@ -5189,110 +5189,110 @@
         <v>6</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P34" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R34" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R34" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V34" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA34" s="1" t="n">
         <v>26</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K35" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M35" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O35" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P35" s="1" t="n">
         <v>2</v>
@@ -5301,34 +5301,34 @@
         <v>7</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V35" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W35" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X35" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y35" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z35" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB35" s="1" t="n">
         <v>10</v>
@@ -5337,11 +5337,11 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>26</v>
@@ -5356,13 +5356,13 @@
         <v>22</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>3</v>
@@ -5374,13 +5374,13 @@
         <v>18</v>
       </c>
       <c r="M36" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N36" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O36" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>2</v>
@@ -5389,53 +5389,53 @@
         <v>7</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W36" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W36" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y36" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA36" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB36" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z36" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA36" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB36" s="1" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
@@ -5456,19 +5456,19 @@
         <v>3</v>
       </c>
       <c r="K37" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O37" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>2</v>
@@ -5483,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>5</v>
@@ -5513,17 +5513,17 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
@@ -5532,7 +5532,7 @@
         <v>22</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
@@ -5541,37 +5541,37 @@
         <v>6</v>
       </c>
       <c r="J38" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O38" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P38" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K38" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O38" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P38" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q38" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U38" s="1" t="n">
         <v>5</v>
@@ -5580,47 +5580,47 @@
         <v>8</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z38" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA38" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA38" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB38" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C39" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F39" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G39" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
@@ -5629,155 +5629,155 @@
         <v>6</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L39" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N39" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N39" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O39" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P39" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z39" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P40" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V40" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W40" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W40" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X40" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z40" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -5787,16 +5787,16 @@
         <v>14</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L41" s="1" t="n">
         <v>11</v>
@@ -5817,7 +5817,7 @@
         <v>12</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O41" s="1" t="n">
         <v>10</v>
@@ -5826,10 +5826,10 @@
         <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>2</v>
@@ -5838,7 +5838,7 @@
         <v>23</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V41" s="1" t="n">
         <v>9</v>
@@ -5847,13 +5847,13 @@
         <v>15</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y41" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA41" s="1" t="n">
         <v>26</v>
@@ -5865,26 +5865,26 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F42" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4</v>
@@ -5896,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
@@ -5905,7 +5905,7 @@
         <v>12</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>10</v>
@@ -5914,16 +5914,16 @@
         <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R42" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R42" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>8</v>
@@ -5932,28 +5932,28 @@
         <v>9</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X42" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z42" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB42" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -5963,7 +5963,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>27</v>
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
@@ -5999,7 +5999,7 @@
         <v>10</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>6</v>
@@ -6008,10 +6008,10 @@
         <v>7</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>8</v>
@@ -6029,7 +6029,7 @@
         <v>16</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA43" s="1" t="n">
         <v>25</v>
@@ -6041,26 +6041,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>4</v>
@@ -6072,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
@@ -6081,28 +6081,28 @@
         <v>12</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R44" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U44" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U44" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V44" s="1" t="n">
         <v>9</v>
@@ -6111,16 +6111,16 @@
         <v>14</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z44" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB44" s="1" t="n">
         <v>15</v>
@@ -6129,11 +6129,11 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>25</v>
@@ -6142,13 +6142,13 @@
         <v>22</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>4</v>
@@ -6157,43 +6157,43 @@
         <v>5</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P45" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R45" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W45" s="1" t="n">
         <v>14</v>
@@ -6202,13 +6202,13 @@
         <v>21</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z45" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA45" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>15</v>
@@ -6217,23 +6217,23 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>12</v>
@@ -6245,10 +6245,10 @@
         <v>5</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>11</v>
@@ -6263,13 +6263,13 @@
         <v>9</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S46" s="1" t="n">
         <v>1</v>
@@ -6278,7 +6278,7 @@
         <v>17</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V46" s="1" t="n">
         <v>10</v>
@@ -6287,16 +6287,16 @@
         <v>14</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y46" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z46" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA46" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA46" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>15</v>
@@ -6305,7 +6305,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
@@ -6315,7 +6315,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>27</v>
@@ -6324,16 +6324,16 @@
         <v>20</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K47" s="1" t="n">
         <v>19</v>
@@ -6342,16 +6342,16 @@
         <v>11</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>6</v>
@@ -6366,7 +6366,7 @@
         <v>17</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V47" s="1" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
         <v>14</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>18</v>
@@ -6393,26 +6393,26 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>2</v>
@@ -6424,28 +6424,28 @@
         <v>5</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L48" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q48" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R48" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R48" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>1</v>
@@ -6454,7 +6454,7 @@
         <v>17</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V48" s="1" t="n">
         <v>10</v>
@@ -6463,7 +6463,7 @@
         <v>14</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y48" s="1" t="n">
         <v>18</v>
@@ -6472,7 +6472,7 @@
         <v>23</v>
       </c>
       <c r="AA48" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>15</v>
@@ -6481,32 +6481,32 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>5</v>
@@ -6521,65 +6521,65 @@
         <v>13</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O49" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R49" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U49" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S49" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T49" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U49" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y49" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z49" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA49" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>25</v>
@@ -6588,22 +6588,22 @@
         <v>14</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M50" s="1" t="n">
         <v>13</v>
@@ -6612,28 +6612,28 @@
         <v>17</v>
       </c>
       <c r="O50" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q50" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R50" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R50" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S50" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U50" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V50" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V50" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W50" s="1" t="n">
         <v>15</v>
@@ -6645,7 +6645,7 @@
         <v>19</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>22</v>
@@ -6657,7 +6657,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -6667,31 +6667,31 @@
         <v>24</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J51" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K51" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>13</v>
@@ -6700,7 +6700,7 @@
         <v>17</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P51" s="1" t="n">
         <v>5</v>
@@ -6709,16 +6709,16 @@
         <v>6</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V51" s="1" t="n">
         <v>9</v>
@@ -6730,13 +6730,13 @@
         <v>26</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z51" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA51" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA51" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB51" s="1" t="n">
         <v>16</v>
@@ -6745,41 +6745,41 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D52" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="E52" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>13</v>
@@ -6788,25 +6788,25 @@
         <v>17</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V52" s="1" t="n">
         <v>9</v>
@@ -6818,10 +6818,10 @@
         <v>26</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>25</v>
@@ -6833,23 +6833,23 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>11</v>
@@ -6873,7 +6873,7 @@
         <v>13</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O53" s="1" t="n">
         <v>8</v>
@@ -6891,16 +6891,16 @@
         <v>1</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U53" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V53" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V53" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W53" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X53" s="1" t="n">
         <v>26</v>
@@ -6909,19 +6909,19 @@
         <v>20</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB53" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -6931,7 +6931,7 @@
         <v>24</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>21</v>
@@ -6949,7 +6949,7 @@
         <v>5</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" s="1" t="n">
         <v>19</v>
@@ -6964,19 +6964,19 @@
         <v>16</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T54" s="1" t="n">
         <v>17</v>
@@ -6997,7 +6997,7 @@
         <v>20</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
@@ -7009,7 +7009,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -7019,43 +7019,43 @@
         <v>24</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H55" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K55" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L55" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>6</v>
@@ -7064,19 +7064,19 @@
         <v>8</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X55" s="1" t="n">
         <v>26</v>
@@ -7085,19 +7085,19 @@
         <v>20</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -7107,16 +7107,16 @@
         <v>24</v>
       </c>
       <c r="D56" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E56" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F56" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>3</v>
@@ -7128,10 +7128,10 @@
         <v>5</v>
       </c>
       <c r="K56" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L56" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>13</v>
@@ -7143,25 +7143,25 @@
         <v>10</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U56" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W56" s="1" t="n">
         <v>15</v>
@@ -7170,10 +7170,10 @@
         <v>26</v>
       </c>
       <c r="Y56" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z56" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z56" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
@@ -7185,23 +7185,23 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D57" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F57" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>18</v>
@@ -7213,46 +7213,46 @@
         <v>4</v>
       </c>
       <c r="J57" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L57" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M57" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K57" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L57" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M57" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N57" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X57" s="1" t="n">
         <v>26</v>
@@ -7261,35 +7261,35 @@
         <v>21</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>18</v>
@@ -7301,31 +7301,31 @@
         <v>4</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K58" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N58" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
@@ -7334,98 +7334,98 @@
         <v>20</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D59" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D59" s="1" t="n">
+      <c r="E59" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U59" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V59" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V59" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>14</v>
@@ -7434,7 +7434,7 @@
         <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>21</v>
@@ -7449,17 +7449,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>22</v>
@@ -7468,31 +7468,31 @@
         <v>19</v>
       </c>
       <c r="G60" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L60" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M60" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N60" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H60" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I60" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" s="1" t="n">
+      <c r="O60" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K60" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L60" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M60" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N60" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O60" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>1</v>
@@ -7501,56 +7501,56 @@
         <v>5</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y60" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z60" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z60" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>19</v>
@@ -7559,7 +7559,7 @@
         <v>18</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>8</v>
@@ -7568,13 +7568,13 @@
         <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L61" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N61" s="1" t="n">
         <v>14</v>
@@ -7589,7 +7589,7 @@
         <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
@@ -7598,10 +7598,10 @@
         <v>12</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>15</v>
@@ -7610,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z61" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA61" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Z61" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA61" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB61" s="1" t="n">
         <v>16</v>
@@ -7625,7 +7625,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
@@ -7638,16 +7638,16 @@
         <v>23</v>
       </c>
       <c r="E62" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="F62" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>18</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>8</v>
@@ -7662,7 +7662,7 @@
         <v>17</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>14</v>
@@ -7677,7 +7677,7 @@
         <v>5</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
@@ -7686,7 +7686,7 @@
         <v>12</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V62" s="1" t="n">
         <v>9</v>
@@ -7713,17 +7713,17 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D63" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>19</v>
@@ -7735,7 +7735,7 @@
         <v>18</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>8</v>
@@ -7750,7 +7750,7 @@
         <v>17</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N63" s="1" t="n">
         <v>14</v>
@@ -7765,16 +7765,16 @@
         <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>9</v>
@@ -7786,13 +7786,13 @@
         <v>26</v>
       </c>
       <c r="Y63" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z63" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB63" s="1" t="n">
         <v>16</v>
@@ -7801,29 +7801,29 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>20</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>8</v>
@@ -7832,16 +7832,16 @@
         <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M64" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
@@ -7853,7 +7853,7 @@
         <v>5</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
@@ -7868,7 +7868,7 @@
         <v>9</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X64" s="1" t="n">
         <v>26</v>
@@ -7877,41 +7877,41 @@
         <v>24</v>
       </c>
       <c r="Z64" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA64" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>22</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="H65" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>8</v>
@@ -7920,16 +7920,16 @@
         <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="O65" s="1" t="n">
         <v>4</v>
@@ -7941,83 +7941,83 @@
         <v>5</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V65" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X65" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y65" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z65" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA65" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB65" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E66" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H66" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>4</v>
@@ -8026,25 +8026,25 @@
         <v>1</v>
       </c>
       <c r="Q66" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R66" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R66" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U66" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V66" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="X66" s="1" t="n">
         <v>26</v>
@@ -8053,13 +8053,13 @@
         <v>25</v>
       </c>
       <c r="Z66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA66" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="AA66" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB66" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0;-0;0"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,9 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -435,23 +440,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,60 +475,75 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>1-Week Rank Delta</t>
+          <t>5D Rank Velocity</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>10D Rank Velocity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>20D Rank Velocity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>65D Rank Velocity</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>% Chg</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>5D RS %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>21D RS %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>65D RS %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RS Trend (&gt;50 SMA)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>% Off RS High</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>&gt; 10 EMA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>&gt; 20 EMA</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>&gt; 50 SMA</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>&gt; 200 SMA</t>
         </is>
@@ -535,50 +558,57 @@
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>88.28</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>-0.33</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>-1.85</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>8.1</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>12.07</v>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>-9.470000000000001</v>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -593,50 +623,57 @@
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>26.28</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="H3" s="1" t="n">
         <v>-0.15</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="I3" s="1" t="n">
         <v>1.42</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>3.43</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <v>11.53</v>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>-0.42</v>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -651,50 +688,57 @@
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>16.68</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>2.6</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>9.529999999999999</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>-0.34</v>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -709,50 +753,57 @@
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>30.18</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>2.64</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>6.7</v>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="O5" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="P5" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="Q5" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -767,50 +818,57 @@
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>281.18</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>-0.89</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>2.47</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>2.3</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>4.91</v>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>-2.29</v>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="O6" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
+      <c r="P6" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N6" s="1" t="inlineStr">
+      <c r="Q6" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -825,50 +883,57 @@
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>102.55</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>1.99</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.43</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>4.13</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>-2.7</v>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="O7" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="P7" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="Q7" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -883,50 +948,57 @@
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>52.81</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>-0.28</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>-0.75</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>-2.59</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v/>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="O8" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M8" s="1" t="inlineStr">
+      <c r="P8" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N8" s="1" t="inlineStr">
+      <c r="Q8" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -941,50 +1013,57 @@
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>31.64</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>5.61</v>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="L9" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>-0.06</v>
       </c>
-      <c r="K9" s="1" t="inlineStr">
+      <c r="N9" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="O9" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M9" s="1" t="inlineStr">
+      <c r="P9" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N9" s="1" t="inlineStr">
+      <c r="Q9" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -999,50 +1078,57 @@
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>77.3</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>-0.76</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>-2.38</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>4.03</v>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="M10" s="1" t="n">
         <v>-17.12</v>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="O10" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M10" s="1" t="inlineStr">
+      <c r="P10" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
+      <c r="Q10" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1057,50 +1143,57 @@
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="C11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>12.97</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="H11" s="1" t="n">
         <v>-1.14</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="I11" s="1" t="n">
         <v>-1.72</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="J11" s="1" t="n">
         <v>5.26</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <v>3.24</v>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
+      <c r="Q11" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1115,50 +1208,57 @@
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="C12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>84.04000000000001</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="H12" s="1" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>0.38</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="J12" s="1" t="n">
         <v>4.97</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <v>2.82</v>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="M12" s="1" t="n">
         <v>-13.11</v>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
+      <c r="P12" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="Q12" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1173,50 +1273,57 @@
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>161.52</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="H13" s="1" t="n">
         <v>-0.33</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>1.69</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>0.61</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>2.04</v>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="M13" s="1" t="n">
         <v>-1.18</v>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1231,50 +1338,57 @@
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>130.19</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="H14" s="1" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="I14" s="1" t="n">
         <v>1.88</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="J14" s="1" t="n">
         <v>1.84</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <v>1.73</v>
       </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="M14" s="1" t="n">
         <v>-6.03</v>
       </c>
-      <c r="K14" s="1" t="inlineStr">
+      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L14" s="1" t="inlineStr">
+      <c r="O14" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="P14" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="Q14" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1289,50 +1403,57 @@
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="C15" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>27.86</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="H15" s="1" t="n">
         <v>0.11</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>-2.33</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="J15" s="1" t="n">
         <v>-2.38</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <v>1.34</v>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="M15" s="1" t="n">
         <v>-4.09</v>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1347,50 +1468,57 @@
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="C16" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>587.76</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="I16" s="1" t="n">
         <v>-1.04</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="J16" s="1" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="M16" s="1" t="n">
         <v>-5.19</v>
       </c>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="N16" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L16" s="1" t="inlineStr">
+      <c r="O16" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="P16" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
+      <c r="Q16" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1405,50 +1533,57 @@
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="C17" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>33.37</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="H17" s="1" t="n">
         <v>-0.12</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="I17" s="1" t="n">
         <v>1.79</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="J17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="K17" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="M17" s="1" t="n">
         <v>-1.86</v>
       </c>
-      <c r="K17" s="1" t="inlineStr">
+      <c r="N17" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
+      <c r="O17" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="P17" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
+      <c r="Q17" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1463,50 +1598,57 @@
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>+10</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="C18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="H18" s="1" t="n">
         <v>0.82</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>0.46</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="J18" s="1" t="n">
         <v>6.32</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>-0.25</v>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>-25.03</v>
       </c>
-      <c r="K18" s="1" t="inlineStr">
+      <c r="N18" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
+      <c r="O18" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M18" s="1" t="inlineStr">
+      <c r="P18" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
+      <c r="Q18" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1521,50 +1663,57 @@
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="C19" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>32.01</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="H19" s="1" t="n">
         <v>-0.09</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="I19" s="1" t="n">
         <v>0.22</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="J19" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="K19" s="1" t="n">
         <v>-0.44</v>
       </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="M19" s="1" t="n">
         <v>-2.34</v>
       </c>
-      <c r="K19" s="1" t="inlineStr">
+      <c r="N19" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L19" s="1" t="inlineStr">
+      <c r="O19" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M19" s="1" t="inlineStr">
+      <c r="P19" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N19" s="1" t="inlineStr">
+      <c r="Q19" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1579,50 +1728,57 @@
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="C20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>30.57</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="H20" s="1" t="n">
         <v>-0.68</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="I20" s="1" t="n">
         <v>-1.22</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="J20" s="1" t="n">
         <v>0.64</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <v>-1.3</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="M20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="N20" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="P20" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N20" s="1" t="inlineStr">
+      <c r="Q20" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1637,50 +1793,57 @@
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="C21" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>94.89</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="H21" s="1" t="n">
         <v>-0.73</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="I21" s="1" t="n">
         <v>0.12</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="J21" s="1" t="n">
         <v>-1.68</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="K21" s="1" t="n">
         <v>-1.41</v>
       </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="M21" s="1" t="n">
         <v>-3.36</v>
       </c>
-      <c r="K21" s="1" t="inlineStr">
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L21" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M21" s="1" t="inlineStr">
+      <c r="P21" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N21" s="1" t="inlineStr">
+      <c r="Q21" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1695,50 +1858,57 @@
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>11.24</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="H22" s="1" t="n">
         <v>-0.35</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="I22" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="J22" s="1" t="n">
         <v>0.34</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <v>-3.47</v>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="M22" s="1" t="n">
         <v>-8.51</v>
       </c>
-      <c r="K22" s="1" t="inlineStr">
+      <c r="N22" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L22" s="1" t="inlineStr">
+      <c r="O22" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="P22" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="Q22" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1753,50 +1923,57 @@
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>12.5</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="H23" s="1" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="I23" s="1" t="n">
         <v>1.85</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="J23" s="1" t="n">
         <v>1.04</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <v>-3.73</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="L23" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="M23" s="1" t="n">
         <v>-10.07</v>
       </c>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="N23" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
+      <c r="O23" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="P23" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="Q23" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1811,50 +1988,57 @@
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="C24" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-22</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>39.06</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="H24" s="1" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="I24" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="J24" s="1" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="K24" s="1" t="n">
         <v>-3.84</v>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="L24" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="M24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="N24" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="O24" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M24" s="1" t="inlineStr">
+      <c r="P24" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
+      <c r="Q24" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1869,50 +2053,57 @@
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="C25" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>52.69</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="H25" s="1" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="I25" s="1" t="n">
         <v>2.59</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="J25" s="1" t="n">
         <v>0.44</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="K25" s="1" t="n">
         <v>-4.56</v>
       </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="L25" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="M25" s="1" t="n">
         <v>-13.98</v>
       </c>
-      <c r="K25" s="1" t="inlineStr">
+      <c r="N25" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L25" s="1" t="inlineStr">
+      <c r="O25" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M25" s="1" t="inlineStr">
+      <c r="P25" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
+      <c r="Q25" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1927,50 +2118,57 @@
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="C26" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>99.62</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="H26" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="I26" s="1" t="n">
         <v>1.46</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="J26" s="1" t="n">
         <v>-0.02</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="K26" s="1" t="n">
         <v>-4.76</v>
       </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="L26" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="M26" s="1" t="n">
         <v>-7.13</v>
       </c>
-      <c r="K26" s="1" t="inlineStr">
+      <c r="N26" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
+      <c r="O26" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M26" s="1" t="inlineStr">
+      <c r="P26" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
+      <c r="Q26" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1985,50 +2183,57 @@
       <c r="B27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="C27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>93.42</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="H27" s="1" t="n">
         <v>0.58</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="I27" s="1" t="n">
         <v>1.67</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="J27" s="1" t="n">
         <v>-2.29</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="K27" s="1" t="n">
         <v>-6.22</v>
       </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="L27" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="M27" s="1" t="n">
         <v>-13.47</v>
       </c>
-      <c r="K27" s="1" t="inlineStr">
+      <c r="N27" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L27" s="1" t="inlineStr">
+      <c r="O27" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M27" s="1" t="inlineStr">
+      <c r="P27" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N27" s="1" t="inlineStr">
+      <c r="Q27" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2043,57 +2248,64 @@
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="C28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>10.33</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="H28" s="1" t="n">
         <v>-0.19</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="I28" s="1" t="n">
         <v>2.04</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="J28" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="K28" s="1" t="n">
         <v>-7.41</v>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="L28" s="1" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="M28" s="1" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="K28" s="1" t="inlineStr">
+      <c r="N28" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L28" s="1" t="inlineStr">
+      <c r="O28" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M28" s="1" t="inlineStr">
+      <c r="P28" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="Q28" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:H28">
+  <conditionalFormatting sqref="C2:F28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-10"/>
@@ -2105,16 +2317,28 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I28">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+  <conditionalFormatting sqref="I2:K28">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="-10"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L28">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"Up"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
       <formula>"Down"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J28">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="M2:M28">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-15"/>
         <cfvo type="num" val="-5"/>
@@ -2125,35 +2349,35 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K28">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+  <conditionalFormatting sqref="N2:N28">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L28">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
+  <conditionalFormatting sqref="O2:O28">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M28">
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
+  <conditionalFormatting sqref="P2:P28">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N28">
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
+  <conditionalFormatting sqref="Q2:Q28">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -2391,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB66"/>
+  <dimension ref="A1:AB67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8286,8 +8286,96 @@
         <v>16</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="L67" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N67" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O67" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R67" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="U67" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="V67" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="W67" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="X67" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y67" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z67" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA67" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB67" s="1" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:AB66">
+  <conditionalFormatting sqref="B2:AB67">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="1"/>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>20D Rank Velocity</t>
+          <t>21D Rank Velocity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>6</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>4</v>
@@ -1150,7 +1150,7 @@
         <v>-5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>15</v>
@@ -1280,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>-3</v>
@@ -1475,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>2</v>
@@ -1670,7 +1670,7 @@
         <v>-7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>-6</v>
@@ -1865,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>-6</v>
@@ -1930,7 +1930,7 @@
         <v>-3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>-19</v>
@@ -2060,7 +2060,7 @@
         <v>-4</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>-11</v>
@@ -2125,7 +2125,7 @@
         <v>-4</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>-19</v>
@@ -2190,7 +2190,7 @@
         <v>-1</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>-15</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -568,22 +568,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>88.28</v>
+        <v>90.38</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>-0.33</v>
+        <v>2.38</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-1.85</v>
+        <v>-0.63</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>8.1</v>
+        <v>9.52</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>12.07</v>
+        <v>11.71</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-9.470000000000001</v>
+        <v>-5.73</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -630,25 +630,25 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.28</v>
+        <v>26.72</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>-0.15</v>
+        <v>1.67</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.42</v>
+        <v>0.61</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>3.43</v>
+        <v>4.08</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.53</v>
+        <v>10.75</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -695,25 +695,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>16.68</v>
+        <v>16.97</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>-0.3</v>
+        <v>1.74</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.6</v>
+        <v>0.86</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.529999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -721,16 +721,16 @@
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -763,22 +763,22 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>30.18</v>
+        <v>30.54</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.1</v>
+        <v>1.19</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.31</v>
+        <v>0.86</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -819,31 +819,31 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>281.18</v>
+        <v>285.24</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>-0.89</v>
+        <v>1.44</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>4.91</v>
+        <v>4.86</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-2.29</v>
+        <v>-1.9</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -877,47 +877,47 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v/>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>102.55</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>-2.7</v>
-      </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
           <t>No</t>
@@ -930,19 +930,19 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
@@ -952,32 +952,32 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>52.81</v>
+        <v>13.26</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-0.28</v>
+        <v>2.24</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-0.75</v>
+        <v>-0.48</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-2.59</v>
+        <v>6.5</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v/>
+        <v>5.59</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
@@ -985,60 +985,60 @@
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>31.64</v>
+        <v>78.81</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.25</v>
+        <v>1.95</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>2.4</v>
+        <v>0.44</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0.97</v>
+        <v>-1.51</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>5.61</v>
+        <v>4.86</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-0.06</v>
+        <v>-16.37</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1055,24 +1055,24 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -1082,28 +1082,28 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>77.3</v>
+        <v>31.94</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.09</v>
+        <v>0.95</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>-0.76</v>
+        <v>2.17</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-2.38</v>
+        <v>0.87</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>4.03</v>
+        <v>4.8</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-17.12</v>
+        <v>-0.15</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1130,45 +1130,45 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>15</v>
+        <v>-8</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12.97</v>
+        <v>103.31</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.14</v>
+        <v>0.74</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>-1.72</v>
+        <v>1.48</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>5.26</v>
+        <v>0.13</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>3.24</v>
+        <v>4.28</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1212,28 +1212,28 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>84.04000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.38</v>
+        <v>1.15</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>4.97</v>
+        <v>5.79</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2.82</v>
+        <v>4.15</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-13.11</v>
+        <v>-12.44</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1267,38 +1267,38 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>161.52</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>1.69</v>
-      </c>
       <c r="J13" s="1" t="n">
-        <v>0.61</v>
+        <v>2.38</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>2.04</v>
+        <v>2.57</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,16 +1306,16 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-1.18</v>
+        <v>-5.52</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1332,38 +1332,38 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="G14" s="1" t="n">
-        <v>130.19</v>
+        <v>32.58</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-0.6</v>
+        <v>1.78</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>1.88</v>
+        <v>0.61</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>1.84</v>
+        <v>0.88</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,11 +1371,11 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-6.03</v>
+        <v>-1.63</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1404,10 +1404,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>-6</v>
@@ -1416,27 +1416,27 @@
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>27.86</v>
+        <v>27.92</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-2.33</v>
+        <v>-1.04</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-2.38</v>
+        <v>-3.19</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-4.09</v>
+        <v>-4.88</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,38 +1462,38 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>587.76</v>
+        <v>163.08</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.18</v>
+        <v>0.97</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-1.04</v>
+        <v>0.92</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-1.5</v>
+        <v>0.53</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.04</v>
+        <v>1.31</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-5.19</v>
+        <v>-1.26</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1534,48 +1534,48 @@
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-9</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>33.37</v>
+        <v>33.65</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.12</v>
+        <v>0.84</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="J17" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="1" t="n">
-        <v>0.03</v>
-      </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-1.86</v>
+        <v>-2.07</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -1592,38 +1592,38 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10</v>
+        <v>-3</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>32</v>
+        <v>591.4400000000001</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.67</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>6.32</v>
+        <v>-1.91</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>-0.25</v>
+        <v>0.51</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-25.03</v>
+        <v>-5.59</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1657,46 +1657,46 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>32.01</v>
+        <v>31.01</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.09</v>
+        <v>1.44</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.22</v>
+        <v>-0.98</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.44</v>
+        <v>-0.23</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-2.34</v>
+        <v>0</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1710,50 +1710,50 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Q19" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>30.57</v>
+        <v>32.7</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>-0.68</v>
+        <v>2.19</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-1.22</v>
+        <v>1.79</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.64</v>
+        <v>7.52</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-1.3</v>
+        <v>-0.27</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0</v>
+        <v>-24.19</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1797,7 +1797,7 @@
         <v>-2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-1</v>
@@ -1806,19 +1806,19 @@
         <v>-10</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>94.89</v>
+        <v>95.63</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-0.73</v>
+        <v>0.78</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.12</v>
+        <v>-0.88</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-1.68</v>
+        <v>-1.94</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-1.41</v>
+        <v>-2.16</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-3.36</v>
+        <v>-3.62</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="F22" s="2" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>11.24</v>
+        <v>53.18</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-0.35</v>
+        <v>0.93</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-3.47</v>
+        <v>-3.86</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,21 +1891,21 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-8.51</v>
+        <v>-14.08</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q22" s="1" t="inlineStr">
@@ -1917,38 +1917,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="2" t="n">
-        <v>-3</v>
-      </c>
       <c r="E23" s="2" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-19</v>
+        <v>-8</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>12.5</v>
+        <v>11.27</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>1.85</v>
+        <v>-1.3</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1.04</v>
+        <v>-0.44</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-3.73</v>
+        <v>-4.65</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-10.07</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1975,45 +1975,45 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>39.06</v>
+        <v>12.54</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-0.05</v>
+        <v>0.32</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>1.25</v>
+        <v>0.16</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-0.98</v>
+        <v>0.31</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-3.84</v>
+        <v>-5.21</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0</v>
+        <v>-10.72</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2040,45 +2040,45 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>52.69</v>
+        <v>38.95</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.28</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>2.59</v>
+        <v>-1.25</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.44</v>
+        <v>-2.28</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-4.56</v>
+        <v>-5.44</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-13.98</v>
+        <v>0</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2122,28 +2122,28 @@
         <v>-2</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>99.62</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-0.3</v>
+        <v>0.23</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>1.46</v>
+        <v>-0.38</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.83</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-4.76</v>
+        <v>-6</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-7.13</v>
+        <v>-7.88</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2187,28 +2187,28 @@
         <v>-1</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>93.42</v>
+        <v>93.52</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.58</v>
+        <v>0.11</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>1.67</v>
+        <v>-1.97</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-2.29</v>
+        <v>-3.2</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-6.22</v>
+        <v>-6.2</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M27" s="1" t="n">
-        <v>-13.47</v>
+        <v>-14.28</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>-1</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>-1</v>
@@ -2261,19 +2261,19 @@
         <v>-23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>10.33</v>
+        <v>10.39</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-0.19</v>
+        <v>0.58</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>2.04</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.97</v>
+        <v>0.51</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-7.41</v>
+        <v>-7.65</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2569,14 +2569,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>14</v>
@@ -2588,7 +2588,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>2</v>
@@ -2597,25 +2597,25 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>25</v>
@@ -2624,47 +2624,47 @@
         <v>16</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB2" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>14</v>
@@ -2685,34 +2685,34 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>21</v>
@@ -2724,13 +2724,13 @@
         <v>12</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="1" t="n">
         <v>9</v>
@@ -2739,13 +2739,13 @@
         <v>19</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -2758,40 +2758,40 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L4" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>23</v>
@@ -2800,56 +2800,56 @@
         <v>13</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W4" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X4" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="Y4" s="1" t="n">
+      <c r="AB4" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="Z4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F5" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>24</v>
@@ -2858,61 +2858,61 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L5" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>8</v>
@@ -2921,47 +2921,47 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C6" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>26</v>
@@ -2985,16 +2985,16 @@
         <v>4</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z6" s="1" t="n">
         <v>9</v>
@@ -3003,29 +3003,29 @@
         <v>20</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>22</v>
@@ -3049,22 +3049,22 @@
         <v>18</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>21</v>
@@ -3073,50 +3073,50 @@
         <v>4</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="AA7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA7" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>2</v>
@@ -3134,7 +3134,7 @@
         <v>16</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>14</v>
@@ -3143,65 +3143,65 @@
         <v>26</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S8" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X8" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y8" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z8" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>21</v>
@@ -3213,25 +3213,25 @@
         <v>3</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>23</v>
@@ -3240,28 +3240,28 @@
         <v>9</v>
       </c>
       <c r="S9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V9" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9" s="1" t="n">
         <v>20</v>
@@ -3273,23 +3273,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>20</v>
@@ -3301,13 +3301,13 @@
         <v>3</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>18</v>
@@ -3316,10 +3316,10 @@
         <v>15</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>23</v>
@@ -3334,25 +3334,25 @@
         <v>24</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>10</v>
@@ -3361,26 +3361,26 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2</v>
@@ -3401,13 +3401,13 @@
         <v>18</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>23</v>
@@ -3425,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>4</v>
@@ -3440,7 +3440,7 @@
         <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -3459,16 +3459,16 @@
         <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2</v>
@@ -3486,22 +3486,22 @@
         <v>11</v>
       </c>
       <c r="M12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N12" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N12" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O12" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>6</v>
@@ -3513,13 +3513,13 @@
         <v>8</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>5</v>
@@ -3528,71 +3528,71 @@
         <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O13" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q13" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" s="1" t="n">
         <v>24</v>
@@ -3604,132 +3604,132 @@
         <v>13</v>
       </c>
       <c r="W13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X13" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y13" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z13" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y14" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>20</v>
@@ -3738,7 +3738,7 @@
         <v>6</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>19</v>
@@ -3759,10 +3759,10 @@
         <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R15" s="1" t="n">
         <v>10</v>
@@ -3771,53 +3771,53 @@
         <v>2</v>
       </c>
       <c r="T15" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X15" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U15" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X15" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>20</v>
@@ -3826,25 +3826,25 @@
         <v>6</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
         <v>17</v>
@@ -3853,31 +3853,31 @@
         <v>22</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W16" s="1" t="n">
+      <c r="Y16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X16" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z16" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA16" s="1" t="n">
         <v>21</v>
@@ -3889,32 +3889,32 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>18</v>
@@ -3923,13 +3923,13 @@
         <v>1</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>24</v>
@@ -3941,28 +3941,28 @@
         <v>22</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="1" t="n">
         <v>5</v>
@@ -3971,68 +3971,68 @@
         <v>21</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E18" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>26</v>
@@ -4041,7 +4041,7 @@
         <v>7</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>4</v>
@@ -4059,62 +4059,62 @@
         <v>21</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O19" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P19" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="R19" s="1" t="n">
         <v>3</v>
@@ -4123,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U19" s="1" t="n">
         <v>7</v>
@@ -4135,7 +4135,7 @@
         <v>4</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y19" s="1" t="n">
         <v>6</v>
@@ -4147,47 +4147,47 @@
         <v>21</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
@@ -4196,37 +4196,37 @@
         <v>17</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z20" s="1" t="n">
         <v>5</v>
@@ -4241,7 +4241,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
@@ -4251,10 +4251,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>18</v>
@@ -4263,19 +4263,19 @@
         <v>21</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>19</v>
@@ -4287,122 +4287,122 @@
         <v>23</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X21" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA21" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z22" s="1" t="n">
         <v>4</v>
@@ -4417,41 +4417,41 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M23" s="1" t="n">
         <v>19</v>
@@ -4466,7 +4466,7 @@
         <v>12</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>7</v>
@@ -4475,13 +4475,13 @@
         <v>1</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U23" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>3</v>
@@ -4490,7 +4490,7 @@
         <v>23</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="1" t="n">
         <v>4</v>
@@ -4505,190 +4505,190 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V24" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X24" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z24" s="1" t="n">
+      <c r="AA24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB24" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB24" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB25" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>15</v>
@@ -4697,128 +4697,128 @@
         <v>25</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" s="1" t="n">
+      <c r="P26" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L26" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N26" s="1" t="n">
+      <c r="Q26" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="O26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P26" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="R26" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V26" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W26" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X26" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y26" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z26" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J27" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R27" s="1" t="n">
         <v>10</v>
@@ -4830,77 +4830,77 @@
         <v>26</v>
       </c>
       <c r="U27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X27" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y27" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z27" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L28" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N28" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M28" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O28" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P28" s="1" t="n">
         <v>8</v>
@@ -4921,83 +4921,83 @@
         <v>7</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z28" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H29" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I29" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J29" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O29" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S29" s="1" t="n">
         <v>1</v>
@@ -5009,47 +5009,47 @@
         <v>7</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W29" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>22</v>
@@ -5058,43 +5058,43 @@
         <v>20</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P30" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U30" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N30" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O30" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R30" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S30" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T30" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U30" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V30" s="1" t="n">
         <v>15</v>
@@ -5103,25 +5103,25 @@
         <v>3</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA30" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
@@ -5131,37 +5131,37 @@
         <v>21</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J31" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L31" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>24</v>
@@ -5170,13 +5170,13 @@
         <v>2</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R31" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>25</v>
@@ -5185,19 +5185,19 @@
         <v>6</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W31" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y31" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X31" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y31" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z31" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA31" s="1" t="n">
         <v>23</v>
@@ -5209,44 +5209,44 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C32" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F32" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M32" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N32" s="1" t="n">
         <v>17</v>
@@ -5258,34 +5258,34 @@
         <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R32" s="1" t="n">
+      <c r="W32" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y32" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W32" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X32" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y32" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z32" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="AA32" s="1" t="n">
         <v>24</v>
@@ -5297,141 +5297,141 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="F33" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G33" s="1" t="n">
+      <c r="H33" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M33" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L33" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M33" s="1" t="n">
+      <c r="N33" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N33" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O33" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y33" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA33" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB33" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>11</v>
@@ -5440,13 +5440,13 @@
         <v>7</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V34" s="1" t="n">
         <v>12</v>
@@ -5455,44 +5455,44 @@
         <v>8</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y34" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA34" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB34" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z34" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA34" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB34" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C35" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C35" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D35" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>5</v>
@@ -5501,110 +5501,110 @@
         <v>6</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P35" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q35" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R35" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R35" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y35" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB35" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="X35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y35" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z35" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA35" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB35" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O36" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>2</v>
@@ -5613,34 +5613,34 @@
         <v>7</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V36" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W36" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y36" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W36" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X36" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y36" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z36" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA36" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB36" s="1" t="n">
         <v>10</v>
@@ -5649,11 +5649,11 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>26</v>
@@ -5668,13 +5668,13 @@
         <v>22</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>3</v>
@@ -5686,13 +5686,13 @@
         <v>18</v>
       </c>
       <c r="M37" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O37" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>2</v>
@@ -5701,53 +5701,53 @@
         <v>7</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W37" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y37" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z37" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB37" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z37" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA37" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB37" s="1" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
@@ -5768,19 +5768,19 @@
         <v>3</v>
       </c>
       <c r="K38" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O38" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P38" s="1" t="n">
         <v>2</v>
@@ -5795,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
         <v>5</v>
@@ -5816,7 +5816,7 @@
         <v>21</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB38" s="1" t="n">
         <v>12</v>
@@ -5825,17 +5825,17 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
@@ -5844,7 +5844,7 @@
         <v>22</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
@@ -5853,37 +5853,37 @@
         <v>6</v>
       </c>
       <c r="J39" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O39" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P39" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N39" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O39" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q39" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>5</v>
@@ -5892,47 +5892,47 @@
         <v>8</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z39" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA39" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA39" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB39" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F40" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4</v>
@@ -5941,74 +5941,74 @@
         <v>6</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L40" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N40" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M40" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N40" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O40" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P40" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z40" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA40" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA40" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="AB40" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>24</v>
@@ -6017,79 +6017,79 @@
         <v>27</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V41" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W41" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W41" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X41" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -6099,16 +6099,16 @@
         <v>14</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4</v>
@@ -6120,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L42" s="1" t="n">
         <v>11</v>
@@ -6129,7 +6129,7 @@
         <v>12</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O42" s="1" t="n">
         <v>10</v>
@@ -6138,10 +6138,10 @@
         <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>2</v>
@@ -6150,7 +6150,7 @@
         <v>23</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V42" s="1" t="n">
         <v>9</v>
@@ -6159,13 +6159,13 @@
         <v>15</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y42" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z42" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA42" s="1" t="n">
         <v>26</v>
@@ -6177,26 +6177,26 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F43" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>4</v>
@@ -6208,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
@@ -6217,7 +6217,7 @@
         <v>12</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>10</v>
@@ -6226,16 +6226,16 @@
         <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R43" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R43" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S43" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U43" s="1" t="n">
         <v>8</v>
@@ -6244,28 +6244,28 @@
         <v>9</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X43" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -6275,7 +6275,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>27</v>
@@ -6296,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
@@ -6311,7 +6311,7 @@
         <v>10</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>6</v>
@@ -6320,10 +6320,10 @@
         <v>7</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>8</v>
@@ -6341,7 +6341,7 @@
         <v>16</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA44" s="1" t="n">
         <v>25</v>
@@ -6353,26 +6353,26 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>4</v>
@@ -6384,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
@@ -6393,28 +6393,28 @@
         <v>12</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R45" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S45" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U45" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S45" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T45" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U45" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V45" s="1" t="n">
         <v>9</v>
@@ -6423,16 +6423,16 @@
         <v>14</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z45" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB45" s="1" t="n">
         <v>15</v>
@@ -6441,11 +6441,11 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="1" t="n">
         <v>25</v>
@@ -6454,13 +6454,13 @@
         <v>22</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>4</v>
@@ -6469,43 +6469,43 @@
         <v>5</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P46" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R46" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W46" s="1" t="n">
         <v>14</v>
@@ -6514,13 +6514,13 @@
         <v>21</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z46" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA46" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA46" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>15</v>
@@ -6529,23 +6529,23 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>12</v>
@@ -6557,10 +6557,10 @@
         <v>5</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>11</v>
@@ -6575,13 +6575,13 @@
         <v>9</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>1</v>
@@ -6590,7 +6590,7 @@
         <v>17</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V47" s="1" t="n">
         <v>10</v>
@@ -6599,16 +6599,16 @@
         <v>14</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z47" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA47" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>15</v>
@@ -6617,7 +6617,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -6627,7 +6627,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>27</v>
@@ -6636,16 +6636,16 @@
         <v>20</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K48" s="1" t="n">
         <v>19</v>
@@ -6654,16 +6654,16 @@
         <v>11</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>6</v>
@@ -6678,7 +6678,7 @@
         <v>17</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V48" s="1" t="n">
         <v>10</v>
@@ -6687,16 +6687,16 @@
         <v>14</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y48" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z48" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA48" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA48" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>15</v>
@@ -6705,26 +6705,26 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>2</v>
@@ -6736,28 +6736,28 @@
         <v>5</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N49" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q49" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R49" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R49" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>1</v>
@@ -6766,7 +6766,7 @@
         <v>17</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>10</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>18</v>
@@ -6784,7 +6784,7 @@
         <v>23</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>15</v>
@@ -6793,32 +6793,32 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>5</v>
@@ -6833,65 +6833,65 @@
         <v>13</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O50" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R50" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U50" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S50" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T50" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V50" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>25</v>
@@ -6900,22 +6900,22 @@
         <v>14</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M51" s="1" t="n">
         <v>13</v>
@@ -6924,28 +6924,28 @@
         <v>17</v>
       </c>
       <c r="O51" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R51" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P51" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q51" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R51" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S51" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T51" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V51" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V51" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>15</v>
@@ -6957,7 +6957,7 @@
         <v>19</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>22</v>
@@ -6969,7 +6969,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -6979,31 +6979,31 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I52" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J52" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K52" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>13</v>
@@ -7012,7 +7012,7 @@
         <v>17</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P52" s="1" t="n">
         <v>5</v>
@@ -7021,16 +7021,16 @@
         <v>6</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V52" s="1" t="n">
         <v>9</v>
@@ -7042,13 +7042,13 @@
         <v>26</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z52" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA52" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA52" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB52" s="1" t="n">
         <v>16</v>
@@ -7057,41 +7057,41 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D53" s="1" t="n">
+      <c r="E53" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E53" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G53" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L53" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>13</v>
@@ -7100,25 +7100,25 @@
         <v>17</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V53" s="1" t="n">
         <v>9</v>
@@ -7130,10 +7130,10 @@
         <v>26</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>25</v>
@@ -7145,23 +7145,23 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>11</v>
@@ -7185,7 +7185,7 @@
         <v>13</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O54" s="1" t="n">
         <v>8</v>
@@ -7203,16 +7203,16 @@
         <v>1</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U54" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V54" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V54" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W54" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X54" s="1" t="n">
         <v>26</v>
@@ -7221,19 +7221,19 @@
         <v>20</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -7243,7 +7243,7 @@
         <v>24</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>21</v>
@@ -7261,7 +7261,7 @@
         <v>5</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>19</v>
@@ -7276,19 +7276,19 @@
         <v>16</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" s="1" t="n">
         <v>17</v>
@@ -7309,7 +7309,7 @@
         <v>20</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
@@ -7321,7 +7321,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -7331,43 +7331,43 @@
         <v>24</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I56" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K56" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L56" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M56" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>6</v>
@@ -7376,19 +7376,19 @@
         <v>8</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>26</v>
@@ -7397,19 +7397,19 @@
         <v>20</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -7419,16 +7419,16 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F57" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>3</v>
@@ -7440,10 +7440,10 @@
         <v>5</v>
       </c>
       <c r="K57" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L57" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>13</v>
@@ -7455,25 +7455,25 @@
         <v>10</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T57" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U57" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W57" s="1" t="n">
         <v>15</v>
@@ -7482,10 +7482,10 @@
         <v>26</v>
       </c>
       <c r="Y57" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z57" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z57" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>25</v>
@@ -7497,23 +7497,23 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D58" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F58" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>18</v>
@@ -7525,46 +7525,46 @@
         <v>4</v>
       </c>
       <c r="J58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L58" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M58" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K58" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L58" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M58" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N58" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X58" s="1" t="n">
         <v>26</v>
@@ -7573,35 +7573,35 @@
         <v>21</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>18</v>
@@ -7613,31 +7613,31 @@
         <v>4</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K59" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
@@ -7646,98 +7646,98 @@
         <v>20</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X59" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="E60" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U60" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V60" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V60" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>14</v>
@@ -7746,7 +7746,7 @@
         <v>26</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z60" s="1" t="n">
         <v>21</v>
@@ -7761,17 +7761,17 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>22</v>
@@ -7780,31 +7780,31 @@
         <v>19</v>
       </c>
       <c r="G61" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L61" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M61" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N61" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H61" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K61" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L61" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M61" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N61" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P61" s="1" t="n">
         <v>1</v>
@@ -7813,56 +7813,56 @@
         <v>5</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z61" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z61" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA61" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>19</v>
@@ -7871,7 +7871,7 @@
         <v>18</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>8</v>
@@ -7880,13 +7880,13 @@
         <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L62" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>14</v>
@@ -7901,7 +7901,7 @@
         <v>5</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
@@ -7910,10 +7910,10 @@
         <v>12</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>15</v>
@@ -7922,13 +7922,13 @@
         <v>26</v>
       </c>
       <c r="Y62" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z62" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA62" s="1" t="n">
         <v>25</v>
-      </c>
-      <c r="Z62" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA62" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB62" s="1" t="n">
         <v>16</v>
@@ -7937,29 +7937,29 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>8</v>
@@ -7971,13 +7971,13 @@
         <v>13</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>4</v>
@@ -7989,7 +7989,7 @@
         <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
@@ -7998,56 +7998,56 @@
         <v>12</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V63" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X63" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y63" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA63" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Y63" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z63" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA63" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="AB63" s="1" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>8</v>
@@ -8059,13 +8059,13 @@
         <v>13</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
@@ -8077,65 +8077,65 @@
         <v>5</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T64" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V64" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W64" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X64" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y64" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z64" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA64" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Y64" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z64" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA64" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="AB64" s="1" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="G65" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>8</v>
@@ -8144,16 +8144,16 @@
         <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M65" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O65" s="1" t="n">
         <v>4</v>
@@ -8165,7 +8165,7 @@
         <v>5</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>2</v>
@@ -8180,50 +8180,50 @@
         <v>9</v>
       </c>
       <c r="W65" s="1" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X65" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y65" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z65" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA65" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Y65" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z65" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA65" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="AB65" s="1" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>8</v>
@@ -8232,16 +8232,16 @@
         <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>10</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O66" s="1" t="n">
         <v>4</v>
@@ -8253,77 +8253,77 @@
         <v>5</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U66" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V66" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W66" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X66" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y66" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z66" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA66" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Y66" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z66" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA66" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="AB66" s="1" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>20</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H67" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="I67" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>10</v>
@@ -8338,40 +8338,40 @@
         <v>1</v>
       </c>
       <c r="Q67" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="R67" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R67" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U67" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V67" s="1" t="n">
         <v>9</v>
       </c>
       <c r="W67" s="1" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="X67" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y67" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z67" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA67" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="Y67" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z67" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA67" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB67" s="1" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -559,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -568,22 +568,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>90.38</v>
+        <v>92.22</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.79</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>9.52</v>
+        <v>12.37</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>11.71</v>
+        <v>14.62</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-5.73</v>
+        <v>-3.36</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -624,31 +624,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.72</v>
+        <v>26.73</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.67</v>
+        <v>0.04</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>4.08</v>
+        <v>2.69</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>10.75</v>
+        <v>10.89</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>16.97</v>
+        <v>16.99</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.74</v>
+        <v>0.12</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.33</v>
+        <v>10.01</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -747,42 +747,42 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Market</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>30.54</v>
+        <v>52.86</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.19</v>
+        <v>-0.53</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.86</v>
+        <v>-1.51</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2.79</v>
+        <v>-4.02</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
@@ -790,17 +790,17 @@
       </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
@@ -812,38 +812,38 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>285.24</v>
+        <v>13.49</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2.7</v>
+        <v>7.47</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>4.86</v>
+        <v>7.66</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
@@ -877,60 +877,60 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Capital Market</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-3</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>53.14</v>
+        <v>87.62</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.62</v>
+        <v>2.38</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>-1.68</v>
+        <v>4.13</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>-3</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v/>
+        <v>7.15</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0</v>
+        <v>-10.2</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -942,38 +942,38 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>13.26</v>
+        <v>287.37</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>2.24</v>
+        <v>0.75</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>-0.48</v>
+        <v>3.13</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>6.5</v>
+        <v>4.86</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>5.59</v>
+        <v>6.64</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1007,38 +1007,38 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>78.81</v>
+        <v>31.8</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.95</v>
+        <v>-0.44</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.44</v>
+        <v>0.9</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>-1.51</v>
+        <v>1.29</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>4.86</v>
+        <v>5.24</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-16.37</v>
+        <v>-0.43</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1065,45 +1065,45 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>31.94</v>
+        <v>78.7</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.95</v>
+        <v>-0.14</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>2.17</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0.87</v>
+        <v>-0.67</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>4.8</v>
+        <v>5.17</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-0.15</v>
+        <v>-16.35</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P10" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="D11" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>-4</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>-9</v>
-      </c>
       <c r="F11" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>103.31</v>
+        <v>30.16</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.74</v>
+        <v>-1.24</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>1.48</v>
+        <v>-1.81</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.13</v>
+        <v>2.6</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>4.28</v>
+        <v>4.59</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,64 +1176,64 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P11" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>85.58</v>
+        <v>33.77</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.83</v>
+        <v>3.27</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>1.15</v>
+        <v>5.95</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>5.79</v>
+        <v>11.93</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>4.15</v>
+        <v>3.71</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-12.44</v>
+        <v>-21.58</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1274,31 +1274,31 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>132.26</v>
+        <v>132.83</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.59</v>
+        <v>0.43</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>2.57</v>
+        <v>3.41</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-5.52</v>
+        <v>-4.96</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1332,60 +1332,60 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>32.58</v>
+        <v>101.3</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.78</v>
+        <v>-1.95</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.61</v>
+        <v>-1.17</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.88</v>
+        <v>-2.22</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-1.63</v>
+        <v>-4.73</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -1404,31 +1404,31 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="D15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>-1</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-6</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>27.92</v>
+        <v>27.77</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.22</v>
+        <v>-0.54</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-1.04</v>
+        <v>-1.32</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-3.19</v>
+        <v>-3.08</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-4.88</v>
+        <v>-5.23</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr">
@@ -1462,103 +1462,103 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>587.54</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>163.08</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0.92</v>
-      </c>
       <c r="J16" s="1" t="n">
-        <v>0.53</v>
+        <v>-2.24</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-1.26</v>
+        <v>-6.05</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P16" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>-5</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>-7</v>
-      </c>
       <c r="E17" s="2" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>33.65</v>
+        <v>32.43</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.84</v>
+        <v>-0.46</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>1.37</v>
+        <v>0.16</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.79</v>
+        <v>0.46</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-2.07</v>
+        <v>-1.92</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -1592,46 +1592,46 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>591.4400000000001</v>
+        <v>162.11</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-0.67</v>
+        <v>0.3</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-1.91</v>
+        <v>0.38</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-5.59</v>
+        <v>-1.69</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1650,53 +1650,53 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8</v>
+        <v>-11</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>31.01</v>
+        <v>33.44</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.44</v>
+        <v>-0.62</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-0.98</v>
+        <v>0.64</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.49</v>
+        <v>0.16</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>-0.23</v>
+        <v>0.66</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1715,45 +1715,45 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>32.7</v>
+        <v>31.01</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>1.79</v>
+        <v>-0.75</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>7.52</v>
+        <v>0.4</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.49</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-24.19</v>
+        <v>0</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1806,19 +1806,19 @@
         <v>-10</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>95.63</v>
+        <v>95.17</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.78</v>
+        <v>-0.48</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-1.94</v>
+        <v>-2.03</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-2.16</v>
+        <v>-2.84</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-3.62</v>
+        <v>-3.92</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1859,31 +1859,31 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>53.18</v>
+        <v>52.43</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.93</v>
+        <v>-1.41</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.32</v>
+        <v>-0.82</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-3.86</v>
+        <v>-4.99</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,21 +1891,21 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-14.08</v>
+        <v>-15.15</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q22" s="1" t="inlineStr">
@@ -1917,38 +1917,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="F23" s="2" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>11.27</v>
+        <v>92.73</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.27</v>
+        <v>-0.84</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-1.3</v>
+        <v>-1.83</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-0.44</v>
+        <v>-3.4</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-4.65</v>
+        <v>-5.12</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-9.220000000000001</v>
+        <v>-14.86</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1989,31 +1989,31 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>-4</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>-20</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>12.54</v>
+        <v>12.46</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.32</v>
+        <v>-0.64</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.16</v>
+        <v>-1.04</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.31</v>
+        <v>-1.52</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-5.21</v>
+        <v>-6.25</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-10.72</v>
+        <v>-11.14</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2047,38 +2047,38 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-12</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-23</v>
+        <v>-13</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>38.95</v>
+        <v>11.24</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-1.25</v>
+        <v>-0.91</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-2.28</v>
+        <v>-0.05</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-5.44</v>
+        <v>-6.5</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0</v>
+        <v>-9.31</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
         <v>-20</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>99.84999999999999</v>
+        <v>98.87</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.23</v>
+        <v>-0.98</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-0.38</v>
+        <v>-1.51</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-0.83</v>
+        <v>-1.27</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-6</v>
+        <v>-7.38</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-7.88</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2177,46 +2177,46 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="D27" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>93.52</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="K27" s="1" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>-14.28</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
         <v>-2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>-23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>10.39</v>
+        <v>10.25</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.58</v>
+        <v>-1.35</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.9</v>
+        <v>-0.33</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.46</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-7.65</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-8.630000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2569,23 +2569,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>21</v>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>20</v>
@@ -2615,56 +2615,56 @@
         <v>27</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S2" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T2" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T2" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U2" s="1" t="n">
+      <c r="V2" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W2" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V2" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W2" s="1" t="n">
+      <c r="X2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X2" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y2" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z2" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB2" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>14</v>
@@ -2676,7 +2676,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2685,25 +2685,25 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O3" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>25</v>
@@ -2712,50 +2712,50 @@
         <v>16</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>26</v>
@@ -2773,7 +2773,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
@@ -2782,25 +2782,25 @@
         <v>18</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1" t="n">
         <v>21</v>
@@ -2812,74 +2812,74 @@
         <v>12</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA4" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L5" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>23</v>
@@ -2888,56 +2888,56 @@
         <v>13</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="AB5" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="Z5" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB5" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F6" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>24</v>
@@ -2946,61 +2946,61 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L6" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>8</v>
@@ -3009,47 +3009,47 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>26</v>
@@ -3073,16 +3073,16 @@
         <v>4</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="1" t="n">
         <v>9</v>
@@ -3091,29 +3091,29 @@
         <v>20</v>
       </c>
       <c r="AB7" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>22</v>
@@ -3137,22 +3137,22 @@
         <v>18</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>21</v>
@@ -3161,50 +3161,50 @@
         <v>4</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z8" s="1" t="n">
+      <c r="AA8" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB8" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA8" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB8" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
@@ -3222,7 +3222,7 @@
         <v>16</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>14</v>
@@ -3231,68 +3231,68 @@
         <v>26</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R9" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V9" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X9" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y9" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z9" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2</v>
@@ -3301,25 +3301,25 @@
         <v>3</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>23</v>
@@ -3328,31 +3328,31 @@
         <v>9</v>
       </c>
       <c r="S10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T10" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V10" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB10" s="1" t="n">
         <v>10</v>
@@ -3361,23 +3361,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>20</v>
@@ -3389,13 +3389,13 @@
         <v>3</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>18</v>
@@ -3404,10 +3404,10 @@
         <v>15</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>23</v>
@@ -3422,25 +3422,25 @@
         <v>24</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>10</v>
@@ -3449,26 +3449,26 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2</v>
@@ -3489,13 +3489,13 @@
         <v>18</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>23</v>
@@ -3513,7 +3513,7 @@
         <v>8</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>4</v>
@@ -3528,7 +3528,7 @@
         <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>10</v>
@@ -3537,7 +3537,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -3547,16 +3547,16 @@
         <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>2</v>
@@ -3574,22 +3574,22 @@
         <v>11</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N13" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O13" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S13" s="1" t="n">
         <v>6</v>
@@ -3601,13 +3601,13 @@
         <v>8</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>5</v>
@@ -3616,71 +3616,71 @@
         <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB13" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N14" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O14" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P14" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q14" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" s="1" t="n">
         <v>24</v>
@@ -3692,132 +3692,132 @@
         <v>13</v>
       </c>
       <c r="W14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y14" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X14" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y14" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O15" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y15" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>20</v>
@@ -3826,7 +3826,7 @@
         <v>6</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>19</v>
@@ -3847,10 +3847,10 @@
         <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>10</v>
@@ -3859,53 +3859,53 @@
         <v>2</v>
       </c>
       <c r="T16" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W16" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X16" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>20</v>
@@ -3914,25 +3914,25 @@
         <v>6</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
         <v>17</v>
@@ -3941,31 +3941,31 @@
         <v>22</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T17" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W17" s="1" t="n">
+      <c r="Y17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X17" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y17" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z17" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA17" s="1" t="n">
         <v>21</v>
@@ -3977,32 +3977,32 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>18</v>
@@ -4011,13 +4011,13 @@
         <v>1</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O18" s="1" t="n">
         <v>24</v>
@@ -4029,28 +4029,28 @@
         <v>22</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z18" s="1" t="n">
         <v>5</v>
@@ -4059,68 +4059,68 @@
         <v>21</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E19" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" s="1" t="n">
         <v>26</v>
@@ -4129,7 +4129,7 @@
         <v>7</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>4</v>
@@ -4147,62 +4147,62 @@
         <v>21</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O20" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P20" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R20" s="1" t="n">
         <v>3</v>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>7</v>
@@ -4223,7 +4223,7 @@
         <v>4</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y20" s="1" t="n">
         <v>6</v>
@@ -4232,50 +4232,50 @@
         <v>5</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>19</v>
@@ -4284,37 +4284,37 @@
         <v>17</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W21" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z21" s="1" t="n">
         <v>5</v>
@@ -4329,7 +4329,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -4339,10 +4339,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>18</v>
@@ -4351,19 +4351,19 @@
         <v>21</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>19</v>
@@ -4375,122 +4375,122 @@
         <v>23</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X22" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA22" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB22" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M23" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U23" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W23" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z23" s="1" t="n">
         <v>4</v>
@@ -4505,41 +4505,41 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M24" s="1" t="n">
         <v>19</v>
@@ -4554,7 +4554,7 @@
         <v>12</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R24" s="1" t="n">
         <v>7</v>
@@ -4563,13 +4563,13 @@
         <v>1</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U24" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>3</v>
@@ -4578,7 +4578,7 @@
         <v>23</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z24" s="1" t="n">
         <v>4</v>
@@ -4593,320 +4593,320 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V25" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X25" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y25" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z25" s="1" t="n">
+      <c r="AA25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB25" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB25" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB26" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M27" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N27" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V27" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y27" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W27" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X27" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y27" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z27" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J28" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K28" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L28" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N28" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O28" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q28" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R28" s="1" t="n">
         <v>10</v>
@@ -4918,77 +4918,77 @@
         <v>26</v>
       </c>
       <c r="U28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z28" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V28" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X28" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z28" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>23</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N29" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O29" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P29" s="1" t="n">
         <v>8</v>
@@ -5009,83 +5009,83 @@
         <v>7</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z29" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H30" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J30" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O30" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S30" s="1" t="n">
         <v>1</v>
@@ -5097,47 +5097,47 @@
         <v>7</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y30" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>22</v>
@@ -5146,43 +5146,43 @@
         <v>20</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q31" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R31" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U31" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N31" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O31" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P31" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R31" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S31" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V31" s="1" t="n">
         <v>15</v>
@@ -5191,25 +5191,25 @@
         <v>3</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA31" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
@@ -5219,52 +5219,52 @@
         <v>21</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J32" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L32" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R32" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" s="1" t="n">
         <v>25</v>
@@ -5273,22 +5273,22 @@
         <v>6</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X32" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y32" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X32" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y32" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z32" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB32" s="1" t="n">
         <v>8</v>
@@ -5297,44 +5297,44 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C33" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F33" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M33" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M33" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N33" s="1" t="n">
         <v>17</v>
@@ -5346,34 +5346,34 @@
         <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R33" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="W33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="S33" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U33" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V33" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W33" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X33" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y33" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z33" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="AA33" s="1" t="n">
         <v>24</v>
@@ -5385,141 +5385,141 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="F34" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G34" s="1" t="n">
+      <c r="H34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L34" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M34" s="1" t="n">
+      <c r="N34" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N34" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O34" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T34" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y34" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA34" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB34" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="1" t="n">
         <v>11</v>
@@ -5528,13 +5528,13 @@
         <v>7</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>12</v>
@@ -5543,44 +5543,44 @@
         <v>8</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y35" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA35" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB35" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z35" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA35" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB35" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C36" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D36" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>5</v>
@@ -5589,110 +5589,110 @@
         <v>6</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q36" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R36" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R36" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S36" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V36" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W36" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X36" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y36" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA36" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB36" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="X36" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y36" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z36" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA36" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB36" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M37" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O37" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>2</v>
@@ -5701,34 +5701,34 @@
         <v>7</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V37" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W37" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X37" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y37" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W37" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X37" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y37" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z37" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB37" s="1" t="n">
         <v>10</v>
@@ -5737,11 +5737,11 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>26</v>
@@ -5756,13 +5756,13 @@
         <v>22</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>3</v>
@@ -5774,13 +5774,13 @@
         <v>18</v>
       </c>
       <c r="M38" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N38" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O38" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P38" s="1" t="n">
         <v>2</v>
@@ -5789,7 +5789,7 @@
         <v>7</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>1</v>
@@ -5798,44 +5798,44 @@
         <v>25</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V38" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W38" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA38" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB38" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>27</v>
@@ -5856,19 +5856,19 @@
         <v>3</v>
       </c>
       <c r="K39" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N39" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O39" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P39" s="1" t="n">
         <v>2</v>
@@ -5883,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
         <v>5</v>
@@ -5904,7 +5904,7 @@
         <v>21</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB39" s="1" t="n">
         <v>12</v>
@@ -5913,17 +5913,17 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
@@ -5932,7 +5932,7 @@
         <v>22</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>4</v>
@@ -5941,31 +5941,31 @@
         <v>6</v>
       </c>
       <c r="J40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O40" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P40" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K40" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O40" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P40" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>1</v>
@@ -5980,47 +5980,47 @@
         <v>8</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA40" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB40" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C41" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D41" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F41" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
@@ -6029,74 +6029,74 @@
         <v>6</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L41" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N41" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M41" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N41" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O41" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U41" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z41" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA41" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA41" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB41" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>24</v>
@@ -6105,79 +6105,79 @@
         <v>27</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J42" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V42" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W42" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W42" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X42" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z42" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA42" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB42" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -6187,16 +6187,16 @@
         <v>14</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>4</v>
@@ -6208,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L43" s="1" t="n">
         <v>11</v>
@@ -6217,7 +6217,7 @@
         <v>12</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O43" s="1" t="n">
         <v>10</v>
@@ -6226,10 +6226,10 @@
         <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S43" s="1" t="n">
         <v>2</v>
@@ -6238,7 +6238,7 @@
         <v>23</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V43" s="1" t="n">
         <v>9</v>
@@ -6247,13 +6247,13 @@
         <v>15</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y43" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA43" s="1" t="n">
         <v>26</v>
@@ -6265,26 +6265,26 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F44" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>4</v>
@@ -6296,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
@@ -6305,7 +6305,7 @@
         <v>12</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>10</v>
@@ -6314,16 +6314,16 @@
         <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R44" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R44" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U44" s="1" t="n">
         <v>8</v>
@@ -6332,28 +6332,28 @@
         <v>9</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X44" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z44" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -6363,7 +6363,7 @@
         <v>13</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>27</v>
@@ -6384,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
@@ -6399,7 +6399,7 @@
         <v>10</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>6</v>
@@ -6408,10 +6408,10 @@
         <v>7</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>8</v>
@@ -6429,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA45" s="1" t="n">
         <v>25</v>
@@ -6441,26 +6441,26 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>4</v>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>11</v>
@@ -6481,28 +6481,28 @@
         <v>12</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O46" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R46" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U46" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V46" s="1" t="n">
         <v>9</v>
@@ -6511,16 +6511,16 @@
         <v>14</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z46" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB46" s="1" t="n">
         <v>15</v>
@@ -6529,11 +6529,11 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>25</v>
@@ -6542,13 +6542,13 @@
         <v>22</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>4</v>
@@ -6557,43 +6557,43 @@
         <v>5</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N47" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P47" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R47" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W47" s="1" t="n">
         <v>14</v>
@@ -6602,13 +6602,13 @@
         <v>21</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z47" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA47" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>15</v>
@@ -6617,23 +6617,23 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>12</v>
@@ -6645,10 +6645,10 @@
         <v>5</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L48" s="1" t="n">
         <v>11</v>
@@ -6663,13 +6663,13 @@
         <v>9</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>1</v>
@@ -6678,7 +6678,7 @@
         <v>17</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V48" s="1" t="n">
         <v>10</v>
@@ -6687,7 +6687,7 @@
         <v>14</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y48" s="1" t="n">
         <v>18</v>
@@ -6705,7 +6705,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -6715,7 +6715,7 @@
         <v>25</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>27</v>
@@ -6724,16 +6724,16 @@
         <v>20</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K49" s="1" t="n">
         <v>19</v>
@@ -6742,16 +6742,16 @@
         <v>11</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N49" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>6</v>
@@ -6766,7 +6766,7 @@
         <v>17</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>10</v>
@@ -6775,16 +6775,16 @@
         <v>14</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z49" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA49" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA49" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB49" s="1" t="n">
         <v>15</v>
@@ -6793,26 +6793,26 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C50" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>2</v>
@@ -6824,28 +6824,28 @@
         <v>5</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L50" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N50" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P50" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q50" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R50" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R50" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>1</v>
@@ -6854,7 +6854,7 @@
         <v>17</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V50" s="1" t="n">
         <v>10</v>
@@ -6863,7 +6863,7 @@
         <v>14</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y50" s="1" t="n">
         <v>18</v>
@@ -6872,7 +6872,7 @@
         <v>23</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>15</v>
@@ -6881,32 +6881,32 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>5</v>
@@ -6921,65 +6921,65 @@
         <v>13</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O51" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U51" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S51" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T51" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U51" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V51" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB51" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>25</v>
@@ -6988,22 +6988,22 @@
         <v>14</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M52" s="1" t="n">
         <v>13</v>
@@ -7012,28 +7012,28 @@
         <v>17</v>
       </c>
       <c r="O52" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P52" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P52" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q52" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R52" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S52" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U52" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V52" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V52" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W52" s="1" t="n">
         <v>15</v>
@@ -7045,7 +7045,7 @@
         <v>19</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>22</v>
@@ -7057,7 +7057,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -7067,31 +7067,31 @@
         <v>24</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F53" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I53" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J53" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K53" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>13</v>
@@ -7100,7 +7100,7 @@
         <v>17</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P53" s="1" t="n">
         <v>5</v>
@@ -7109,16 +7109,16 @@
         <v>6</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V53" s="1" t="n">
         <v>9</v>
@@ -7130,13 +7130,13 @@
         <v>26</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z53" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA53" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA53" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB53" s="1" t="n">
         <v>16</v>
@@ -7145,41 +7145,41 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="E54" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G54" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>13</v>
@@ -7188,25 +7188,25 @@
         <v>17</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V54" s="1" t="n">
         <v>9</v>
@@ -7218,10 +7218,10 @@
         <v>26</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA54" s="1" t="n">
         <v>25</v>
@@ -7233,23 +7233,23 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>11</v>
@@ -7273,7 +7273,7 @@
         <v>13</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O55" s="1" t="n">
         <v>8</v>
@@ -7291,16 +7291,16 @@
         <v>1</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U55" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V55" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V55" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W55" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X55" s="1" t="n">
         <v>26</v>
@@ -7309,19 +7309,19 @@
         <v>20</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB55" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
@@ -7331,7 +7331,7 @@
         <v>24</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>21</v>
@@ -7349,7 +7349,7 @@
         <v>5</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>19</v>
@@ -7364,19 +7364,19 @@
         <v>16</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" s="1" t="n">
         <v>17</v>
@@ -7397,7 +7397,7 @@
         <v>20</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
@@ -7409,7 +7409,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -7419,43 +7419,43 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I57" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K57" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L57" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>6</v>
@@ -7464,19 +7464,19 @@
         <v>8</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X57" s="1" t="n">
         <v>26</v>
@@ -7485,19 +7485,19 @@
         <v>20</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -7507,16 +7507,16 @@
         <v>24</v>
       </c>
       <c r="D58" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F58" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>3</v>
@@ -7528,10 +7528,10 @@
         <v>5</v>
       </c>
       <c r="K58" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L58" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L58" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>13</v>
@@ -7543,25 +7543,25 @@
         <v>10</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T58" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U58" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V58" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V58" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W58" s="1" t="n">
         <v>15</v>
@@ -7570,10 +7570,10 @@
         <v>26</v>
       </c>
       <c r="Y58" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z58" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z58" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>25</v>
@@ -7585,23 +7585,23 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D59" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F59" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>18</v>
@@ -7613,46 +7613,46 @@
         <v>4</v>
       </c>
       <c r="J59" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L59" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M59" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L59" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M59" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X59" s="1" t="n">
         <v>26</v>
@@ -7661,35 +7661,35 @@
         <v>21</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>18</v>
@@ -7701,31 +7701,31 @@
         <v>4</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
@@ -7734,98 +7734,98 @@
         <v>20</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D61" s="1" t="n">
+      <c r="E61" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M61" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U61" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V61" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V61" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>14</v>
@@ -7834,7 +7834,7 @@
         <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z61" s="1" t="n">
         <v>21</v>
@@ -7849,17 +7849,17 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D62" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>22</v>
@@ -7868,31 +7868,31 @@
         <v>19</v>
       </c>
       <c r="G62" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L62" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M62" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N62" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H62" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="1" t="n">
+      <c r="O62" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K62" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L62" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M62" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N62" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O62" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P62" s="1" t="n">
         <v>1</v>
@@ -7901,65 +7901,65 @@
         <v>5</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U62" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V62" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W62" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X62" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y62" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z62" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z62" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA62" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F63" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D63" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E63" s="1" t="n">
+      <c r="G63" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F63" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="H63" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>8</v>
@@ -7968,16 +7968,16 @@
         <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L63" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N63" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="M63" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N63" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="O63" s="1" t="n">
         <v>4</v>
@@ -7989,7 +7989,7 @@
         <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
@@ -7998,34 +7998,34 @@
         <v>12</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W63" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X63" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y63" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="X63" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y63" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="Z63" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -8038,16 +8038,16 @@
         <v>20</v>
       </c>
       <c r="E64" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F64" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>15</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>8</v>
@@ -8062,7 +8062,7 @@
         <v>14</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N64" s="1" t="n">
         <v>16</v>
@@ -8077,7 +8077,7 @@
         <v>5</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
@@ -8086,7 +8086,7 @@
         <v>12</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V64" s="1" t="n">
         <v>9</v>
@@ -8113,17 +8113,17 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C65" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D65" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>17</v>
@@ -8135,7 +8135,7 @@
         <v>15</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>8</v>
@@ -8150,7 +8150,7 @@
         <v>14</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N65" s="1" t="n">
         <v>16</v>
@@ -8165,16 +8165,16 @@
         <v>5</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T65" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V65" s="1" t="n">
         <v>9</v>
@@ -8201,29 +8201,29 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C66" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D66" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D66" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E66" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>8</v>
@@ -8232,10 +8232,10 @@
         <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M66" s="1" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
         <v>5</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>2</v>
@@ -8289,29 +8289,29 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>20</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>8</v>
@@ -8320,10 +8320,10 @@
         <v>3</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>10</v>
@@ -8341,16 +8341,16 @@
         <v>5</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T67" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U67" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V67" s="1" t="n">
         <v>9</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -559,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -568,22 +568,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>92.22</v>
+        <v>91.83</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2.04</v>
+        <v>-0.42</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>12.37</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>14.62</v>
+        <v>11.64</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>-3.36</v>
+        <v>-4.75</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -630,25 +630,25 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>26.73</v>
+        <v>27.08</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.04</v>
+        <v>1.31</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.54</v>
+        <v>1.24</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>10.89</v>
+        <v>11.15</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -689,31 +689,31 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>16.99</v>
+        <v>17.17</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.12</v>
+        <v>1.06</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>10.01</v>
+        <v>9.84</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>52.86</v>
+        <v>53.1</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>-0.53</v>
+        <v>0.45</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-1.51</v>
+        <v>-1.92</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-4.02</v>
+        <v>-4.29</v>
       </c>
       <c r="K5" s="1" t="n">
         <v/>
@@ -825,25 +825,25 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>13.49</v>
+        <v>13.65</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>7.47</v>
+        <v>6.93</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.66</v>
+        <v>9.09</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>11</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>19</v>
@@ -896,19 +896,19 @@
         <v>18</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>87.62</v>
+        <v>89.2</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.13</v>
+        <v>5.11</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>8.970000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7.15</v>
+        <v>7.71</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-10.2</v>
+        <v>-9.51</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -935,45 +935,45 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11</v>
+        <v>-2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>287.37</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>3.13</v>
+        <v>0.68</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>4.86</v>
+        <v>-2.1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>6.64</v>
+        <v>5.33</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-1.01</v>
+        <v>-16.52</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1007,38 +1007,38 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EV &amp; New Age Auto</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>287.38</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>-0.44</v>
-      </c>
       <c r="I9" s="1" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>1.29</v>
+        <v>3.64</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>5.24</v>
+        <v>5.13</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-0.43</v>
+        <v>-2.01</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
@@ -1072,55 +1072,55 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>EV &amp; New Age Auto</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-5</v>
-      </c>
       <c r="F10" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>78.7</v>
+        <v>32.05</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.79</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="J10" s="1" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
         <v>-0.67</v>
       </c>
-      <c r="K10" s="1" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>-16.35</v>
-      </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1130,45 +1130,45 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>-2</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-4</v>
+        <v>17</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>30.16</v>
+        <v>34.54</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>-1.24</v>
+        <v>2.28</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>-1.81</v>
+        <v>7.96</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2.6</v>
+        <v>16.48</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0</v>
+        <v>-20.6</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1202,38 +1202,38 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>16</v>
+        <v>-7</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>33.77</v>
+        <v>30.37</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>3.27</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>5.95</v>
+        <v>-1.73</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>11.93</v>
+        <v>0.93</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>3.71</v>
+        <v>4.36</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-21.58</v>
+        <v>0</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>3</v>
@@ -1286,19 +1286,19 @@
         <v>4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>132.83</v>
+        <v>133.71</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>2.33</v>
+        <v>0.89</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>3.41</v>
+        <v>2.53</v>
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>-4.96</v>
+        <v>-5.3</v>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
@@ -1332,38 +1332,38 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>Private Bank</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-11</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>101.3</v>
+        <v>28.11</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>-1.95</v>
+        <v>1.22</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-1.17</v>
+        <v>-0.71</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-2.22</v>
+        <v>-2.4</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-4.73</v>
+        <v>-5.05</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1385,50 +1385,50 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Private Bank</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>27.77</v>
+        <v>591.74</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>-0.54</v>
+        <v>0.71</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-1.32</v>
+        <v>-0.97</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-3.08</v>
+        <v>-2.29</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-5.23</v>
+        <v>-6.34</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr">
@@ -1462,55 +1462,55 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>587.54</v>
+        <v>32.77</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-0.66</v>
+        <v>1.05</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-1</v>
+        <v>0.43</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-2.24</v>
+        <v>-0.13</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-6.05</v>
+        <v>-1.9</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -1520,45 +1520,45 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>32.43</v>
+        <v>31.45</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>-0.46</v>
+        <v>1.42</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.16</v>
+        <v>-1.25</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.92</v>
+        <v>1.11</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1566,26 +1566,26 @@
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>-1.92</v>
+        <v>0</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q17" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1599,10 +1599,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-2</v>
@@ -1611,19 +1611,19 @@
         <v>-8</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>162.11</v>
+        <v>163.6</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>-0.59</v>
+        <v>0.92</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-1.69</v>
+        <v>-1.79</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1657,38 +1657,38 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-7</v>
+        <v>-13</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-11</v>
+        <v>-16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>33.44</v>
+        <v>101.16</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.62</v>
+        <v>-0.14</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0.64</v>
+        <v>-2.92</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0.16</v>
+        <v>-4.83</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.66</v>
+        <v>0.21</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-2.52</v>
+        <v>-5.83</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -1722,55 +1722,55 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>7</v>
+        <v>-13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>31.01</v>
+        <v>33.75</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.75</v>
+        <v>-0.45</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.4</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0</v>
+        <v>-2.61</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>-2</v>
@@ -1806,19 +1806,19 @@
         <v>-10</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>95.17</v>
+        <v>95.84</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>-0.48</v>
+        <v>0.7</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-2.03</v>
+        <v>-2.1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-2.84</v>
+        <v>-3.39</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-3.92</v>
+        <v>-4.23</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
@@ -1852,38 +1852,38 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>52.43</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>-1.41</v>
+        <v>0.28</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>1.01</v>
+        <v>-1.61</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-0.82</v>
+        <v>-3.7</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-4.99</v>
+        <v>-5.09</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-15.15</v>
+        <v>-15.49</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
@@ -1917,38 +1917,38 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-7</v>
+        <v>-19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>92.73</v>
+        <v>12.75</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>-0.84</v>
+        <v>2.33</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-1.83</v>
+        <v>-0.18</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-3.4</v>
+        <v>-0.04</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-5.12</v>
+        <v>-5.19</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,64 +1956,64 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-14.86</v>
+        <v>-10</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P23" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P23" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>12.46</v>
+        <v>53.27</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>-0.64</v>
+        <v>1.6</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-1.04</v>
+        <v>-0.04</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>-1.52</v>
+        <v>0.2</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-6.25</v>
+        <v>-5.62</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,64 +2021,64 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-11.14</v>
+        <v>-14.67</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P24" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>11.24</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>-0.27</v>
+        <v>1.13</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-0.91</v>
+        <v>-1.86</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-0.05</v>
+        <v>-1.42</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-6.5</v>
+        <v>-6.97</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,64 +2086,64 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-9.31</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="P25" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P25" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>98.87</v>
+        <v>11.24</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-1.51</v>
+        <v>-2.11</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-1.27</v>
+        <v>-1.26</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-7.38</v>
+        <v>-7.8</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-8.630000000000001</v>
+        <v>-10.24</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2184,31 +2184,31 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>-25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>38.28</v>
+        <v>38.23</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-1.72</v>
+        <v>-0.13</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>-2.44</v>
+        <v>-3.95</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-4.97</v>
+        <v>-5.6</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-8.26</v>
+        <v>-8.83</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>-1</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>-4</v>
@@ -2264,16 +2264,16 @@
         <v>10.25</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>-0.33</v>
+        <v>-2.13</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-1.46</v>
+        <v>-2.39</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-9.710000000000001</v>
+        <v>-10.63</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,26 +2569,26 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>2</v>
@@ -2597,13 +2597,13 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>20</v>
@@ -2618,19 +2618,19 @@
         <v>26</v>
       </c>
       <c r="Q2" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="R2" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="U2" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V2" s="1" t="n">
         <v>17</v>
@@ -2645,35 +2645,35 @@
         <v>5</v>
       </c>
       <c r="Z2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB2" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA2" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB2" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>21</v>
@@ -2691,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>20</v>
@@ -2703,56 +2703,56 @@
         <v>27</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U3" s="1" t="n">
+      <c r="V3" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W3" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V3" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W3" s="1" t="n">
+      <c r="X3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X3" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y3" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>14</v>
@@ -2764,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>2</v>
@@ -2773,25 +2773,25 @@
         <v>3</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>25</v>
@@ -2800,50 +2800,50 @@
         <v>16</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V4" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W4" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y4" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB4" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA4" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>26</v>
@@ -2861,7 +2861,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
@@ -2870,25 +2870,25 @@
         <v>18</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" s="1" t="n">
         <v>21</v>
@@ -2900,74 +2900,74 @@
         <v>12</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L6" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>23</v>
@@ -2976,56 +2976,56 @@
         <v>13</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X6" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="Y6" s="1" t="n">
+      <c r="AB6" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="Z6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB6" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F7" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>24</v>
@@ -3034,61 +3034,61 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L7" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>8</v>
@@ -3097,47 +3097,47 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M8" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>26</v>
@@ -3161,16 +3161,16 @@
         <v>4</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="1" t="n">
         <v>9</v>
@@ -3179,29 +3179,29 @@
         <v>20</v>
       </c>
       <c r="AB8" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>22</v>
@@ -3225,22 +3225,22 @@
         <v>18</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>21</v>
@@ -3249,50 +3249,50 @@
         <v>4</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z9" s="1" t="n">
+      <c r="AA9" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB9" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA9" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB9" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2</v>
@@ -3310,7 +3310,7 @@
         <v>16</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>14</v>
@@ -3319,68 +3319,68 @@
         <v>26</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R10" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U10" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V10" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W10" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X10" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y10" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z10" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2</v>
@@ -3389,25 +3389,25 @@
         <v>3</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O11" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>23</v>
@@ -3416,31 +3416,31 @@
         <v>9</v>
       </c>
       <c r="S11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V11" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>10</v>
@@ -3449,23 +3449,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>20</v>
@@ -3477,13 +3477,13 @@
         <v>3</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>18</v>
@@ -3492,10 +3492,10 @@
         <v>15</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>23</v>
@@ -3510,25 +3510,25 @@
         <v>24</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>10</v>
@@ -3537,26 +3537,26 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>2</v>
@@ -3577,13 +3577,13 @@
         <v>18</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>23</v>
@@ -3601,7 +3601,7 @@
         <v>8</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>4</v>
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB13" s="1" t="n">
         <v>10</v>
@@ -3625,7 +3625,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
@@ -3635,16 +3635,16 @@
         <v>16</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>2</v>
@@ -3662,22 +3662,22 @@
         <v>11</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N14" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O14" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S14" s="1" t="n">
         <v>6</v>
@@ -3689,13 +3689,13 @@
         <v>8</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X14" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y14" s="1" t="n">
         <v>5</v>
@@ -3704,71 +3704,71 @@
         <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O15" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P15" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q15" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T15" s="1" t="n">
         <v>24</v>
@@ -3780,132 +3780,132 @@
         <v>13</v>
       </c>
       <c r="W15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y15" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X15" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y15" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M16" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O16" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>20</v>
@@ -3914,7 +3914,7 @@
         <v>6</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>19</v>
@@ -3935,10 +3935,10 @@
         <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R17" s="1" t="n">
         <v>10</v>
@@ -3947,53 +3947,53 @@
         <v>2</v>
       </c>
       <c r="T17" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X17" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X17" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>20</v>
@@ -4002,25 +4002,25 @@
         <v>6</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>17</v>
@@ -4029,31 +4029,31 @@
         <v>22</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T18" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U18" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W18" s="1" t="n">
+      <c r="Y18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X18" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y18" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z18" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA18" s="1" t="n">
         <v>21</v>
@@ -4065,32 +4065,32 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>18</v>
@@ -4099,13 +4099,13 @@
         <v>1</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O19" s="1" t="n">
         <v>24</v>
@@ -4117,28 +4117,28 @@
         <v>22</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X19" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y19" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19" s="1" t="n">
         <v>5</v>
@@ -4147,68 +4147,68 @@
         <v>21</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E20" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" s="1" t="n">
         <v>26</v>
@@ -4217,7 +4217,7 @@
         <v>7</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>4</v>
@@ -4235,62 +4235,62 @@
         <v>21</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O21" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="P21" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>21</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>3</v>
@@ -4299,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>7</v>
@@ -4311,7 +4311,7 @@
         <v>4</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y21" s="1" t="n">
         <v>6</v>
@@ -4320,50 +4320,50 @@
         <v>5</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB21" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M22" s="1" t="n">
         <v>19</v>
@@ -4372,37 +4372,37 @@
         <v>17</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="S22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W22" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z22" s="1" t="n">
         <v>5</v>
@@ -4417,7 +4417,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -4427,10 +4427,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>18</v>
@@ -4439,19 +4439,19 @@
         <v>21</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K23" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M23" s="1" t="n">
         <v>19</v>
@@ -4463,122 +4463,122 @@
         <v>23</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23" s="1" t="n">
         <v>15</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X23" s="1" t="n">
         <v>25</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB23" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>24</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>21</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M24" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q24" s="1" t="n">
         <v>20</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U24" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z24" s="1" t="n">
         <v>4</v>
@@ -4593,41 +4593,41 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M25" s="1" t="n">
         <v>19</v>
@@ -4642,7 +4642,7 @@
         <v>12</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>7</v>
@@ -4651,13 +4651,13 @@
         <v>1</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W25" s="1" t="n">
         <v>3</v>
@@ -4666,7 +4666,7 @@
         <v>23</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z25" s="1" t="n">
         <v>4</v>
@@ -4681,320 +4681,320 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K26" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S26" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V26" s="1" t="n">
         <v>14</v>
       </c>
       <c r="W26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X26" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z26" s="1" t="n">
+      <c r="AA26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB26" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="AA26" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB26" s="1" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N27" s="1" t="n">
         <v>18</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U27" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X27" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y27" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z27" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA27" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB27" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>15</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L28" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M28" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M28" s="1" t="n">
-        <v>16</v>
-      </c>
       <c r="N28" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V28" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y28" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="W28" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X28" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>8</v>
-      </c>
       <c r="Z28" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>12</v>
-      </c>
       <c r="J29" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K29" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L29" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>18</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="R29" s="1" t="n">
         <v>10</v>
@@ -5006,77 +5006,77 @@
         <v>26</v>
       </c>
       <c r="U29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="V29" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="W29" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X29" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y29" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z29" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="AA29" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB29" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>23</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L30" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N30" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="M30" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N30" s="1" t="n">
-        <v>13</v>
-      </c>
       <c r="O30" s="1" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>8</v>
@@ -5097,83 +5097,83 @@
         <v>7</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z30" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB30" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F31" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="H31" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I31" s="1" t="n">
-        <v>21</v>
-      </c>
       <c r="J31" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O31" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S31" s="1" t="n">
         <v>1</v>
@@ -5185,47 +5185,47 @@
         <v>7</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W31" s="1" t="n">
         <v>3</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y31" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>22</v>
@@ -5234,43 +5234,43 @@
         <v>20</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J32" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q32" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="R32" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="U32" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="K32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="N32" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="O32" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="P32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="R32" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="S32" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="U32" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V32" s="1" t="n">
         <v>15</v>
@@ -5279,25 +5279,25 @@
         <v>3</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>4</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA32" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AB32" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -5307,52 +5307,52 @@
         <v>21</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J33" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="L33" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>16</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R33" s="1" t="n">
         <v>9</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" s="1" t="n">
         <v>25</v>
@@ -5361,22 +5361,22 @@
         <v>6</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y33" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="X33" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y33" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z33" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB33" s="1" t="n">
         <v>8</v>
@@ -5385,44 +5385,44 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C34" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="F34" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>22</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>17</v>
@@ -5434,34 +5434,34 @@
         <v>2</v>
       </c>
       <c r="Q34" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R34" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V34" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="W34" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z34" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="S34" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="U34" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W34" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X34" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y34" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z34" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="AA34" s="1" t="n">
         <v>24</v>
@@ -5473,141 +5473,141 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="F35" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D35" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="G35" s="1" t="n">
+      <c r="H35" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M35" s="1" t="n">
+      <c r="N35" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N35" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="O35" s="1" t="n">
         <v>23</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T35" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y35" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA35" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB35" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>11</v>
@@ -5616,13 +5616,13 @@
         <v>7</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>26</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V36" s="1" t="n">
         <v>12</v>
@@ -5631,44 +5631,44 @@
         <v>8</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y36" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA36" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB36" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="Z36" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA36" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB36" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C37" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="D37" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>5</v>
@@ -5677,110 +5677,110 @@
         <v>6</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P37" s="1" t="n">
         <v>2</v>
       </c>
       <c r="Q37" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="R37" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R37" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V37" s="1" t="n">
         <v>12</v>
       </c>
       <c r="W37" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X37" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y37" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z37" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB37" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="X37" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y37" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z37" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA37" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB37" s="1" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="M38" s="1" t="n">
         <v>15</v>
       </c>
       <c r="N38" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="O38" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="P38" s="1" t="n">
         <v>2</v>
@@ -5789,34 +5789,34 @@
         <v>7</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V38" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="W38" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="X38" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y38" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="W38" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="X38" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y38" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Z38" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB38" s="1" t="n">
         <v>10</v>
@@ -5825,11 +5825,11 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>26</v>
@@ -5844,13 +5844,13 @@
         <v>22</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>3</v>
@@ -5862,13 +5862,13 @@
         <v>18</v>
       </c>
       <c r="M39" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="N39" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="O39" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="P39" s="1" t="n">
         <v>2</v>
@@ -5877,7 +5877,7 @@
         <v>7</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S39" s="1" t="n">
         <v>1</v>
@@ -5886,44 +5886,44 @@
         <v>25</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="W39" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="X39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA39" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AB39" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>27</v>
@@ -5944,19 +5944,19 @@
         <v>3</v>
       </c>
       <c r="K40" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="L40" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N40" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O40" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N40" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="O40" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="P40" s="1" t="n">
         <v>2</v>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>5</v>
@@ -5992,7 +5992,7 @@
         <v>21</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB40" s="1" t="n">
         <v>12</v>
@@ -6001,17 +6001,17 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>27</v>
@@ -6020,7 +6020,7 @@
         <v>22</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>4</v>
@@ -6029,31 +6029,31 @@
         <v>6</v>
       </c>
       <c r="J41" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N41" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O41" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="P41" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="L41" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="N41" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="O41" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P41" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>1</v>
@@ -6068,47 +6068,47 @@
         <v>8</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA41" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB41" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C42" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" s="1" t="n">
         <v>26</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F42" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>4</v>
@@ -6117,74 +6117,74 @@
         <v>6</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L42" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N42" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="M42" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="N42" s="1" t="n">
-        <v>17</v>
-      </c>
       <c r="O42" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P42" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA42" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="AA42" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="AB42" s="1" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>24</v>
@@ -6193,79 +6193,79 @@
         <v>27</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P43" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S43" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V43" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W43" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W43" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="X43" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z43" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB43" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -6275,16 +6275,16 @@
         <v>14</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>4</v>
@@ -6296,7 +6296,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L44" s="1" t="n">
         <v>11</v>
@@ -6305,7 +6305,7 @@
         <v>12</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O44" s="1" t="n">
         <v>10</v>
@@ -6314,10 +6314,10 @@
         <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>2</v>
@@ -6326,7 +6326,7 @@
         <v>23</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V44" s="1" t="n">
         <v>9</v>
@@ -6335,13 +6335,13 @@
         <v>15</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y44" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA44" s="1" t="n">
         <v>26</v>
@@ -6353,26 +6353,26 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F45" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>4</v>
@@ -6384,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L45" s="1" t="n">
         <v>11</v>
@@ -6393,7 +6393,7 @@
         <v>12</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O45" s="1" t="n">
         <v>10</v>
@@ -6402,16 +6402,16 @@
         <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R45" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="R45" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>8</v>
@@ -6420,28 +6420,28 @@
         <v>9</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X45" s="1" t="n">
         <v>22</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z45" s="1" t="n">
         <v>24</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB45" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -6451,7 +6451,7 @@
         <v>13</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>27</v>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L46" s="1" t="n">
         <v>11</v>
@@ -6487,7 +6487,7 @@
         <v>10</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>6</v>
@@ -6496,10 +6496,10 @@
         <v>7</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U46" s="1" t="n">
         <v>8</v>
@@ -6517,7 +6517,7 @@
         <v>16</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA46" s="1" t="n">
         <v>25</v>
@@ -6529,26 +6529,26 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>27</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>4</v>
@@ -6560,7 +6560,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L47" s="1" t="n">
         <v>11</v>
@@ -6569,28 +6569,28 @@
         <v>12</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O47" s="1" t="n">
         <v>10</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R47" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="U47" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S47" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T47" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U47" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="V47" s="1" t="n">
         <v>9</v>
@@ -6599,16 +6599,16 @@
         <v>14</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z47" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB47" s="1" t="n">
         <v>15</v>
@@ -6617,11 +6617,11 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>25</v>
@@ -6630,13 +6630,13 @@
         <v>22</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>4</v>
@@ -6645,43 +6645,43 @@
         <v>5</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L48" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R48" s="1" t="n">
         <v>8</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W48" s="1" t="n">
         <v>14</v>
@@ -6690,13 +6690,13 @@
         <v>21</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z48" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA48" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="AA48" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="AB48" s="1" t="n">
         <v>15</v>
@@ -6705,23 +6705,23 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>12</v>
@@ -6733,10 +6733,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L49" s="1" t="n">
         <v>11</v>
@@ -6751,13 +6751,13 @@
         <v>9</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>1</v>
@@ -6766,7 +6766,7 @@
         <v>17</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V49" s="1" t="n">
         <v>10</v>
@@ -6775,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="X49" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y49" s="1" t="n">
         <v>18</v>
@@ -6793,7 +6793,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -6803,7 +6803,7 @@
         <v>25</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>27</v>
@@ -6812,16 +6812,16 @@
         <v>20</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50" s="1" t="n">
         <v>19</v>
@@ -6830,16 +6830,16 @@
         <v>11</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N50" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>6</v>
@@ -6854,7 +6854,7 @@
         <v>17</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V50" s="1" t="n">
         <v>10</v>
@@ -6863,16 +6863,16 @@
         <v>14</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y50" s="1" t="n">
         <v>18</v>
       </c>
       <c r="Z50" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA50" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="AA50" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="AB50" s="1" t="n">
         <v>15</v>
@@ -6881,26 +6881,26 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>2</v>
@@ -6912,28 +6912,28 @@
         <v>5</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L51" s="1" t="n">
         <v>11</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N51" s="1" t="n">
         <v>16</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P51" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Q51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="R51" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>1</v>
@@ -6942,7 +6942,7 @@
         <v>17</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V51" s="1" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
         <v>14</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y51" s="1" t="n">
         <v>18</v>
@@ -6960,7 +6960,7 @@
         <v>23</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB51" s="1" t="n">
         <v>15</v>
@@ -6969,32 +6969,32 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>21</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>12</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>5</v>
@@ -7009,65 +7009,65 @@
         <v>13</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O52" s="1" t="n">
         <v>9</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R52" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S52" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="U52" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="S52" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="T52" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="U52" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="V52" s="1" t="n">
         <v>10</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>22</v>
       </c>
       <c r="AB52" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>25</v>
@@ -7076,22 +7076,22 @@
         <v>14</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M53" s="1" t="n">
         <v>13</v>
@@ -7100,28 +7100,28 @@
         <v>17</v>
       </c>
       <c r="O53" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R53" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="P53" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q53" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="R53" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="S53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" s="1" t="n">
         <v>18</v>
       </c>
       <c r="U53" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="V53" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="V53" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W53" s="1" t="n">
         <v>15</v>
@@ -7133,7 +7133,7 @@
         <v>19</v>
       </c>
       <c r="Z53" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA53" s="1" t="n">
         <v>22</v>
@@ -7145,7 +7145,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
@@ -7155,31 +7155,31 @@
         <v>24</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I54" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J54" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="K54" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M54" s="1" t="n">
         <v>13</v>
@@ -7188,7 +7188,7 @@
         <v>17</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P54" s="1" t="n">
         <v>5</v>
@@ -7197,16 +7197,16 @@
         <v>6</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V54" s="1" t="n">
         <v>9</v>
@@ -7218,13 +7218,13 @@
         <v>26</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z54" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA54" s="1" t="n">
         <v>22</v>
-      </c>
-      <c r="AA54" s="1" t="n">
-        <v>25</v>
       </c>
       <c r="AB54" s="1" t="n">
         <v>16</v>
@@ -7233,41 +7233,41 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D55" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="E55" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>14</v>
       </c>
       <c r="G55" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="H55" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="L55" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>13</v>
@@ -7276,25 +7276,25 @@
         <v>17</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V55" s="1" t="n">
         <v>9</v>
@@ -7306,10 +7306,10 @@
         <v>26</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA55" s="1" t="n">
         <v>25</v>
@@ -7321,23 +7321,23 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>11</v>
@@ -7361,7 +7361,7 @@
         <v>13</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O56" s="1" t="n">
         <v>8</v>
@@ -7379,16 +7379,16 @@
         <v>1</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U56" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="V56" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="W56" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>26</v>
@@ -7397,19 +7397,19 @@
         <v>20</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB56" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
@@ -7419,7 +7419,7 @@
         <v>24</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>21</v>
@@ -7437,7 +7437,7 @@
         <v>5</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57" s="1" t="n">
         <v>19</v>
@@ -7452,19 +7452,19 @@
         <v>16</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T57" s="1" t="n">
         <v>17</v>
@@ -7485,7 +7485,7 @@
         <v>20</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>25</v>
@@ -7497,7 +7497,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -7507,43 +7507,43 @@
         <v>24</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H58" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I58" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K58" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L58" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="L58" s="1" t="n">
-        <v>11</v>
       </c>
       <c r="M58" s="1" t="n">
         <v>13</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="1" t="n">
         <v>6</v>
@@ -7552,19 +7552,19 @@
         <v>8</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X58" s="1" t="n">
         <v>26</v>
@@ -7573,19 +7573,19 @@
         <v>20</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA58" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB58" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -7595,16 +7595,16 @@
         <v>24</v>
       </c>
       <c r="D59" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="E59" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="F59" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G59" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>3</v>
@@ -7616,10 +7616,10 @@
         <v>5</v>
       </c>
       <c r="K59" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="L59" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="L59" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="M59" s="1" t="n">
         <v>13</v>
@@ -7631,25 +7631,25 @@
         <v>10</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T59" s="1" t="n">
         <v>19</v>
       </c>
       <c r="U59" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="V59" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="V59" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="W59" s="1" t="n">
         <v>15</v>
@@ -7658,10 +7658,10 @@
         <v>26</v>
       </c>
       <c r="Y59" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z59" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z59" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>25</v>
@@ -7673,23 +7673,23 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D60" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>22</v>
-      </c>
       <c r="F60" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>18</v>
@@ -7701,46 +7701,46 @@
         <v>4</v>
       </c>
       <c r="J60" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="L60" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M60" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="K60" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="L60" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="M60" s="1" t="n">
-        <v>14</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>26</v>
@@ -7749,35 +7749,35 @@
         <v>21</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB60" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>18</v>
@@ -7789,31 +7789,31 @@
         <v>4</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K61" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N61" s="1" t="n">
         <v>17</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S61" s="1" t="n">
         <v>2</v>
@@ -7822,98 +7822,98 @@
         <v>20</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X61" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA61" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB61" s="1" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D62" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D62" s="1" t="n">
+      <c r="E62" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>19</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M62" s="1" t="n">
         <v>12</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S62" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T62" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U62" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="V62" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="V62" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="W62" s="1" t="n">
         <v>14</v>
@@ -7922,7 +7922,7 @@
         <v>26</v>
       </c>
       <c r="Y62" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z62" s="1" t="n">
         <v>21</v>
@@ -7937,17 +7937,17 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D63" s="1" t="n">
         <v>23</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>24</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>22</v>
@@ -7956,31 +7956,31 @@
         <v>19</v>
       </c>
       <c r="G63" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I63" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L63" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N63" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="H63" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J63" s="1" t="n">
+      <c r="O63" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="K63" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="L63" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="M63" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="N63" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="O63" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="P63" s="1" t="n">
         <v>1</v>
@@ -7989,65 +7989,65 @@
         <v>5</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S63" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T63" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U63" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V63" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W63" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X63" s="1" t="n">
         <v>26</v>
       </c>
       <c r="Y63" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z63" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="Z63" s="1" t="n">
-        <v>20</v>
       </c>
       <c r="AA63" s="1" t="n">
         <v>25</v>
       </c>
       <c r="AB63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D64" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E64" s="1" t="n">
+      <c r="G64" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F64" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="H64" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>8</v>
@@ -8056,16 +8056,16 @@
         <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L64" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" s="1" t="n">
         <v>14</v>
-      </c>
-      <c r="M64" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="N64" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>4</v>
@@ -8077,7 +8077,7 @@
         <v>5</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S64" s="1" t="n">
         <v>2</v>
@@ -8086,34 +8086,34 @@
         <v>12</v>
       </c>
       <c r="U64" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V64" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W64" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="X64" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y64" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="X64" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y64" s="1" t="n">
-        <v>23</v>
-      </c>
       <c r="Z64" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA64" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB64" s="1" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
@@ -8126,16 +8126,16 @@
         <v>20</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>15</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>8</v>
@@ -8150,7 +8150,7 @@
         <v>14</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N65" s="1" t="n">
         <v>16</v>
@@ -8165,7 +8165,7 @@
         <v>5</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S65" s="1" t="n">
         <v>2</v>
@@ -8174,7 +8174,7 @@
         <v>12</v>
       </c>
       <c r="U65" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V65" s="1" t="n">
         <v>9</v>
@@ -8201,17 +8201,17 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C66" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="D66" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>19</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>17</v>
@@ -8223,7 +8223,7 @@
         <v>15</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>8</v>
@@ -8238,7 +8238,7 @@
         <v>14</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N66" s="1" t="n">
         <v>16</v>
@@ -8253,16 +8253,16 @@
         <v>5</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S66" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T66" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U66" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V66" s="1" t="n">
         <v>9</v>
@@ -8289,29 +8289,29 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C67" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D67" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D67" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="E67" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F67" s="1" t="n">
         <v>18</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>8</v>
@@ -8320,10 +8320,10 @@
         <v>3</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M67" s="1" t="n">
         <v>10</v>
@@ -8341,7 +8341,7 @@
         <v>5</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S67" s="1" t="n">
         <v>2</v>

--- a/NSE_Sector_Monitor.xlsx
+++ b/NSE_Sector_Monitor.xlsx
@@ -552,46 +552,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>91.83</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>-4.75</v>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -627,28 +627,28 @@
         <v>-1</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>27.08</v>
+        <v>89.66</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.31</v>
+        <v>-2.36</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.24</v>
+        <v>-0.38</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2.4</v>
+        <v>3.66</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.15</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>0</v>
+        <v>-5.83</v>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -689,31 +689,31 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>17.17</v>
+        <v>17.21</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.06</v>
+        <v>0.23</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>9.84</v>
+        <v>9.19</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         <v>17</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>53.1</v>
+        <v>52.65</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.45</v>
+        <v>-0.85</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>-1.92</v>
+        <v>-2.17</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>-4.29</v>
+        <v>-6.45</v>
       </c>
       <c r="K5" s="1" t="n">
         <v/>
@@ -819,31 +819,31 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>13.65</v>
+        <v>13.63</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.19</v>
+        <v>-0.15</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>6.93</v>
+        <v>4.08</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>9.09</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -884,31 +884,31 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>89.2</v>
+        <v>88.95</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.8</v>
+        <v>-0.28</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>5.11</v>
+        <v>4.75</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>10.56</v>
+        <v>10.98</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7.71</v>
+        <v>6.99</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>-9.51</v>
+        <v>-9.77</v>
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
@@ -942,38 +942,38 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>79.34999999999999</v>
+        <v>291.79</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.83</v>
+        <v>1.53</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.68</v>
+        <v>1.22</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>-2.1</v>
+        <v>4.59</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>5.33</v>
+        <v>6.62</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>-16.52</v>
+        <v>-0.51</v>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
@@ -1017,28 +1017,28 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10</v>
+        <v>-3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>287.38</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>1.07</v>
+        <v>0.26</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>3.64</v>
+        <v>-3.13</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>5.13</v>
+        <v>4.43</v>
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-2.01</v>
+        <v>-17.23</v>
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P9" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -1091,19 +1091,19 @@
         <v>18</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>32.05</v>
+        <v>32.29</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0.33</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>4.84</v>
+        <v>4.37</v>
       </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1156,19 +1156,19 @@
         <v>15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>34.54</v>
+        <v>34.62</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>2.28</v>
+        <v>0.23</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>7.96</v>
+        <v>7.34</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>16.48</v>
+        <v>19.67</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>4.5</v>
+        <v>3.66</v>
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>-20.6</v>
+        <v>-20.42</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1202,38 +1202,38 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>30.37</v>
+        <v>134.51</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-1.73</v>
+        <v>1.07</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.93</v>
+        <v>2.56</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>4.36</v>
+        <v>3</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1260,72 +1260,72 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>133.71</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>-5.3</v>
-      </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1339,31 +1339,31 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>28.11</v>
+        <v>28.06</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.22</v>
+        <v>-0.18</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-0.71</v>
+        <v>-0.78</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>-2.4</v>
+        <v>-3.28</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>-5.05</v>
+        <v>-5.22</v>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
@@ -1404,31 +1404,31 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>591.74</v>
+        <v>591.08</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.71</v>
+        <v>-0.11</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-0.97</v>
+        <v>-0.86</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>-2.29</v>
+        <v>-2.76</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-6.34</v>
+        <v>-6.45</v>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
@@ -1462,38 +1462,38 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Fin Services</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>32.77</v>
+        <v>164.26</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.43</v>
+        <v>-0.25</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.6</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1527,46 +1527,46 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fin Services</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="E17" s="2" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>31.45</v>
+        <v>32.58</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>1.42</v>
+        <v>-0.58</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-1.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1.15</v>
+        <v>-1.37</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1.11</v>
+        <v>0.59</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
@@ -1585,53 +1585,53 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>163.6</v>
+        <v>31.28</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.92</v>
+        <v>-0.54</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>-0.29</v>
+        <v>0.01</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.59</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.78</v>
+        <v>0.47</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>-1.79</v>
+        <v>0</v>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
@@ -1650,45 +1650,45 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Defence</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>101.16</v>
+        <v>33.76</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-2.92</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>-4.83</v>
+        <v>-1.15</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.21</v>
+        <v>-0.33</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>-5.83</v>
+        <v>-2.59</v>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -1722,38 +1722,38 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNC</t>
+          <t>Defence</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-5</v>
+        <v>-18</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>33.75</v>
+        <v>100.73</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.93</v>
+        <v>-0.43</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-0.45</v>
+        <v>-3.63</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.85</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.1</v>
+        <v>-0.64</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>-2.61</v>
+        <v>-6.23</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr">
@@ -1787,38 +1787,38 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>95.84</v>
+        <v>12.77</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.7</v>
+        <v>0.16</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-1.3</v>
+        <v>-0.02</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>-2.1</v>
+        <v>1.67</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>-3.39</v>
+        <v>-3.1</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1826,64 +1826,64 @@
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>-4.23</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P21" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>PSU Bank</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>92.98999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>-1.61</v>
+        <v>-0.99</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>-3.7</v>
+        <v>-1.88</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>-5.09</v>
+        <v>-3.46</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1891,64 +1891,64 @@
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>-15.49</v>
+        <v>-3.91</v>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P22" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>PSU Bank</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-19</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>12.75</v>
+        <v>93.16</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>2.33</v>
+        <v>0.18</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>-0.18</v>
+        <v>-1.29</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>-0.04</v>
+        <v>-3.94</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>-5.19</v>
+        <v>-4.29</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="M23" s="1" t="n">
-        <v>-10</v>
+        <v>-15.34</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1992,28 +1992,28 @@
         <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>-3</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>-2</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>-8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>53.27</v>
+        <v>53.23</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.6</v>
+        <v>-0.08</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.64</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.2</v>
+        <v>-1.28</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>-5.62</v>
+        <v>-5.43</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="M24" s="1" t="n">
-        <v>-14.67</v>
+        <v>-14.73</v>
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
@@ -2060,25 +2060,25 @@
         <v>-1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>-19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>99.92</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>-1.86</v>
+        <v>-1.59</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>-1.42</v>
+        <v>-0.62</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>-6.97</v>
+        <v>-7.05</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
         </is>
       </c>
       <c r="M25" s="1" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2119,31 +2119,31 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="D26" s="2" t="n">
-        <v>-1</v>
-      </c>
       <c r="E26" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>11.24</v>
+        <v>11.3</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>-2.11</v>
+        <v>-1.41</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>-1.26</v>
+        <v>-0.51</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>-7.8</v>
+        <v>-7.61</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2151,11 +2151,11 @@
         </is>
       </c>
       <c r="M26" s="1" t="n">
-        <v>-10.24</v>
+        <v>-9.76</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2184,31 +2184,31 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>-25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>38.23</v>
+        <v>38.46</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.6</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>-3.95</v>
+        <v>-3.15</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>-5.6</v>
+        <v>-4.39</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>-8.83</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2249,31 +2249,31 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>-23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>-2.13</v>
+        <v>-2.25</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>-2.39</v>
+        <v>-1.8</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.31</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-10.63</v>
+        <v>-10.37</v>
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -2582,34 +2582,34 @@
         <v>13</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>23</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O2" s="1" t="n">
         <v>27</v>
@@ -2621,19 +2621,19 @@
         <v>24</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>19</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>18</v>
       </c>
       <c r="T2" s="1" t="n">
         <v>25</v>
       </c>
       <c r="U2" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W2" s="1" t="n">
         <v>4</v>
@@ -2645,10 +2645,10 @@
         <v>5</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>9</v>
@@ -2657,26 +2657,26 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>2</v>
@@ -2685,13 +2685,13 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>20</v>
@@ -2706,19 +2706,19 @@
         <v>26</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="R3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="U3" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V3" s="1" t="n">
         <v>17</v>
@@ -2733,35 +2733,35 @@
         <v>5</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA3" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>21</v>
@@ -2779,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>20</v>
@@ -2791,56 +2791,56 @@
         <v>27</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>25</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T4" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U4" s="1" t="n">
+      <c r="V4" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="W4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V4" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="W4" s="1" t="n">
+      <c r="X4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X4" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Y4" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB4" s="1" t="n">
         <v>8</v>
-      </c>
-      <c r="AA4" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB4" s="1" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>17</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>14</v>
@@ -2852,7 +2852,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
@@ -2861,25 +2861,25 @@
         <v>3</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>20</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>25</v>
@@ -2888,50 +2888,50 @@
         <v>16</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>11</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB5" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="AA5" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB5" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>26</v>
@@ -2949,7 +2949,7 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1</v>
@@ -2958,25 +2958,25 @@
         <v>18</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O6" s="1" t="n">
         <v>27</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" s="1" t="n">
         <v>21</v>
@@ -2988,74 +2988,74 @@
         <v>12</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z6" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>17</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>23</v>
@@ -3064,56 +3064,56 @@
         <v>13</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="Z7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB7" s="1" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F8" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>24</v>
@@ -3122,61 +3122,61 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L8" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O8" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB8" s="1" t="n">
         <v>8</v>
@@ -3185,47 +3185,47 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>13</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M9" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>26</v>
@@ -3249,16 +3249,16 @@
         <v>4</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="1" t="n">
         <v>9</v>
@@ -3267,29 +3267,29 @@
         <v>20</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>22</v>
@@ -3313,22 +3313,22 @@
         <v>18</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>21</v>
@@ -3337,50 +3337,50 @@
         <v>4</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>17</v>
       </c>
       <c r="Y10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Z10" s="1" t="n">
+      <c r="AA10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB10" s="1" t="n">
         <v>10</v>
-      </c>
-      <c r="AA10" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB10" s="1" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2</v>
@@ -3398,7 +3398,7 @@
         <v>16</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N11" s="1" t="n">
         <v>14</v>
@@ -3407,68 +3407,68 @@
         <v>26</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>23</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S11" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="T11" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="U11" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="W11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="X11" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y11" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Z11" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB11" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>25</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2</v>
@@ -3477,25 +3477,25 @@
         <v>3</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O12" s="1" t="n">
         <v>26</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>23</v>
@@ -3504,31 +3504,31 @@
         <v>9</v>
       </c>
       <c r="S12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T12" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="V12" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>10</v>
@@ -3537,23 +3537,23 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>20</v>
@@ -3565,13 +3565,13 @@
         <v>3</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>18</v>
@@ -3580,10 +3580,10 @@
         <v>15</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>23</v>
@@ -3598,25 +3598,25 @@
         <v>24</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W13" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB13" s="1" t="n">
         <v>10</v>
@@ -3625,26 +3625,26 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C14" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>16</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>13</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>22</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>2</v>
@@ -3665,13 +3665,13 @@
         <v>18</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O14" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>23</v>
@@ -3689,7 +3689,7 @@
         <v>8</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W14" s="1" t="n">
         <v>4</v>
@@ -3704,7 +3704,7 @@
         <v>7</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB14" s="1" t="n">
         <v>10</v>
@@ -3713,7 +3713,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
@@ -3723,16 +3723,16 @@
         <v>16</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>2</v>
@@ -3750,22 +3750,22 @@
         <v>11</v>
       </c>
       <c r="M15" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="N15" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="O15" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S15" s="1" t="n">
         <v>6</v>
@@ -3777,13 +3777,13 @@
         <v>8</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X15" s="1" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Y15" s="1" t="n">
         <v>5</v>
@@ -3792,71 +3792,71 @@
         <v>7</v>
       </c>
       <c r="AA15" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB15" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>20</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>17</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>11</v>
-      </c>
       <c r="Q16" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T16" s="1" t="n">
         <v>24</v>
@@ -3868,132 +3868,132 @@
         <v>13</v>
       </c>
       <c r="W16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y16" s="1" t="n">
         <v>5</v>
-      </c>
-      <c r="X16" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y16" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Z16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB16" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O17" s="1" t="n">
         <v>25</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17" s="1" t="n">
         <v>13</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB17" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>20</v>
@@ -4002,7 +4002,7 @@
         <v>6</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>19</v>
@@ -4023,10 +4023,10 @@
         <v>25</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>10</v>
@@ -4035,53 +4035,53 @@
         <v>2</v>
       </c>
       <c r="T18" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="X18" s="1" t="n">
         <v>24</v>
-      </c>
-      <c r="U18" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="W18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="X18" s="1" t="n">
-        <v>23</v>
       </c>
       <c r="Y18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB18" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>26</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>20</v>
@@ -4090,25 +4090,25 @@
         <v>6</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P19" s="1" t="n">
         <v>17</v>
@@ -4117,31 +4117,31 @@
         <v>22</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S19" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T19" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="W19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="U19" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="W19" s="1" t="n">
+      <c r="Y19" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="X19" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y19" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z19" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="AA19" s="1" t="n">
         <v>21</v>
@@ -4153,32 +4153,32 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>12</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>18</v>
@@ -4187,13 +4187,13 @@
         <v>1</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>24</v>
@@ -4205,28 +4205,28 @@
         <v>22</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="1" t="n">
         <v>5</v>
@@ -4235,68 +4235,68 @@
         <v>21</v>
       </c>
       <c r="AB20" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="E21" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>18</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>14</v>
+